--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.5%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.6%</t>
+          <t>-659.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.3%</t>
+          <t>-153.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-191.6%</t>
+          <t>-192.2%</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-91.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.2%</t>
+          <t>-232.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-67.8%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.94171006726932</v>
+        <v>-4.879970580450472</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9849481994925329</v>
+        <v>1.009643994220072</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2202129852772741</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.72168926923231</v>
+        <v>-4.659949782413461</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.074535555717951</v>
+        <v>1.099231350445491</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3614328303452544</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.588821580169032</v>
+        <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.143576814145085</v>
+        <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3614328303452544</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.468648496804533</v>
+        <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.192791891931187</v>
+        <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4816059137097533</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.323976351704796</v>
+        <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.260748852532522</v>
+        <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6262780588094907</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.383851179062488</v>
+        <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.222836412990871</v>
+        <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5664032314517986</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.264030948151651</v>
+        <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.286053674589414</v>
+        <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5664032314517986</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.266500654613457</v>
+        <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.192709991327133</v>
+        <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5639335249899924</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.334870840937468</v>
+        <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.084623778282831</v>
+        <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5732092240262073</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.348658893784514</v>
+        <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.069545265775903</v>
+        <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5732092240262073</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.404178969677104</v>
+        <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.18436807211107</v>
+        <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5732092240262073</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.228704709884635</v>
+        <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.259125008019845</v>
+        <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5732092240262073</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.339640962525884</v>
+        <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.190492535724552</v>
+        <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5732092240262073</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.305977417053602</v>
+        <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132496267314915</v>
+        <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6068727694984892</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.246124797849879</v>
+        <v>-4.184385311031029</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166609701428537</v>
+        <v>1.191305496156077</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6068727694984892</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.159881334823501</v>
+        <v>-4.098141848004651</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.196053357212948</v>
+        <v>1.220749151940488</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6068727694984892</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.205188154222481</v>
+        <v>-4.143448667403631</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169706404897882</v>
+        <v>1.194402199625421</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5660626064892584</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.234221258924782</v>
+        <v>-4.172481772105932</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158645036050063</v>
+        <v>1.183340830777603</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5660626064892584</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.141410777473922</v>
+        <v>-4.079671290655073</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.125041920521772</v>
+        <v>1.149737715249312</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6588730879401178</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.18580024680335</v>
+        <v>-4.1240607599845</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.109159608714602</v>
+        <v>1.133855403442142</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6144836186106901</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.302341851908692</v>
+        <v>-4.240602365089843</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.057618675184188</v>
+        <v>1.082314469911728</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4979420135053474</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.189964850726019</v>
+        <v>-4.12822536390717</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.108060771487925</v>
+        <v>1.132756566215464</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4979420135053474</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.217745248627372</v>
+        <v>-4.156005761808522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.108445814095923</v>
+        <v>1.133141608823462</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4701616156039943</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.33612592135751</v>
+        <v>-4.274386434538661</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8994492650045205</v>
+        <v>0.9241450597320604</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4029437634530181</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.444739999800841</v>
+        <v>-4.383000512981992</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9761532943463938</v>
+        <v>1.000849089073933</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4029437634530181</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.409330961552699</v>
+        <v>-4.347591474733849</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.004829935747974</v>
+        <v>1.029525730475514</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4029437634530181</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.370947298994547</v>
+        <v>-4.309207812175698</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.017602842113603</v>
+        <v>1.042298636841143</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4413274260111693</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.193830968959381</v>
+        <v>-4.132091482140532</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.085178402972971</v>
+        <v>1.109874197700511</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4413274260111693</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.238923213792927</v>
+        <v>-4.177183726974078</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.067824896801466</v>
+        <v>1.092520691529006</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3794313828417795</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.059547792554159</v>
+        <v>-3.99780830573531</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.133362040603388</v>
+        <v>1.158057835330927</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5362081410124981</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.104562006074765</v>
+        <v>-4.042822519255916</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.096163810526735</v>
+        <v>1.120859605254275</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5058592456978935</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.3715665163472</v>
+        <v>-4.309827029528351</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9950535687567068</v>
+        <v>1.019749363484246</v>
       </c>
       <c r="F1959" t="n">
         <v>0.311496207654945</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.472764297784373</v>
+        <v>-4.411024810965523</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9537783780783391</v>
+        <v>0.9784741728058788</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2430873941096258</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.46625333117006</v>
+        <v>-4.404513844351211</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9539827262783809</v>
+        <v>0.9786785210059206</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2430873941096258</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.447215203462763</v>
+        <v>-4.385475716643914</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9581226965695446</v>
+        <v>0.9828184912970845</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1849037827784312</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.478341834613381</v>
+        <v>-4.416602347794532</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.064966445743488</v>
+        <v>1.089662240471027</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1849037827784312</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.492208595947299</v>
+        <v>-4.43046910912845</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.060253070196054</v>
+        <v>1.084948864923594</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1470458660446083</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.447404424407369</v>
+        <v>-4.38566493758852</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.084183269208952</v>
+        <v>1.108879063936492</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1470458660446083</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.299661454172367</v>
+        <v>-4.237921967353517</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.041230678580153</v>
+        <v>1.065926473307692</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3148532232794914</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.383482675447065</v>
+        <v>-4.321743188628216</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.010495811601754</v>
+        <v>1.035191606329294</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3148532232794914</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.377329969394281</v>
+        <v>-4.315590482575431</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.013619242414526</v>
+        <v>1.038315037142066</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3210059293322757</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.394139267544783</v>
+        <v>-4.332399780725933</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.005975999894436</v>
+        <v>1.030671794621975</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3041966311817741</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.33184126876866</v>
+        <v>-4.270101781949811</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.097230753201706</v>
+        <v>1.121926547929245</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3041966311817741</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.130051071103503</v>
+        <v>-4.068311584284653</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9802388339818957</v>
+        <v>1.004934628709436</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5022148233509285</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.180937783789697</v>
+        <v>-4.119198296970848</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.030174381229593</v>
+        <v>1.054870175957133</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4513281106647339</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.278678328414672</v>
+        <v>-4.216938841595822</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.005705899495647</v>
+        <v>1.030401694223187</v>
       </c>
       <c r="F1973" t="n">
         <v>0.4354388325317538</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.338887626419957</v>
+        <v>-4.277148139601107</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9801581611182046</v>
+        <v>1.004853955845745</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3752295345264692</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.26246557998803</v>
+        <v>-4.20072609316918</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.009218597730904</v>
+        <v>1.033914392458444</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.218092448349461</v>
+        <v>-4.156352961530612</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.026830717821768</v>
+        <v>1.051526512549307</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.240572799208346</v>
+        <v>-4.178833312389497</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.012232371616804</v>
+        <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4196026661650378</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190328</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.19291706864729</v>
+        <v>-4.131177581828441</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.037676420869031</v>
+        <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4672583967260935</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.82267821056962</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.092398910148535</v>
+        <v>-4.030659423329686</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.082776057643258</v>
+        <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
         <v>0.567776555224848</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.153065500550925</v>
+        <v>-4.091326013732075</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.045264093958174</v>
+        <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4860782385063144</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.108227098942526</v>
+        <v>-4.046487612123677</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.067297157212162</v>
+        <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4906216714511838</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.127725555184535</v>
+        <v>-4.065986068365685</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.063658714346437</v>
+        <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4425370301712795</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.083522718098634</v>
+        <v>-4.021783231279785</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.087219451708634</v>
+        <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
         <v>0.48673986725718</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.120501745762077</v>
+        <v>-4.058762258943228</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.070837841112505</v>
+        <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5237137690485105</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.962210328222805</v>
+        <v>-3.900470841403955</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.185402173311253</v>
+        <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5237137690485105</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.754568324588329</v>
+        <v>-3.692828837769479</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.266899679359297</v>
+        <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7313557726829867</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.7035362318658</v>
+        <v>-3.641796745046951</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.282260744686578</v>
+        <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7823878654055146</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.638312050738595</v>
+        <v>-3.576572563919745</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.325537821230165</v>
+        <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8476120465327203</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.600885030667461</v>
+        <v>-3.539145543848611</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.336469601557899</v>
+        <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8528635845619019</v>
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.620996686702169</v>
+        <v>-3.623940245222266</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.329681731475256</v>
+        <v>1.328504308067218</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8638909295593211</v>
+        <v>0.8723798291916631</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.296771388205464</v>
+        <v>3.301864727984869</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.567251872274964</v>
+        <v>-3.570195430795061</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.511737428267349</v>
+        <v>1.51056000485931</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8739542389997831</v>
+        <v>0.8824431386321251</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.463367144890952</v>
+        <v>3.468460484670358</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.492469611249952</v>
+        <v>-3.495413169770048</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.661763241895171</v>
+        <v>1.660585818487132</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9572253996571377</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.628349410723777</v>
+        <v>3.633442750503182</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.466385526986144</v>
+        <v>-3.46932908550624</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.663904851614553</v>
+        <v>1.662727428206515</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9572253996571377</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.620057386737636</v>
+        <v>3.625150726517041</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.388254346137197</v>
+        <v>-3.391197904657294</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.693350519537911</v>
+        <v>1.692173096129873</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.02291331090848</v>
+        <v>1.031402210540822</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.662756668851626</v>
+        <v>3.667850008631031</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.379361884743914</v>
+        <v>-3.382305443264011</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.714461909822016</v>
+        <v>1.713284486413977</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.02291331090848</v>
+        <v>1.031402210540822</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.680311074578417</v>
+        <v>3.685404414357823</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.547838001713792</v>
+        <v>-3.550781560233889</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.638926510438649</v>
+        <v>1.63774908703061</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9949654751918995</v>
+        <v>1.003454374824241</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655397420553053</v>
+        <v>3.660490760332458</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.850038472852209</v>
+        <v>-2.852982031372306</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.899316019171144</v>
+        <v>1.898138595763105</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.9331063154538308</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.594458282118668</v>
+        <v>3.599551621898073</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.827317369169056</v>
+        <v>-2.830260927689153</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.89906848314131</v>
+        <v>1.897891059733271</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.9331063154538308</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.585122304615573</v>
+        <v>3.590215644394978</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.956519182463099</v>
+        <v>-2.959462740983196</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.006293883674862</v>
+        <v>2.005116460266823</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7954156025274466</v>
+        <v>0.8039045021597886</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.666507342490317</v>
+        <v>3.671600682269722</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.111300189241354</v>
+        <v>-3.114243747761451</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.981459303457206</v>
+        <v>1.980281880049167</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7620479284729704</v>
+        <v>0.7705368281053124</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.683564560551277</v>
+        <v>3.688657900330683</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.104245499026181</v>
+        <v>-3.107189057546277</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.980956535532821</v>
+        <v>1.979779112124782</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7691026186881442</v>
+        <v>0.7775915183204862</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.684472730669927</v>
+        <v>3.689566070449332</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.077294274699693</v>
+        <v>-3.08023783321979</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.001743178908157</v>
+        <v>2.000565755500118</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.7034070919313</v>
+        <v>3.708500431710705</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.213247282756009</v>
+        <v>-3.216190841276106</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.131465107830591</v>
+        <v>2.130287684422552</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.88751022407626</v>
+        <v>3.892603563855665</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.235655400560881</v>
+        <v>-3.238598959080978</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.114618555611635</v>
+        <v>2.113441132203596</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.879626918979253</v>
+        <v>3.884720258758658</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.38366116804028</v>
+        <v>-3.386604726560377</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.057470248169512</v>
+        <v>2.056292824761474</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6972559558523219</v>
+        <v>0.7057448554846639</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.829644713210765</v>
+        <v>3.834738052990171</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.39310209392881</v>
+        <v>-3.396045652448907</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.109947595535948</v>
+        <v>2.108770172127909</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8196830733957133</v>
+        <v>0.8281719730280553</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.959354701458647</v>
+        <v>3.964448041238052</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.445375701264452</v>
+        <v>-3.448319259784549</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.091929247146992</v>
+        <v>2.090751823738954</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7758983656924141</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.930881631602563</v>
+        <v>3.935974971381969</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.521705678865358</v>
+        <v>-3.524649237385455</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.059509069000405</v>
+        <v>2.058331645592366</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7758983656924141</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.928993444496339</v>
+        <v>3.934086784275744</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.723959399189711</v>
+        <v>-3.726902957709808</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.973427810473526</v>
+        <v>1.972250387065487</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5651557457357186</v>
+        <v>0.5736446453680606</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.802461441904589</v>
+        <v>3.807554781683994</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.885527824716966</v>
+        <v>-3.888471383237063</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.907234450472776</v>
+        <v>1.906057027064737</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.724825697836013</v>
+        <v>3.729919037615419</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.01782911681452</v>
+        <v>-4.020772675334617</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.867387340499673</v>
+        <v>1.866209917091634</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.737899104701932</v>
+        <v>3.742992444481337</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.019390759629379</v>
+        <v>-4.022334318149476</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.866762683373729</v>
+        <v>1.865585259965691</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.737899104701932</v>
+        <v>3.742992444481337</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392114</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.047291546738852</v>
+        <v>-4.050235105258949</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.854126409656942</v>
+        <v>1.852948986248903</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4037758977949044</v>
+        <v>0.4122647974272464</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.715664991343173</v>
+        <v>3.720758331122579</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.169817649441746</v>
+        <v>-4.172761207961843</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.801880412552983</v>
+        <v>1.800702989144945</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2812497950920105</v>
+        <v>0.2897386947243525</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.638913773698636</v>
+        <v>3.644007113478041</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971076</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.400332145627335</v>
+        <v>-4.403275704147432</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.776380573669252</v>
+        <v>1.775203150261213</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05073529890642181</v>
+        <v>0.05922419853876382</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.567311035577786</v>
+        <v>3.572404375357191</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.657052963622158</v>
+        <v>-4.659996522142256</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.814003965473169</v>
+        <v>1.81282654206513</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.642574010093345</v>
+        <v>3.64766734987275</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.811039381398299</v>
+        <v>-4.813982939918397</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.821389667508353</v>
+        <v>1.820212244100314</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.711554279238984</v>
+        <v>3.716647619018389</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.760517477570633</v>
+        <v>-4.763461036090731</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.82764963115954</v>
+        <v>1.826472207751501</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.697605481359105</v>
+        <v>3.70269882113851</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.012992631578357</v>
+        <v>-5.015936190098455</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.738530058611865</v>
+        <v>1.737352635203825</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.709475970414519</v>
+        <v>3.714569310193924</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.305888388057769</v>
+        <v>-5.308831946577867</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.622582290539043</v>
+        <v>1.621404867131004</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.710686504933463</v>
+        <v>3.715779844712868</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.463432459787211</v>
+        <v>-5.466376018307309</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.563686404074588</v>
+        <v>1.562508980666549</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1245810803776675</v>
+        <v>-0.1160921807453255</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.674667164076619</v>
+        <v>3.679760503856025</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.741396855370485</v>
+        <v>-5.744340413890582</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.447578498577468</v>
+        <v>1.446401075169429</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2057119150308098</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.615973176241519</v>
+        <v>3.621066516020924</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.858364548009376</v>
+        <v>-5.861308106529473</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.562995478220956</v>
+        <v>1.561818054812917</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2057119150308098</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.778177232940562</v>
+        <v>3.783270572719968</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.943082490230329</v>
+        <v>-5.946026048750427</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.523954939296388</v>
+        <v>1.522777515888349</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2993168435911981</v>
+        <v>-0.2908279439588561</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.721954253547549</v>
+        <v>3.727047593326954</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.025017308499212</v>
+        <v>-6.02796086701931</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.501410429557327</v>
+        <v>1.500233006149287</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3092515891782783</v>
+        <v>-0.3007626895459363</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.726222823763792</v>
+        <v>3.731316163543197</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.126993430747619</v>
+        <v>-6.129936989267717</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.469545619113866</v>
+        <v>1.468368195705827</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4112277114266859</v>
+        <v>-0.4027388117943439</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.67396278887065</v>
+        <v>3.679056128650055</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.016987147270398</v>
+        <v>-6.019930705790496</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.50570101974893</v>
+        <v>1.504523596340891</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3880231395094107</v>
+        <v>-0.3795342398770687</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.68003841926519</v>
+        <v>3.685131759044595</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.873927571529473</v>
+        <v>-5.876871130049571</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.567174860767274</v>
+        <v>1.565997437359235</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3800097129194314</v>
+        <v>-0.3715208132870894</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.689096485941152</v>
+        <v>3.694189825720557</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.572480846057635</v>
+        <v>-5.575424404577733</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.695014433838546</v>
+        <v>1.693837010430506</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.87722540410679</v>
+        <v>3.882318743886196</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.597071090292819</v>
+        <v>-5.600014648812917</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.686149513897182</v>
+        <v>1.684972090489143</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.878196581859501</v>
+        <v>3.883289921638906</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.546032714286299</v>
+        <v>-5.548976272806397</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.707407768679546</v>
+        <v>1.706230345271507</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.879039486239256</v>
+        <v>3.884132826018662</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.504893419419668</v>
+        <v>-5.507836977939766</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.742901585500344</v>
+        <v>1.741724162092304</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.03742369258096334</v>
+        <v>-0.02893479294862134</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.92276116203338</v>
+        <v>3.927854501812785</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085617</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.394287279340066</v>
+        <v>-5.397230837860164</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.603328037656119</v>
+        <v>1.602150614248079</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.07318244749863867</v>
+        <v>0.08167134713098068</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.805308842205076</v>
+        <v>3.810402181984481</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462779</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.524868013870909</v>
+        <v>-5.527811572391006</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.554597787917745</v>
+        <v>1.553420364509706</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.730462445560534</v>
+        <v>3.735555785339939</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218597</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.360371679679947</v>
+        <v>-5.363315238200045</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.604823140670212</v>
+        <v>1.603645717262173</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.714889264636617</v>
+        <v>3.719982604416022</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.235891198955995</v>
+        <v>-5.238834757476093</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.653803043396223</v>
+        <v>1.652625619988184</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.714076975073046</v>
+        <v>3.719170314852452</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.246276393845885</v>
+        <v>-5.249219952365983</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.65951774456534</v>
+        <v>1.658340321157301</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.06778348192209316</v>
+        <v>-0.05929458228975115</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.717714637264185</v>
+        <v>3.72280797704359</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83442965412042</v>
+        <v>3.834429654120423</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.26486455256811</v>
+        <v>-5.267808111088208</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.722919486852875</v>
+        <v>1.721742063444835</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.07788274101197651</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.777398747807275</v>
+        <v>3.782492087586681</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.123147804753705</v>
+        <v>-5.126091363273803</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.776475196796935</v>
+        <v>1.775297773388896</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.07788274101197651</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.774267758625574</v>
+        <v>3.779361098404979</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.821627292747972</v>
+        <v>3.835263801896224</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.960193438495192</v>
+        <v>-4.975369436950295</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.846187838239732</v>
+        <v>1.84011743885769</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.08181155168389148</v>
+        <v>-0.08046947582201458</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.781534706941221</v>
+        <v>3.782339952458347</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>126.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.1%</t>
+          <t>-666.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.5%</t>
+          <t>-153.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.2%</t>
+          <t>-195.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>-99.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-232.0%</t>
+          <t>-231.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-67.8%</t>
+          <t>-67.4%</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.527082093350184</v>
+        <v>-4.618984306435109</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.168272608872625</v>
+        <v>1.131511723638655</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3614328303452544</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.406909009985685</v>
+        <v>-4.498811223070611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.217487686658726</v>
+        <v>1.180726801424756</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4816059137097533</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.262236864885947</v>
+        <v>-4.354139077970873</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.285444647260061</v>
+        <v>1.248683762026091</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6262780588094907</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.32211169224364</v>
+        <v>-4.414013905328566</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24753220771841</v>
+        <v>1.21077132248444</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5664032314517986</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.202291461332803</v>
+        <v>-4.294193674417729</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.310749469316953</v>
+        <v>1.273988584082983</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5664032314517986</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.204761167794609</v>
+        <v>-4.296663380879535</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.217405786054673</v>
+        <v>1.180644900820702</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5639335249899924</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.273131354118619</v>
+        <v>-4.365033567203545</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10931957301037</v>
+        <v>1.0725586877764</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5732092240262073</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.286919406965666</v>
+        <v>-4.378821620050592</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094241060503442</v>
+        <v>1.057480175269472</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5732092240262073</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.342439482858255</v>
+        <v>-4.434341695943181</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.209063866838609</v>
+        <v>1.172302981604639</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5732092240262073</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.166965223065786</v>
+        <v>-4.258867436150712</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.283820802747385</v>
+        <v>1.247059917513414</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5732092240262073</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.277901475707035</v>
+        <v>-4.369803688791961</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.215188330452092</v>
+        <v>1.178427445218122</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5732092240262073</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.244237930234752</v>
+        <v>-4.336140143319679</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.157192062042455</v>
+        <v>1.120431176808484</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6068727694984892</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.184385311031029</v>
+        <v>-4.276287524115956</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191305496156077</v>
+        <v>1.154544610922106</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6068727694984892</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>-4.190044061089578</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.220749151940488</v>
+        <v>1.183988266706517</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6068727694984892</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>-4.235350880488558</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.194402199625421</v>
+        <v>1.157641314391451</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5660626064892584</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>-4.264383985190859</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.183340830777603</v>
+        <v>1.146579945543632</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5660626064892584</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>-4.171573503739999</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149737715249312</v>
+        <v>1.112976830015342</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6588730879401178</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>-4.215962973069427</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133855403442142</v>
+        <v>1.097094518208171</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6144836186106901</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>-4.33250457817477</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.082314469911728</v>
+        <v>1.045553584677757</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4979420135053474</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>-4.220127576992097</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.132756566215464</v>
+        <v>1.095995680981494</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4979420135053474</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>-4.247907974893449</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.133141608823462</v>
+        <v>1.096380723589492</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4701616156039943</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>-4.366288647623588</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9241450597320604</v>
+        <v>0.8873841744980897</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4029437634530181</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>-4.474902726066919</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000849089073933</v>
+        <v>0.9640882038399627</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4029437634530181</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>-4.439493687818776</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.029525730475514</v>
+        <v>0.992764845241543</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4029437634530181</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>-4.401110025260625</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.042298636841143</v>
+        <v>1.005537751607172</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4413274260111693</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>-4.223993695225459</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109874197700511</v>
+        <v>1.07311331246654</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4413274260111693</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>-4.269085940059004</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092520691529006</v>
+        <v>1.055759806295035</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3794313828417795</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>-4.089710518820237</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158057835330927</v>
+        <v>1.121296950096957</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5362081410124981</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>-4.134724732340842</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120859605254275</v>
+        <v>1.084098720020304</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5058592456978935</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>-4.401729242613277</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019749363484246</v>
+        <v>0.9829884782502758</v>
       </c>
       <c r="F1959" t="n">
         <v>0.311496207654945</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>-4.50292702405045</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9784741728058788</v>
+        <v>0.9417132875719081</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2430873941096258</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>-4.496416057436138</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9786785210059206</v>
+        <v>0.9419176357719499</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2430873941096258</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>-4.47737792972884</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9828184912970845</v>
+        <v>0.9460576060631138</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1849037827784312</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>-4.508504560879459</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.089662240471027</v>
+        <v>1.052901355237057</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1849037827784312</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>-4.522371322213377</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084948864923594</v>
+        <v>1.048187979689623</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1470458660446083</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>-4.477567150673447</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.108879063936492</v>
+        <v>1.072118178702521</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1470458660446083</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>-4.329824180438444</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.065926473307692</v>
+        <v>1.029165588073722</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3148532232794914</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>-4.413645401713143</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035191606329294</v>
+        <v>0.9984307210953232</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3148532232794914</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>-4.407492695660358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038315037142066</v>
+        <v>1.001554151908095</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3210059293322757</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>-4.42430199381086</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.030671794621975</v>
+        <v>0.9939109093880047</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3041966311817741</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>-4.362003995034738</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.121926547929245</v>
+        <v>1.085165662695275</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3041966311817741</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>-4.16021379736958</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.004934628709436</v>
+        <v>0.9681737434754649</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5022148233509285</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>-4.211100510055775</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.054870175957133</v>
+        <v>1.018109290723162</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4513281106647339</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>-4.308841054680749</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.030401694223187</v>
+        <v>0.9936408089892161</v>
       </c>
       <c r="F1973" t="n">
         <v>0.4354388325317538</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>-4.369050352686034</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.004853955845745</v>
+        <v>0.9680930706117739</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3752295345264692</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>-4.292628306254107</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.033914392458444</v>
+        <v>0.997153507224473</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>-4.248255174615538</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.051526512549307</v>
+        <v>1.014765627315337</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>-4.270735525474423</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.036928166344344</v>
+        <v>1.000167281110373</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4196026661650378</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190328</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>-4.223079794913367</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.062372215596571</v>
+        <v>1.0256113303626</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4672583967260935</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056962</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>-4.122561636414613</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.107471852370798</v>
+        <v>1.070710967136827</v>
       </c>
       <c r="F1979" t="n">
         <v>0.567776555224848</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>-4.183228226817002</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069959888685714</v>
+        <v>1.033199003451743</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4860782385063144</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>-4.138389825208604</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091992951939702</v>
+        <v>1.055232066705731</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4906216714511838</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>-4.157888281450612</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088354509073977</v>
+        <v>1.051593623840006</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4425370301712795</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>-4.113685444364712</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111915246436174</v>
+        <v>1.075154361202203</v>
       </c>
       <c r="F1983" t="n">
         <v>0.48673986725718</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>-4.150664472028154</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095533635840044</v>
+        <v>1.058772750606074</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5237137690485105</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>-3.992373054488882</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210097968038793</v>
+        <v>1.173337082804822</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5237137690485105</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>-3.784731050854406</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291595474086837</v>
+        <v>1.254834588852866</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7313557726829867</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>-3.733698958131878</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306956539414118</v>
+        <v>1.270195654180147</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7823878654055146</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>-3.668474777004672</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350233615957705</v>
+        <v>1.313472730723734</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8476120465327203</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>-3.631047756933538</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361165396285439</v>
+        <v>1.324404511051468</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8528635845619019</v>
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.623940245222266</v>
+        <v>-3.651159412968247</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.328504308067218</v>
+        <v>1.317616640968825</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8723798291916631</v>
+        <v>0.8638909295593211</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.301864727984869</v>
+        <v>3.296771388205464</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.570195430795061</v>
+        <v>-3.597414598541042</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.51056000485931</v>
+        <v>1.499672337760918</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8824431386321251</v>
+        <v>0.8739542389997831</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.468460484670358</v>
+        <v>3.463367144890952</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.495413169770048</v>
+        <v>-3.522632337516029</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.660585818487132</v>
+        <v>1.64969815138874</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9572253996571377</v>
+        <v>0.9487365000247957</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.633442750503182</v>
+        <v>3.628349410723777</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.46932908550624</v>
+        <v>-3.496548253252221</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.662727428206515</v>
+        <v>1.651839761108122</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9572253996571377</v>
+        <v>0.9487365000247957</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.625150726517041</v>
+        <v>3.620057386737636</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.391197904657294</v>
+        <v>-3.418417072403274</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.692173096129873</v>
+        <v>1.681285429031481</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.031402210540822</v>
+        <v>1.02291331090848</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.667850008631031</v>
+        <v>3.662756668851626</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.382305443264011</v>
+        <v>-3.409524611009991</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.713284486413977</v>
+        <v>1.702396819315585</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.031402210540822</v>
+        <v>1.02291331090848</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.685404414357823</v>
+        <v>3.680311074578417</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.550781560233889</v>
+        <v>-3.578000727979869</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.63774908703061</v>
+        <v>1.626861419932218</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.003454374824241</v>
+        <v>0.9949654751918995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.660490760332458</v>
+        <v>3.655397420553053</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.852982031372306</v>
+        <v>-2.880201199118286</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.898138595763105</v>
+        <v>1.887250928664713</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9331063154538308</v>
+        <v>0.9246174158214888</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.599551621898073</v>
+        <v>3.594458282118668</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.830260927689153</v>
+        <v>-2.857480095435133</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.897891059733271</v>
+        <v>1.887003392634879</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9331063154538308</v>
+        <v>0.9246174158214888</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.590215644394978</v>
+        <v>3.585122304615573</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.959462740983196</v>
+        <v>-2.986681908729176</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.005116460266823</v>
+        <v>1.994228793168431</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8039045021597886</v>
+        <v>0.7954156025274466</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.671600682269722</v>
+        <v>3.666507342490317</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.114243747761451</v>
+        <v>-3.141462915507431</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.980281880049167</v>
+        <v>1.969394212950775</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7705368281053124</v>
+        <v>0.7620479284729704</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.688657900330683</v>
+        <v>3.683564560551277</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.107189057546277</v>
+        <v>-3.134408225292258</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.979779112124782</v>
+        <v>1.96889144502639</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7775915183204862</v>
+        <v>0.7691026186881442</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.689566070449332</v>
+        <v>3.684472730669927</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.08023783321979</v>
+        <v>-3.10745700096577</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.000565755500118</v>
+        <v>1.989678088401726</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.708500431710705</v>
+        <v>3.7034070919313</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.216190841276106</v>
+        <v>-3.243410009022086</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.130287684422552</v>
+        <v>2.11940001732416</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.892603563855665</v>
+        <v>3.88751022407626</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.238598959080978</v>
+        <v>-3.265818126826958</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.113441132203596</v>
+        <v>2.102553465105204</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.884720258758658</v>
+        <v>3.879626918979253</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.386604726560377</v>
+        <v>-3.413823894306358</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.056292824761474</v>
+        <v>2.045405157663081</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7057448554846639</v>
+        <v>0.6972559558523219</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.834738052990171</v>
+        <v>3.829644713210765</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.396045652448907</v>
+        <v>-3.423264820194888</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.108770172127909</v>
+        <v>2.097882505029517</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8281719730280553</v>
+        <v>0.8196830733957133</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.964448041238052</v>
+        <v>3.959354701458647</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.448319259784549</v>
+        <v>-3.475538427530529</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.090751823738954</v>
+        <v>2.079864156640561</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7758983656924141</v>
+        <v>0.7674094660600721</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.935974971381969</v>
+        <v>3.930881631602563</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.524649237385455</v>
+        <v>-3.551868405131435</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.058331645592366</v>
+        <v>2.047443978493974</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7758983656924141</v>
+        <v>0.7674094660600721</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.934086784275744</v>
+        <v>3.928993444496339</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.726902957709808</v>
+        <v>-3.754122125455788</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.972250387065487</v>
+        <v>1.961362719967095</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5736446453680606</v>
+        <v>0.5651557457357186</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.807554781683994</v>
+        <v>3.802461441904589</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.888471383237063</v>
+        <v>-3.915690550983043</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.906057027064737</v>
+        <v>1.895169359966345</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.729919037615419</v>
+        <v>3.724825697836013</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.020772675334617</v>
+        <v>-4.047991843080597</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.866209917091634</v>
+        <v>1.855322249993242</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.742992444481337</v>
+        <v>3.737899104701932</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.022334318149476</v>
+        <v>-4.049553485895457</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.865585259965691</v>
+        <v>1.854697592867298</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.742992444481337</v>
+        <v>3.737899104701932</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.050235105258949</v>
+        <v>-4.077454273004929</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.852948986248903</v>
+        <v>1.842061319150512</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4122647974272464</v>
+        <v>0.4037758977949044</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.720758331122579</v>
+        <v>3.715664991343173</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.172761207961843</v>
+        <v>-4.199980375707823</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.800702989144945</v>
+        <v>1.789815322046553</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2897386947243525</v>
+        <v>0.2812497950920105</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.644007113478041</v>
+        <v>3.638913773698636</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.403275704147432</v>
+        <v>-4.430494871893412</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.775203150261213</v>
+        <v>1.764315483162821</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05922419853876382</v>
+        <v>0.05073529890642181</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.572404375357191</v>
+        <v>3.567311035577786</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.659996522142256</v>
+        <v>-4.687215689888236</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.81282654206513</v>
+        <v>1.801938874966738</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.64766734987275</v>
+        <v>3.642574010093345</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.813982939918397</v>
+        <v>-4.841202107664376</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.820212244100314</v>
+        <v>1.809324577001922</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.716647619018389</v>
+        <v>3.711554279238984</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.763461036090731</v>
+        <v>-4.79068020383671</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.826472207751501</v>
+        <v>1.815584540653109</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.70269882113851</v>
+        <v>3.697605481359105</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.015936190098455</v>
+        <v>-5.043155357844435</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.737352635203825</v>
+        <v>1.726464968105434</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.714569310193924</v>
+        <v>3.709475970414519</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.308831946577867</v>
+        <v>-5.336051114323847</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.621404867131004</v>
+        <v>1.610517200032612</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.715779844712868</v>
+        <v>3.710686504933463</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.466376018307309</v>
+        <v>-5.493595186053288</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.562508980666549</v>
+        <v>1.551621313568157</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1160921807453255</v>
+        <v>-0.1245810803776675</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.679760503856025</v>
+        <v>3.674667164076619</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.744340413890582</v>
+        <v>-5.771559581636562</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.446401075169429</v>
+        <v>1.435513408071037</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2057119150308098</v>
+        <v>-0.2142008146631518</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.621066516020924</v>
+        <v>3.615973176241519</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.861308106529473</v>
+        <v>-5.888527274275453</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.561818054812917</v>
+        <v>1.550930387714525</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2057119150308098</v>
+        <v>-0.2142008146631518</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.783270572719968</v>
+        <v>3.778177232940562</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.946026048750427</v>
+        <v>-5.973245216496406</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.522777515888349</v>
+        <v>1.511889848789958</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2908279439588561</v>
+        <v>-0.2993168435911981</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.727047593326954</v>
+        <v>3.721954253547549</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.02796086701931</v>
+        <v>-6.055180034765289</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.500233006149287</v>
+        <v>1.489345339050896</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3007626895459363</v>
+        <v>-0.3092515891782783</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.731316163543197</v>
+        <v>3.726222823763792</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.129936989267717</v>
+        <v>-6.157156157013697</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.468368195705827</v>
+        <v>1.457480528607435</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4027388117943439</v>
+        <v>-0.4112277114266859</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.679056128650055</v>
+        <v>3.67396278887065</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.019930705790496</v>
+        <v>-6.047149873536475</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.504523596340891</v>
+        <v>1.493635929242499</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3795342398770687</v>
+        <v>-0.3880231395094107</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.685131759044595</v>
+        <v>3.68003841926519</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.876871130049571</v>
+        <v>-5.90409029779555</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.565997437359235</v>
+        <v>1.555109770260843</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3715208132870894</v>
+        <v>-0.3800097129194314</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.694189825720557</v>
+        <v>3.689096485941152</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.575424404577733</v>
+        <v>-5.602643572323712</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.693837010430506</v>
+        <v>1.682949343332115</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.882318743886196</v>
+        <v>3.87722540410679</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.600014648812917</v>
+        <v>-5.627233816558896</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.684972090489143</v>
+        <v>1.674084423390751</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.883289921638906</v>
+        <v>3.878196581859501</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.548976272806397</v>
+        <v>-5.576195440552376</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.706230345271507</v>
+        <v>1.695342678173115</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.884132826018662</v>
+        <v>3.879039486239256</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.507836977939766</v>
+        <v>-5.535056145685745</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.741724162092304</v>
+        <v>1.730836494993913</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.02893479294862134</v>
+        <v>-0.03742369258096334</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.927854501812785</v>
+        <v>3.92276116203338</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.397230837860164</v>
+        <v>-5.424450005606143</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.602150614248079</v>
+        <v>1.591262947149688</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08167134713098068</v>
+        <v>0.07318244749863867</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.810402181984481</v>
+        <v>3.805308842205076</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.527811572391006</v>
+        <v>-5.555030740136986</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.553420364509706</v>
+        <v>1.542532697411314</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.735555785339939</v>
+        <v>3.730462445560534</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.363315238200045</v>
+        <v>-5.390534405946024</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.603645717262173</v>
+        <v>1.592758050163782</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.719982604416022</v>
+        <v>3.714889264636617</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.821044820462765</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.238834757476093</v>
+        <v>-5.266053925222073</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.652625619988184</v>
+        <v>1.641737952889792</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.719170314852452</v>
+        <v>3.714076975073046</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.249219952365983</v>
+        <v>-5.276439120111962</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.658340321157301</v>
+        <v>1.647452654058909</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05929458228975115</v>
+        <v>-0.06778348192209316</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.72280797704359</v>
+        <v>3.717714637264185</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120423</v>
+        <v>3.834429654120421</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.267808111088208</v>
+        <v>-5.295027278834187</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.721742063444835</v>
+        <v>1.710854396346444</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.07788274101197651</v>
+        <v>-0.08637164064431851</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.782492087586681</v>
+        <v>3.777398747807275</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881693</v>
+        <v>3.855134695881691</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.126091363273803</v>
+        <v>-5.153310531019782</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.775297773388896</v>
+        <v>1.764410106290504</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.07788274101197651</v>
+        <v>-0.08637164064431851</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.779361098404979</v>
+        <v>3.774267758625574</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.835263801896224</v>
+        <v>3.764667908682236</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.975369436950295</v>
+        <v>-5.052487397329354</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.84011743885769</v>
+        <v>1.809270254706067</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.08046947582201458</v>
+        <v>-0.07390742515996468</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.782339952458347</v>
+        <v>3.786277182855577</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.5%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>454.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.8%</t>
+          <t>-669.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.3%</t>
+          <t>-153.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-195.3%</t>
+          <t>-196.2%</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.618984306435109</v>
+        <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.131511723638655</v>
+        <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3614328303452544</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.498811223070611</v>
+        <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.180726801424756</v>
+        <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4816059137097533</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.354139077970873</v>
+        <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.248683762026091</v>
+        <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6262780588094907</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.414013905328566</v>
+        <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.21077132248444</v>
+        <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5664032314517986</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.294193674417729</v>
+        <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.273988584082983</v>
+        <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5664032314517986</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.296663380879535</v>
+        <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.180644900820702</v>
+        <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5639335249899924</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.365033567203545</v>
+        <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.0725586877764</v>
+        <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5732092240262073</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.378821620050592</v>
+        <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.057480175269472</v>
+        <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5732092240262073</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.434341695943181</v>
+        <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.172302981604639</v>
+        <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5732092240262073</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.258867436150712</v>
+        <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.247059917513414</v>
+        <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5732092240262073</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.369803688791961</v>
+        <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.178427445218122</v>
+        <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5732092240262073</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.336140143319679</v>
+        <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.120431176808484</v>
+        <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6068727694984892</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.276287524115956</v>
+        <v>-4.184385311031029</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.154544610922106</v>
+        <v>1.191305496156077</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6068727694984892</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.190044061089578</v>
+        <v>-4.098141848004651</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.183988266706517</v>
+        <v>1.220749151940488</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6068727694984892</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.235350880488558</v>
+        <v>-4.143448667403631</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.157641314391451</v>
+        <v>1.194402199625421</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5660626064892584</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.264383985190859</v>
+        <v>-4.172481772105932</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.146579945543632</v>
+        <v>1.183340830777603</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5660626064892584</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.171573503739999</v>
+        <v>-4.079671290655073</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.112976830015342</v>
+        <v>1.149737715249312</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6588730879401178</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.215962973069427</v>
+        <v>-4.1240607599845</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.097094518208171</v>
+        <v>1.133855403442142</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6144836186106901</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.33250457817477</v>
+        <v>-4.240602365089843</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.045553584677757</v>
+        <v>1.082314469911728</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4979420135053474</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.220127576992097</v>
+        <v>-4.12822536390717</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.095995680981494</v>
+        <v>1.132756566215464</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4979420135053474</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.247907974893449</v>
+        <v>-4.156005761808522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.096380723589492</v>
+        <v>1.133141608823462</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4701616156039943</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.366288647623588</v>
+        <v>-4.274386434538661</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8873841744980897</v>
+        <v>0.9241450597320604</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4029437634530181</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.474902726066919</v>
+        <v>-4.383000512981992</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9640882038399627</v>
+        <v>1.000849089073933</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4029437634530181</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.439493687818776</v>
+        <v>-4.347591474733849</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.992764845241543</v>
+        <v>1.029525730475514</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4029437634530181</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.401110025260625</v>
+        <v>-4.309207812175698</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.005537751607172</v>
+        <v>1.042298636841143</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4413274260111693</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.223993695225459</v>
+        <v>-4.132091482140532</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.07311331246654</v>
+        <v>1.109874197700511</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4413274260111693</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.269085940059004</v>
+        <v>-4.177183726974078</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.055759806295035</v>
+        <v>1.092520691529006</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3794313828417795</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.089710518820237</v>
+        <v>-3.99780830573531</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.121296950096957</v>
+        <v>1.158057835330927</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5362081410124981</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.134724732340842</v>
+        <v>-4.042822519255916</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.084098720020304</v>
+        <v>1.120859605254275</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5058592456978935</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.401729242613277</v>
+        <v>-4.309827029528351</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9829884782502758</v>
+        <v>1.019749363484246</v>
       </c>
       <c r="F1959" t="n">
         <v>0.311496207654945</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.50292702405045</v>
+        <v>-4.411024810965523</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9417132875719081</v>
+        <v>0.9784741728058788</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2430873941096258</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.496416057436138</v>
+        <v>-4.404513844351211</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9419176357719499</v>
+        <v>0.9786785210059206</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2430873941096258</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.47737792972884</v>
+        <v>-4.385475716643914</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9460576060631138</v>
+        <v>0.9828184912970845</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1849037827784312</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.508504560879459</v>
+        <v>-4.416602347794532</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.052901355237057</v>
+        <v>1.089662240471027</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1849037827784312</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.522371322213377</v>
+        <v>-4.43046910912845</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.048187979689623</v>
+        <v>1.084948864923594</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1470458660446083</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.477567150673447</v>
+        <v>-4.38566493758852</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.072118178702521</v>
+        <v>1.108879063936492</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1470458660446083</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.329824180438444</v>
+        <v>-4.237921967353517</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.029165588073722</v>
+        <v>1.065926473307692</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3148532232794914</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.413645401713143</v>
+        <v>-4.321743188628216</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9984307210953232</v>
+        <v>1.035191606329294</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3148532232794914</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.407492695660358</v>
+        <v>-4.315590482575431</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.001554151908095</v>
+        <v>1.038315037142066</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3210059293322757</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.42430199381086</v>
+        <v>-4.332399780725933</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9939109093880047</v>
+        <v>1.030671794621975</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3041966311817741</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.362003995034738</v>
+        <v>-4.270101781949811</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.085165662695275</v>
+        <v>1.121926547929245</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3041966311817741</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.16021379736958</v>
+        <v>-4.068311584284653</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9681737434754649</v>
+        <v>1.004934628709436</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5022148233509285</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.211100510055775</v>
+        <v>-4.119198296970848</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.018109290723162</v>
+        <v>1.054870175957133</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4513281106647339</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.308841054680749</v>
+        <v>-4.216938841595822</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9936408089892161</v>
+        <v>1.030401694223187</v>
       </c>
       <c r="F1973" t="n">
         <v>0.4354388325317538</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.369050352686034</v>
+        <v>-4.277148139601107</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9680930706117739</v>
+        <v>1.004853955845745</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3752295345264692</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.292628306254107</v>
+        <v>-4.314059064421671</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.997153507224473</v>
+        <v>0.9885812039574475</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.248255174615538</v>
+        <v>-4.269685932783102</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.014765627315337</v>
+        <v>1.006193324048311</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.270735525474423</v>
+        <v>-4.292166283641987</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.000167281110373</v>
+        <v>0.9915949778433477</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4196026661650378</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.223079794913367</v>
+        <v>-4.244510553080931</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.0256113303626</v>
+        <v>1.017039027095575</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4672583967260935</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.122561636414613</v>
+        <v>-4.143992394582177</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.070710967136827</v>
+        <v>1.062138663869801</v>
       </c>
       <c r="F1979" t="n">
         <v>0.567776555224848</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.183228226817002</v>
+        <v>-4.204658984984565</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.033199003451743</v>
+        <v>1.024626700184718</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4860782385063144</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.138389825208604</v>
+        <v>-4.159820583376167</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.055232066705731</v>
+        <v>1.046659763438706</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4906216714511838</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.157888281450612</v>
+        <v>-4.179319039618175</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.051593623840006</v>
+        <v>1.043021320572981</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4425370301712795</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.113685444364712</v>
+        <v>-4.135116202532275</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.075154361202203</v>
+        <v>1.066582057935178</v>
       </c>
       <c r="F1983" t="n">
         <v>0.48673986725718</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.150664472028154</v>
+        <v>-4.172095230195717</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.058772750606074</v>
+        <v>1.050200447339049</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5237137690485105</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.992373054488882</v>
+        <v>-4.013803812656445</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.173337082804822</v>
+        <v>1.164764779537797</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5237137690485105</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.784731050854406</v>
+        <v>-3.806161809021969</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.254834588852866</v>
+        <v>1.246262285585841</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7313557726829867</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.733698958131878</v>
+        <v>-3.755129716299441</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.270195654180147</v>
+        <v>1.261623350913122</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7823878654055146</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.668474777004672</v>
+        <v>-3.689905535172236</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.313472730723734</v>
+        <v>1.304900427456709</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8476120465327203</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.631047756933538</v>
+        <v>-3.652478515101102</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.324404511051468</v>
+        <v>1.315832207784443</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8528635845619019</v>
@@ -47321,10 +47321,10 @@
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.651159412968247</v>
+        <v>-3.67259017113581</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.317616640968825</v>
+        <v>1.3090443377018</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8638909295593211</v>
@@ -47344,10 +47344,10 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.597414598541042</v>
+        <v>-3.618845356708606</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.499672337760918</v>
+        <v>1.491100034493893</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8739542389997831</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.522632337516029</v>
+        <v>-3.544063095683593</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.64969815138874</v>
+        <v>1.641125848121715</v>
       </c>
       <c r="F1992" t="n">
         <v>0.9487365000247957</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.496548253252221</v>
+        <v>-3.517979011419785</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.651839761108122</v>
+        <v>1.643267457841097</v>
       </c>
       <c r="F1993" t="n">
         <v>0.9487365000247957</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.418417072403274</v>
+        <v>-3.439847830570838</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.681285429031481</v>
+        <v>1.672713125764455</v>
       </c>
       <c r="F1994" t="n">
         <v>1.02291331090848</v>
@@ -47436,10 +47436,10 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.409524611009991</v>
+        <v>-3.430955369177555</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.702396819315585</v>
+        <v>1.69382451604856</v>
       </c>
       <c r="F1995" t="n">
         <v>1.02291331090848</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.578000727979869</v>
+        <v>-3.599431486147433</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.626861419932218</v>
+        <v>1.618289116665192</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9949654751918995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.880201199118286</v>
+        <v>-2.90163195728585</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.887250928664713</v>
+        <v>1.878678625397688</v>
       </c>
       <c r="F1997" t="n">
         <v>0.9246174158214888</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.857480095435133</v>
+        <v>-2.878910853602697</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.887003392634879</v>
+        <v>1.878431089367853</v>
       </c>
       <c r="F1998" t="n">
         <v>0.9246174158214888</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.986681908729176</v>
+        <v>-3.00811266689674</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.994228793168431</v>
+        <v>1.985656489901405</v>
       </c>
       <c r="F1999" t="n">
         <v>0.7954156025274466</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.141462915507431</v>
+        <v>-3.162893673674995</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.969394212950775</v>
+        <v>1.96082190968375</v>
       </c>
       <c r="F2000" t="n">
         <v>0.7620479284729704</v>
@@ -47574,10 +47574,10 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.134408225292258</v>
+        <v>-3.155838983459822</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96889144502639</v>
+        <v>1.960319141759364</v>
       </c>
       <c r="F2001" t="n">
         <v>0.7691026186881442</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.10745700096577</v>
+        <v>-3.128887759133334</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.989678088401726</v>
+        <v>1.981105785134701</v>
       </c>
       <c r="F2002" t="n">
         <v>0.7839829647158634</v>
@@ -47620,10 +47620,10 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.243410009022086</v>
+        <v>-3.26484076718965</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.11940001732416</v>
+        <v>2.110827714057134</v>
       </c>
       <c r="F2003" t="n">
         <v>0.7839829647158634</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.265818126826958</v>
+        <v>-3.287248884994522</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.102553465105204</v>
+        <v>2.093981161838179</v>
       </c>
       <c r="F2004" t="n">
         <v>0.7839829647158634</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.413823894306358</v>
+        <v>-3.435254652473922</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.045405157663081</v>
+        <v>2.036832854396056</v>
       </c>
       <c r="F2005" t="n">
         <v>0.6972559558523219</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.423264820194888</v>
+        <v>-3.444695578362452</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.097882505029517</v>
+        <v>2.089310201762491</v>
       </c>
       <c r="F2006" t="n">
         <v>0.8196830733957133</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.475538427530529</v>
+        <v>-3.496969185698093</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.079864156640561</v>
+        <v>2.071291853373536</v>
       </c>
       <c r="F2007" t="n">
         <v>0.7674094660600721</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347699</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.551868405131435</v>
+        <v>-3.573299163298999</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.047443978493974</v>
+        <v>2.038871675226948</v>
       </c>
       <c r="F2008" t="n">
         <v>0.7674094660600721</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.754122125455788</v>
+        <v>-3.775552883623352</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.961362719967095</v>
+        <v>1.952790416700069</v>
       </c>
       <c r="F2009" t="n">
         <v>0.5651557457357186</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.915690550983043</v>
+        <v>-3.937121309150607</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.895169359966345</v>
+        <v>1.88659705669932</v>
       </c>
       <c r="F2010" t="n">
         <v>0.4383728219378392</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.047991843080597</v>
+        <v>-4.069422601248161</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.855322249993242</v>
+        <v>1.846749946726217</v>
       </c>
       <c r="F2011" t="n">
         <v>0.4383728219378392</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763529</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.049553485895457</v>
+        <v>-4.070984244063021</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.854697592867298</v>
+        <v>1.846125289600273</v>
       </c>
       <c r="F2012" t="n">
         <v>0.4383728219378392</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392112</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.077454273004929</v>
+        <v>-4.098885031172493</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.842061319150512</v>
+        <v>1.833489015883486</v>
       </c>
       <c r="F2013" t="n">
         <v>0.4037758977949044</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172523</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.199980375707823</v>
+        <v>-4.221411133875387</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.789815322046553</v>
+        <v>1.781243018779527</v>
       </c>
       <c r="F2014" t="n">
         <v>0.2812497950920105</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971075</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.430494871893412</v>
+        <v>-4.451925630060976</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.764315483162821</v>
+        <v>1.755743179895795</v>
       </c>
       <c r="F2015" t="n">
         <v>0.05073529890642181</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199802</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.687215689888236</v>
+        <v>-4.7086464480558</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.801938874966738</v>
+        <v>1.793366571699712</v>
       </c>
       <c r="F2016" t="n">
         <v>-0.05767927523739302</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622233</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.841202107664376</v>
+        <v>-4.862632865831941</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.809324577001922</v>
+        <v>1.800752273734896</v>
       </c>
       <c r="F2017" t="n">
         <v>-0.05767927523739302</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.79068020383671</v>
+        <v>-4.812110962004275</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.815584540653109</v>
+        <v>1.807012237386083</v>
       </c>
       <c r="F2018" t="n">
         <v>-0.05767927523739302</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.65634689399489</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.043155357844435</v>
+        <v>-5.064586116011999</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.726464968105434</v>
+        <v>1.717892664838407</v>
       </c>
       <c r="F2019" t="n">
         <v>-0.05767927523739302</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358294</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.336051114323847</v>
+        <v>-5.357481872491412</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.610517200032612</v>
+        <v>1.601944896765586</v>
       </c>
       <c r="F2020" t="n">
         <v>-0.05767927523739302</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.493595186053288</v>
+        <v>-5.515025944220853</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.551621313568157</v>
+        <v>1.543049010301131</v>
       </c>
       <c r="F2021" t="n">
         <v>-0.1245810803776675</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.771559581636562</v>
+        <v>-5.792990339804127</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.435513408071037</v>
+        <v>1.426941104804011</v>
       </c>
       <c r="F2022" t="n">
         <v>-0.2142008146631518</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215466</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.888527274275453</v>
+        <v>-5.909958032443018</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.550930387714525</v>
+        <v>1.542358084447499</v>
       </c>
       <c r="F2023" t="n">
         <v>-0.2142008146631518</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456688</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.973245216496406</v>
+        <v>-5.994675974663971</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.511889848789958</v>
+        <v>1.503317545522932</v>
       </c>
       <c r="F2024" t="n">
         <v>-0.2993168435911981</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.055180034765289</v>
+        <v>-6.076610792932854</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.489345339050896</v>
+        <v>1.48077303578387</v>
       </c>
       <c r="F2025" t="n">
         <v>-0.3092515891782783</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717826</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.157156157013697</v>
+        <v>-6.178586915181262</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.457480528607435</v>
+        <v>1.448908225340409</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.4112277114266859</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616944</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.047149873536475</v>
+        <v>-6.06858063170404</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.493635929242499</v>
+        <v>1.485063625975473</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.3880231395094107</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.90409029779555</v>
+        <v>-5.925521055963115</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.555109770260843</v>
+        <v>1.546537466993818</v>
       </c>
       <c r="F2028" t="n">
         <v>-0.3800097129194314</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436924</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.602643572323712</v>
+        <v>-5.624074330491277</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.682949343332115</v>
+        <v>1.674377040065088</v>
       </c>
       <c r="F2029" t="n">
         <v>-0.07856298744759416</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064762</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.627233816558896</v>
+        <v>-5.648664574726461</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.674084423390751</v>
+        <v>1.665512120123725</v>
       </c>
       <c r="F2030" t="n">
         <v>-0.07856298744759416</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859295</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.576195440552376</v>
+        <v>-5.597626198719941</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.695342678173115</v>
+        <v>1.686770374906089</v>
       </c>
       <c r="F2031" t="n">
         <v>-0.07856298744759416</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354679</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.535056145685745</v>
+        <v>-5.55648690385331</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.730836494993913</v>
+        <v>1.722264191726886</v>
       </c>
       <c r="F2032" t="n">
         <v>-0.03742369258096334</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085615</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.424450005606143</v>
+        <v>-5.445880763773708</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.591262947149688</v>
+        <v>1.582690643882662</v>
       </c>
       <c r="F2033" t="n">
         <v>0.07318244749863867</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462776</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.555030740136986</v>
+        <v>-5.576461498304551</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.542532697411314</v>
+        <v>1.533960394144289</v>
       </c>
       <c r="F2034" t="n">
         <v>-0.05739828703220384</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.775043021218592</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.390534405946024</v>
+        <v>-5.411965164113589</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.592758050163782</v>
+        <v>1.584185746896756</v>
       </c>
       <c r="F2035" t="n">
         <v>-0.05739828703220384</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462765</v>
+        <v>3.821044820462763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.266053925222073</v>
+        <v>-5.287484683389637</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.641737952889792</v>
+        <v>1.633165649622766</v>
       </c>
       <c r="F2036" t="n">
         <v>-0.05739828703220384</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.832321184533045</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.276439120111962</v>
+        <v>-5.297869878279527</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.647452654058909</v>
+        <v>1.638880350791883</v>
       </c>
       <c r="F2037" t="n">
         <v>-0.06778348192209316</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120421</v>
+        <v>3.834429654120417</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.295027278834187</v>
+        <v>-5.316458037001752</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.710854396346444</v>
+        <v>1.702282093079418</v>
       </c>
       <c r="F2038" t="n">
         <v>-0.08637164064431851</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881691</v>
+        <v>3.85513469588169</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.153310531019782</v>
+        <v>-5.174741289187347</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.764410106290504</v>
+        <v>1.755837803023478</v>
       </c>
       <c r="F2039" t="n">
         <v>-0.08637164064431851</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.764667908682236</v>
+        <v>3.792071428858693</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.052487397329354</v>
+        <v>-5.073918155496919</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.809270254706067</v>
+        <v>1.800697951439041</v>
       </c>
       <c r="F2040" t="n">
         <v>-0.07390742515996468</v>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -773,11 +773,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>126.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.0%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-669.0%</t>
+          <t>-664.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-153.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-196.2%</t>
+          <t>-194.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-91.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.4%</t>
+          <t>-230.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-63.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2040"/>
+  <dimension ref="A1:G2041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
@@ -46976,10 +46976,10 @@
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.314059064421671</v>
+        <v>-4.20072609316918</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9885812039574475</v>
+        <v>1.033914392458444</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46999,10 +46999,10 @@
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.269685932783102</v>
+        <v>-4.156352961530612</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.006193324048311</v>
+        <v>1.051526512549307</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47022,10 +47022,10 @@
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.292166283641987</v>
+        <v>-4.178833312389497</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9915949778433477</v>
+        <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4196026661650378</v>
@@ -47045,10 +47045,10 @@
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.244510553080931</v>
+        <v>-4.131177581828441</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.017039027095575</v>
+        <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4672583967260935</v>
@@ -47068,10 +47068,10 @@
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.143992394582177</v>
+        <v>-4.030659423329686</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.062138663869801</v>
+        <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
         <v>0.567776555224848</v>
@@ -47091,10 +47091,10 @@
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.204658984984565</v>
+        <v>-4.091326013732075</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.024626700184718</v>
+        <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
         <v>0.4860782385063144</v>
@@ -47114,10 +47114,10 @@
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.159820583376167</v>
+        <v>-4.046487612123677</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.046659763438706</v>
+        <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
         <v>0.4906216714511838</v>
@@ -47137,10 +47137,10 @@
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.179319039618175</v>
+        <v>-4.065986068365685</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.043021320572981</v>
+        <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4425370301712795</v>
@@ -47160,10 +47160,10 @@
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.135116202532275</v>
+        <v>-4.021783231279785</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.066582057935178</v>
+        <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
         <v>0.48673986725718</v>
@@ -47183,10 +47183,10 @@
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.172095230195717</v>
+        <v>-4.058762258943228</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.050200447339049</v>
+        <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5237137690485105</v>
@@ -47206,10 +47206,10 @@
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.013803812656445</v>
+        <v>-3.900470841403955</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.164764779537797</v>
+        <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5237137690485105</v>
@@ -47229,10 +47229,10 @@
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.806161809021969</v>
+        <v>-3.692828837769479</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.246262285585841</v>
+        <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7313557726829867</v>
@@ -47252,10 +47252,10 @@
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.755129716299441</v>
+        <v>-3.641796745046951</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.261623350913122</v>
+        <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7823878654055146</v>
@@ -47275,10 +47275,10 @@
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.689905535172236</v>
+        <v>-3.576572563919745</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.304900427456709</v>
+        <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8476120465327203</v>
@@ -47298,10 +47298,10 @@
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.652478515101102</v>
+        <v>-3.539145543848611</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.315832207784443</v>
+        <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8528635845619019</v>
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.67259017113581</v>
+        <v>-3.623940245222266</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.3090443377018</v>
+        <v>1.328504308067218</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8638909295593211</v>
+        <v>0.8723798291916631</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.296771388205464</v>
+        <v>3.301864727984869</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.618845356708606</v>
+        <v>-3.570195430795061</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491100034493893</v>
+        <v>1.51056000485931</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8739542389997831</v>
+        <v>0.8824431386321251</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.463367144890952</v>
+        <v>3.468460484670358</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.544063095683593</v>
+        <v>-3.495413169770048</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.641125848121715</v>
+        <v>1.660585818487132</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9572253996571377</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.628349410723777</v>
+        <v>3.633442750503182</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.517979011419785</v>
+        <v>-3.46932908550624</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.643267457841097</v>
+        <v>1.662727428206515</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9572253996571377</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.620057386737636</v>
+        <v>3.625150726517041</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.439847830570838</v>
+        <v>-3.391197904657294</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.672713125764455</v>
+        <v>1.692173096129873</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.02291331090848</v>
+        <v>1.031402210540822</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.662756668851626</v>
+        <v>3.667850008631031</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.430955369177555</v>
+        <v>-3.382305443264011</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.69382451604856</v>
+        <v>1.713284486413977</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.02291331090848</v>
+        <v>1.031402210540822</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.680311074578417</v>
+        <v>3.685404414357823</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.599431486147433</v>
+        <v>-3.550781560233889</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618289116665192</v>
+        <v>1.63774908703061</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9949654751918995</v>
+        <v>1.003454374824241</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655397420553053</v>
+        <v>3.660490760332458</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.90163195728585</v>
+        <v>-2.852982031372306</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.878678625397688</v>
+        <v>1.898138595763105</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.9331063154538308</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.594458282118668</v>
+        <v>3.599551621898073</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.878910853602697</v>
+        <v>-2.830260927689153</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.878431089367853</v>
+        <v>1.897891059733271</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.9331063154538308</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.585122304615573</v>
+        <v>3.590215644394978</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.00811266689674</v>
+        <v>-2.959462740983196</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.985656489901405</v>
+        <v>2.005116460266823</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7954156025274466</v>
+        <v>0.8039045021597886</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.666507342490317</v>
+        <v>3.671600682269722</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.162893673674995</v>
+        <v>-3.114243747761451</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.96082190968375</v>
+        <v>1.980281880049167</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7620479284729704</v>
+        <v>0.7705368281053124</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.683564560551277</v>
+        <v>3.688657900330683</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.155838983459822</v>
+        <v>-3.107189057546277</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.960319141759364</v>
+        <v>1.979779112124782</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7691026186881442</v>
+        <v>0.7775915183204862</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.684472730669927</v>
+        <v>3.689566070449332</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.128887759133334</v>
+        <v>-3.08023783321979</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981105785134701</v>
+        <v>2.000565755500118</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.7034070919313</v>
+        <v>3.708500431710705</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.26484076718965</v>
+        <v>-3.216190841276106</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.110827714057134</v>
+        <v>2.130287684422552</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.88751022407626</v>
+        <v>3.892603563855665</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.287248884994522</v>
+        <v>-3.238598959080978</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.093981161838179</v>
+        <v>2.113441132203596</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7924718643482054</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.879626918979253</v>
+        <v>3.884720258758658</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.435254652473922</v>
+        <v>-3.386604726560377</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036832854396056</v>
+        <v>2.056292824761474</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6972559558523219</v>
+        <v>0.7057448554846639</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.829644713210765</v>
+        <v>3.834738052990171</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.444695578362452</v>
+        <v>-3.396045652448907</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.089310201762491</v>
+        <v>2.108770172127909</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8196830733957133</v>
+        <v>0.8281719730280553</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.959354701458647</v>
+        <v>3.964448041238052</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.496969185698093</v>
+        <v>-3.448319259784549</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.071291853373536</v>
+        <v>2.090751823738954</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7758983656924141</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.930881631602563</v>
+        <v>3.935974971381969</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347699</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.573299163298999</v>
+        <v>-3.524649237385455</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.038871675226948</v>
+        <v>2.058331645592366</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7758983656924141</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.928993444496339</v>
+        <v>3.934086784275744</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.775552883623352</v>
+        <v>-3.726902957709808</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.952790416700069</v>
+        <v>1.972250387065487</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5651557457357186</v>
+        <v>0.5736446453680606</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.802461441904589</v>
+        <v>3.807554781683994</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.937121309150607</v>
+        <v>-3.888471383237063</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.88659705669932</v>
+        <v>1.906057027064737</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.724825697836013</v>
+        <v>3.729919037615419</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.7549119076471</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.069422601248161</v>
+        <v>-4.020772675334617</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.846749946726217</v>
+        <v>1.866209917091634</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.737899104701932</v>
+        <v>3.742992444481337</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.070984244063021</v>
+        <v>-4.022334318149476</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.846125289600273</v>
+        <v>1.865585259965691</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4468617215701812</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.737899104701932</v>
+        <v>3.742992444481337</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.098885031172493</v>
+        <v>-4.050235105258949</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.833489015883486</v>
+        <v>1.852948986248903</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4037758977949044</v>
+        <v>0.4122647974272464</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.715664991343173</v>
+        <v>3.720758331122579</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.221411133875387</v>
+        <v>-4.172761207961843</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.781243018779527</v>
+        <v>1.800702989144945</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2812497950920105</v>
+        <v>0.2897386947243525</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.638913773698636</v>
+        <v>3.644007113478041</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.451925630060976</v>
+        <v>-4.403275704147432</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.755743179895795</v>
+        <v>1.775203150261213</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05073529890642181</v>
+        <v>0.05922419853876382</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.567311035577786</v>
+        <v>3.572404375357191</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.7086464480558</v>
+        <v>-4.659996522142256</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.793366571699712</v>
+        <v>1.81282654206513</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.642574010093345</v>
+        <v>3.64766734987275</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.862632865831941</v>
+        <v>-4.813982939918397</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.800752273734896</v>
+        <v>1.820212244100314</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.711554279238984</v>
+        <v>3.716647619018389</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.812110962004275</v>
+        <v>-4.763461036090731</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.807012237386083</v>
+        <v>1.826472207751501</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.697605481359105</v>
+        <v>3.70269882113851</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.064586116011999</v>
+        <v>-5.015936190098455</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.717892664838407</v>
+        <v>1.737352635203825</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.709475970414519</v>
+        <v>3.714569310193924</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.357481872491412</v>
+        <v>-5.308831946577867</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.601944896765586</v>
+        <v>1.621404867131004</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.04919037560505102</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.710686504933463</v>
+        <v>3.715779844712868</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.515025944220853</v>
+        <v>-5.466376018307309</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.543049010301131</v>
+        <v>1.562508980666549</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1245810803776675</v>
+        <v>-0.1160921807453255</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.674667164076619</v>
+        <v>3.679760503856025</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.792990339804127</v>
+        <v>-5.744340413890582</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.426941104804011</v>
+        <v>1.446401075169429</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2057119150308098</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.615973176241519</v>
+        <v>3.621066516020924</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.909958032443018</v>
+        <v>-5.861308106529473</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.542358084447499</v>
+        <v>1.561818054812917</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2057119150308098</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.778177232940562</v>
+        <v>3.783270572719968</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.994675974663971</v>
+        <v>-5.946026048750427</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.503317545522932</v>
+        <v>1.522777515888349</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2993168435911981</v>
+        <v>-0.2908279439588561</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.721954253547549</v>
+        <v>3.727047593326954</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253284</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.076610792932854</v>
+        <v>-6.02796086701931</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.48077303578387</v>
+        <v>1.500233006149287</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3092515891782783</v>
+        <v>-0.3007626895459363</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.726222823763792</v>
+        <v>3.731316163543197</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717826</v>
+        <v>3.783647027717828</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.178586915181262</v>
+        <v>-6.129936989267717</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.448908225340409</v>
+        <v>1.468368195705827</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4112277114266859</v>
+        <v>-0.4027388117943439</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.67396278887065</v>
+        <v>3.679056128650055</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616944</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.06858063170404</v>
+        <v>-6.019930705790496</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.485063625975473</v>
+        <v>1.504523596340891</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3880231395094107</v>
+        <v>-0.3795342398770687</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.68003841926519</v>
+        <v>3.685131759044595</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.925521055963115</v>
+        <v>-5.876871130049571</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.546537466993818</v>
+        <v>1.565997437359235</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3800097129194314</v>
+        <v>-0.3715208132870894</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.689096485941152</v>
+        <v>3.694189825720557</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436924</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.624074330491277</v>
+        <v>-5.575424404577733</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.674377040065088</v>
+        <v>1.693837010430506</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.87722540410679</v>
+        <v>3.882318743886196</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064762</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.648664574726461</v>
+        <v>-5.600014648812917</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.665512120123725</v>
+        <v>1.684972090489143</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.878196581859501</v>
+        <v>3.883289921638906</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859295</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.597626198719941</v>
+        <v>-5.548976272806397</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.686770374906089</v>
+        <v>1.706230345271507</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.07007408781525215</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.879039486239256</v>
+        <v>3.884132826018662</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354679</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.55648690385331</v>
+        <v>-5.507836977939766</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.722264191726886</v>
+        <v>1.741724162092304</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.03742369258096334</v>
+        <v>-0.02893479294862134</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.92276116203338</v>
+        <v>3.927854501812785</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085615</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.445880763773708</v>
+        <v>-5.397230837860164</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.582690643882662</v>
+        <v>1.602150614248079</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.07318244749863867</v>
+        <v>0.08167134713098068</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.805308842205076</v>
+        <v>3.810402181984481</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462776</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.576461498304551</v>
+        <v>-5.527811572391006</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.533960394144289</v>
+        <v>1.553420364509706</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.730462445560534</v>
+        <v>3.735555785339939</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218592</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.411965164113589</v>
+        <v>-5.363315238200045</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.584185746896756</v>
+        <v>1.603645717262173</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.714889264636617</v>
+        <v>3.719982604416022</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462763</v>
+        <v>3.821044820462765</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.287484683389637</v>
+        <v>-5.238834757476093</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.633165649622766</v>
+        <v>1.652625619988184</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.04890938739986184</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.714076975073046</v>
+        <v>3.719170314852452</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533045</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.297869878279527</v>
+        <v>-5.249219952365983</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.638880350791883</v>
+        <v>1.658340321157301</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.06778348192209316</v>
+        <v>-0.05929458228975115</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.717714637264185</v>
+        <v>3.72280797704359</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120417</v>
+        <v>3.834429654120421</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.316458037001752</v>
+        <v>-5.267808111088208</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.702282093079418</v>
+        <v>1.721742063444835</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.07788274101197651</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.777398747807275</v>
+        <v>3.782492087586681</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85513469588169</v>
+        <v>3.855134695881691</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.174741289187347</v>
+        <v>-5.126091363273803</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.755837803023478</v>
+        <v>1.775297773388896</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.07788274101197651</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.774267758625574</v>
+        <v>3.779361098404979</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,45 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.792071428858693</v>
+        <v>3.815657372493991</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.073918155496919</v>
+        <v>-5.025268229583375</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.800697951439041</v>
+        <v>1.820157921804459</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.07390742515996468</v>
+        <v>-0.06541852552762267</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.786277182855577</v>
+        <v>3.791370522634983</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="2" t="n">
+        <v>45503</v>
+      </c>
+      <c r="B2041" t="n">
+        <v>3.836069622906843</v>
+      </c>
+      <c r="C2041" t="n">
+        <v>3.836809100201775</v>
+      </c>
+      <c r="D2041" t="n">
+        <v>-5.025268229583375</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>1.820157921804459</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>-0.06541852552762267</v>
+      </c>
+      <c r="G2041" t="n">
+        <v>3.829872897188143</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.5%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.1%</t>
+          <t>-685.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.5%</t>
+          <t>-153.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.2%</t>
+          <t>-202.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-237.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-60.8%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392984</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.527082093350184</v>
+        <v>-4.618984306435109</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.168272608872625</v>
+        <v>1.131511723638655</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3614328303452544</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.406909009985685</v>
+        <v>-4.498811223070611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.217487686658726</v>
+        <v>1.180726801424756</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4816059137097533</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.262236864885947</v>
+        <v>-4.354139077970873</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.285444647260061</v>
+        <v>1.248683762026091</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6262780588094907</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.32211169224364</v>
+        <v>-4.414013905328566</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24753220771841</v>
+        <v>1.21077132248444</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5664032314517986</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.202291461332803</v>
+        <v>-4.294193674417729</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.310749469316953</v>
+        <v>1.273988584082983</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5664032314517986</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.204761167794609</v>
+        <v>-4.296663380879535</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.217405786054673</v>
+        <v>1.180644900820702</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5639335249899924</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.273131354118619</v>
+        <v>-4.365033567203545</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10931957301037</v>
+        <v>1.0725586877764</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5732092240262073</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.286919406965666</v>
+        <v>-4.378821620050592</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094241060503442</v>
+        <v>1.057480175269472</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5732092240262073</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.342439482858255</v>
+        <v>-4.434341695943181</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.209063866838609</v>
+        <v>1.172302981604639</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5732092240262073</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.166965223065786</v>
+        <v>-4.258867436150712</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.283820802747385</v>
+        <v>1.247059917513414</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5732092240262073</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.277901475707035</v>
+        <v>-4.369803688791961</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.215188330452092</v>
+        <v>1.178427445218122</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5732092240262073</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.244237930234752</v>
+        <v>-4.336140143319679</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.157192062042455</v>
+        <v>1.120431176808484</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6068727694984892</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.184385311031029</v>
+        <v>-4.276287524115956</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191305496156077</v>
+        <v>1.154544610922106</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6068727694984892</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>-4.190044061089578</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.220749151940488</v>
+        <v>1.183988266706517</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6068727694984892</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>-4.235350880488558</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.194402199625421</v>
+        <v>1.157641314391451</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5660626064892584</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>-4.264383985190859</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.183340830777603</v>
+        <v>1.146579945543632</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5660626064892584</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>-4.171573503739999</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149737715249312</v>
+        <v>1.112976830015342</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6588730879401178</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>-4.215962973069427</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133855403442142</v>
+        <v>1.097094518208171</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6144836186106901</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>-4.33250457817477</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.082314469911728</v>
+        <v>1.045553584677757</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4979420135053474</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>-4.220127576992097</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.132756566215464</v>
+        <v>1.095995680981494</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4979420135053474</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>-4.247907974893449</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.133141608823462</v>
+        <v>1.096380723589492</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4701616156039943</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>-4.366288647623588</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9241450597320604</v>
+        <v>0.8873841744980897</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4029437634530181</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>-4.474902726066919</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000849089073933</v>
+        <v>0.9640882038399627</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4029437634530181</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>-4.439493687818776</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.029525730475514</v>
+        <v>0.992764845241543</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4029437634530181</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>-4.401110025260625</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.042298636841143</v>
+        <v>1.005537751607172</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4413274260111693</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>-4.223993695225459</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109874197700511</v>
+        <v>1.07311331246654</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4413274260111693</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>-4.269085940059004</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092520691529006</v>
+        <v>1.055759806295035</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3794313828417795</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>-4.089710518820237</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158057835330927</v>
+        <v>1.121296950096957</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5362081410124981</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>-4.134724732340842</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120859605254275</v>
+        <v>1.084098720020304</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5058592456978935</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>-4.401729242613277</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019749363484246</v>
+        <v>0.9829884782502758</v>
       </c>
       <c r="F1959" t="n">
         <v>0.311496207654945</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>-4.50292702405045</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9784741728058788</v>
+        <v>0.9417132875719081</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2430873941096258</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>-4.496416057436138</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9786785210059206</v>
+        <v>0.9419176357719499</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2430873941096258</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>-4.47737792972884</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9828184912970845</v>
+        <v>0.9460576060631138</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1849037827784312</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>-4.508504560879459</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.089662240471027</v>
+        <v>1.052901355237057</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1849037827784312</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>-4.522371322213377</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084948864923594</v>
+        <v>1.048187979689623</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1470458660446083</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>-4.477567150673447</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.108879063936492</v>
+        <v>1.072118178702521</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1470458660446083</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>-4.329824180438444</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.065926473307692</v>
+        <v>1.029165588073722</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3148532232794914</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>-4.413645401713143</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035191606329294</v>
+        <v>0.9984307210953232</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3148532232794914</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>-4.407492695660358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038315037142066</v>
+        <v>1.001554151908095</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3210059293322757</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>-4.42430199381086</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.030671794621975</v>
+        <v>0.9939109093880047</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3041966311817741</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>-4.362003995034738</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.121926547929245</v>
+        <v>1.085165662695275</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3041966311817741</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>-4.16021379736958</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.004934628709436</v>
+        <v>0.9681737434754649</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5022148233509285</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>-4.211100510055775</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.054870175957133</v>
+        <v>1.018109290723162</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4513281106647339</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>-4.308841054680749</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.030401694223187</v>
+        <v>0.9936408089892161</v>
       </c>
       <c r="F1973" t="n">
         <v>0.4354388325317538</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>-4.369050352686034</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.004853955845745</v>
+        <v>0.9680930706117739</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3752295345264692</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>-4.402361215459609</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.033914392458444</v>
+        <v>0.9532603435422722</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>-4.357988083821041</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.051526512549307</v>
+        <v>0.9708724636331358</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>-4.380468434679925</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.036928166344344</v>
+        <v>0.9562741174281724</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4196026661650378</v>
+        <v>0.4520945778033987</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.960579515312913</v>
+        <v>2.980074662295929</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>-4.33281270411887</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.062372215596571</v>
+        <v>0.9817181666803994</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4672583967260935</v>
+        <v>0.4997503083644543</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.995554710677351</v>
+        <v>3.015049857660367</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>-4.232294545620115</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.107471852370798</v>
+        <v>1.026817803454626</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.567776555224848</v>
+        <v>0.6002684668632089</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.060757979151328</v>
+        <v>3.080253126134345</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>-4.292961136022504</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069959888685714</v>
+        <v>0.9893058397695429</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4860782385063144</v>
+        <v>0.5185701501446752</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.99849366159608</v>
+        <v>3.017988808579097</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.81683703393277</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>-4.248122734414105</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091992951939702</v>
+        <v>1.011338903023531</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4906216714511838</v>
+        <v>0.5231135830895447</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.005317423973631</v>
+        <v>3.024812570956647</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>-4.267621190656113</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088354509073977</v>
+        <v>1.007700460157805</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4425370301712795</v>
+        <v>0.4750289418096404</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.980627578836766</v>
+        <v>3.000122725819783</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>-4.223418353570213</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111915246436174</v>
+        <v>1.031261197520003</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.48673986725718</v>
+        <v>0.5192317788955408</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.013028883616144</v>
+        <v>3.03252403059916</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>-4.260397381233656</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095533635840044</v>
+        <v>1.014879586923873</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5237137690485105</v>
+        <v>0.5562056806868714</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.03362322516019</v>
+        <v>3.053118372143206</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>-4.102105963694384</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210097968038793</v>
+        <v>1.129443919122622</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5237137690485105</v>
+        <v>0.5562056806868714</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.084870990343229</v>
+        <v>3.104366137326246</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>-3.894463960059908</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291595474086837</v>
+        <v>1.210941425170665</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7313557726829867</v>
+        <v>0.7638476843213475</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.207896897118168</v>
+        <v>3.227392044101185</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>-3.84343186733738</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306956539414118</v>
+        <v>1.226302490497946</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7823878654055146</v>
+        <v>0.8148797770438755</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.233464380989955</v>
+        <v>3.252959527972971</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>-3.778207686210174</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350233615957705</v>
+        <v>1.269579567041534</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8476120465327203</v>
+        <v>0.8801039581710811</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.289786293758983</v>
+        <v>3.309281440742</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>-3.74078066613904</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361165396285439</v>
+        <v>1.280511347369268</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8528635845619019</v>
+        <v>0.8853554962002628</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.288898188875772</v>
+        <v>3.308393335858789</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.623940245222266</v>
+        <v>-3.760892322173749</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.328504308067218</v>
+        <v>1.273723477286624</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8723798291916631</v>
+        <v>0.896382841197682</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.301864727984869</v>
+        <v>3.316266535188481</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.570195430795061</v>
+        <v>-3.707147507746544</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.51056000485931</v>
+        <v>1.455779174078717</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8824431386321251</v>
+        <v>0.9064461506381439</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.468460484670358</v>
+        <v>3.482862291873968</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.495413169770048</v>
+        <v>-3.632365246721531</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.660585818487132</v>
+        <v>1.605804987706539</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9572253996571377</v>
+        <v>0.9812284116631566</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.633442750503182</v>
+        <v>3.647844557706793</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.46932908550624</v>
+        <v>-3.606281162457723</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.662727428206515</v>
+        <v>1.607946597425921</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9572253996571377</v>
+        <v>0.9812284116631566</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.625150726517041</v>
+        <v>3.639552533720652</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.391197904657294</v>
+        <v>-3.528149981608776</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.692173096129873</v>
+        <v>1.63739226534928</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.031402210540822</v>
+        <v>1.055405222546841</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.667850008631031</v>
+        <v>3.682251815834642</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.382305443264011</v>
+        <v>-3.519257520215493</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.713284486413977</v>
+        <v>1.658503655633384</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.031402210540822</v>
+        <v>1.055405222546841</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.685404414357823</v>
+        <v>3.699806221561434</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.550781560233889</v>
+        <v>-3.687733637185371</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.63774908703061</v>
+        <v>1.582968256250017</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.003454374824241</v>
+        <v>1.02745738683026</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.660490760332458</v>
+        <v>3.67489256753607</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.852982031372306</v>
+        <v>-2.989934108323788</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.898138595763105</v>
+        <v>1.843357764982512</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9331063154538308</v>
+        <v>0.9571093274598497</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.599551621898073</v>
+        <v>3.613953429101685</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.830260927689153</v>
+        <v>-2.967213004640636</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.897891059733271</v>
+        <v>1.843110228952678</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9331063154538308</v>
+        <v>0.9571093274598497</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.590215644394978</v>
+        <v>3.604617451598589</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.959462740983196</v>
+        <v>-3.096414817934678</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.005116460266823</v>
+        <v>1.95033562948623</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8039045021597886</v>
+        <v>0.8279075141658074</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.671600682269722</v>
+        <v>3.686002489473333</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.114243747761451</v>
+        <v>-3.251195824712934</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.980281880049167</v>
+        <v>1.925501049268574</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7705368281053124</v>
+        <v>0.7945398401113313</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.688657900330683</v>
+        <v>3.703059707534294</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.107189057546277</v>
+        <v>-3.24414113449776</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.979779112124782</v>
+        <v>1.924998281344189</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7775915183204862</v>
+        <v>0.8015945303265051</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.689566070449332</v>
+        <v>3.703967877652943</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.08023783321979</v>
+        <v>-3.217189910171272</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.000565755500118</v>
+        <v>1.945784924719526</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.8164748763542242</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.708500431710705</v>
+        <v>3.722902238914316</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.216190841276106</v>
+        <v>-3.353142918227588</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.130287684422552</v>
+        <v>2.075506853641959</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.8164748763542242</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.892603563855665</v>
+        <v>3.907005371059276</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.238598959080978</v>
+        <v>-3.37555103603246</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.113441132203596</v>
+        <v>2.058660301423003</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7924718643482054</v>
+        <v>0.8164748763542242</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.884720258758658</v>
+        <v>3.899122065962269</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.386604726560377</v>
+        <v>-3.52355680351186</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.056292824761474</v>
+        <v>2.001511993980881</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7057448554846639</v>
+        <v>0.7297478674906828</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.834738052990171</v>
+        <v>3.849139860193782</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.396045652448907</v>
+        <v>-3.53299772940039</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.108770172127909</v>
+        <v>2.053989341347316</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8281719730280553</v>
+        <v>0.8521749850340742</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.964448041238052</v>
+        <v>3.978849848441664</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.448319259784549</v>
+        <v>-3.585271336736031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.090751823738954</v>
+        <v>2.03597099295836</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7758983656924141</v>
+        <v>0.7999013776984329</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.935974971381969</v>
+        <v>3.95037677858558</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.524649237385455</v>
+        <v>-3.661601314336937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.058331645592366</v>
+        <v>2.003550814811773</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7758983656924141</v>
+        <v>0.7999013776984329</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.934086784275744</v>
+        <v>3.948488591479355</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.726902957709808</v>
+        <v>-3.86385503466129</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.972250387065487</v>
+        <v>1.917469556284894</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5736446453680606</v>
+        <v>0.5976476573740794</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.807554781683994</v>
+        <v>3.821956588887605</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.888471383237063</v>
+        <v>-4.025423460188545</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.906057027064737</v>
+        <v>1.851276196284144</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4708647335762001</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.729919037615419</v>
+        <v>3.74432084481903</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.020772675334617</v>
+        <v>-4.157724752286098</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.866209917091634</v>
+        <v>1.811429086311042</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4708647335762001</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.742992444481337</v>
+        <v>3.757394251684949</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763529</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.022334318149476</v>
+        <v>-4.159286395100958</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.865585259965691</v>
+        <v>1.810804429185098</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4468617215701812</v>
+        <v>0.4708647335762001</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.742992444481337</v>
+        <v>3.757394251684949</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392112</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.050235105258949</v>
+        <v>-4.187187182210431</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.852948986248903</v>
+        <v>1.798168155468311</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4122647974272464</v>
+        <v>0.4362678094332653</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.720758331122579</v>
+        <v>3.73516013832619</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172523</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.172761207961843</v>
+        <v>-4.309713284913324</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.800702989144945</v>
+        <v>1.745922158364352</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2897386947243525</v>
+        <v>0.3137417067303714</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.644007113478041</v>
+        <v>3.658408920681652</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.403275704147432</v>
+        <v>-4.540227781098913</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.775203150261213</v>
+        <v>1.72042231948062</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05922419853876382</v>
+        <v>0.08322721054478266</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.572404375357191</v>
+        <v>3.586806182560803</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199802</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.659996522142256</v>
+        <v>-4.796948599093737</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.81282654206513</v>
+        <v>1.758045711284538</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.02518736359903218</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.64766734987275</v>
+        <v>3.662069157076361</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.813982939918397</v>
+        <v>-4.950935016869877</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.820212244100314</v>
+        <v>1.765431413319722</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.02518736359903218</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.716647619018389</v>
+        <v>3.731049426222001</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.763461036090731</v>
+        <v>-4.900413113042211</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.826472207751501</v>
+        <v>1.771691376970909</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.02518736359903218</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.70269882113851</v>
+        <v>3.717100628342122</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65634689399489</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.015936190098455</v>
+        <v>-5.152888267049936</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.737352635203825</v>
+        <v>1.682571804423233</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.02518736359903218</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.714569310193924</v>
+        <v>3.728971117397536</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358294</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.308831946577867</v>
+        <v>-5.445784023529348</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.621404867131004</v>
+        <v>1.566624036350412</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.04919037560505102</v>
+        <v>-0.02518736359903218</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.715779844712868</v>
+        <v>3.730181651916479</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.466376018307309</v>
+        <v>-5.60332809525879</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.562508980666549</v>
+        <v>1.507728149885957</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1160921807453255</v>
+        <v>-0.09208916873930667</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.679760503856025</v>
+        <v>3.694162311059636</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.744340413890582</v>
+        <v>-5.881292490842063</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.446401075169429</v>
+        <v>1.391620244388837</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2057119150308098</v>
+        <v>-0.1817089030247909</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.621066516020924</v>
+        <v>3.635468323224535</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215466</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.861308106529473</v>
+        <v>-5.998260183480954</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.561818054812917</v>
+        <v>1.507037224032324</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2057119150308098</v>
+        <v>-0.1817089030247909</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.783270572719968</v>
+        <v>3.797672379923579</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456688</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.946026048750427</v>
+        <v>-6.082978125701907</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.522777515888349</v>
+        <v>1.467996685107757</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2908279439588561</v>
+        <v>-0.2668249319528373</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.727047593326954</v>
+        <v>3.741449400530565</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253284</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.02796086701931</v>
+        <v>-6.243486157249714</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.500233006149287</v>
+        <v>1.414022890057126</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3007626895459363</v>
+        <v>-0.3738846209631836</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.731316163543197</v>
+        <v>3.687443004692849</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717828</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.129936989267717</v>
+        <v>-6.345462279498121</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.468368195705827</v>
+        <v>1.382158079613665</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4027388117943439</v>
+        <v>-0.4758607432115912</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.679056128650055</v>
+        <v>3.635182969799707</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.019930705790496</v>
+        <v>-6.2354559960209</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.504523596340891</v>
+        <v>1.418313480248729</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3795342398770687</v>
+        <v>-0.452656171294316</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.685131759044595</v>
+        <v>3.641258600194247</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.876871130049571</v>
+        <v>-6.092396420279973</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.565997437359235</v>
+        <v>1.479787321267074</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3715208132870894</v>
+        <v>-0.4446427447043367</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.694189825720557</v>
+        <v>3.650316666870209</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.575424404577733</v>
+        <v>-5.790949694808136</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.693837010430506</v>
+        <v>1.607626894338345</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.1431960192324994</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.882318743886196</v>
+        <v>3.838445585035847</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.600014648812917</v>
+        <v>-5.81553993904332</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.684972090489143</v>
+        <v>1.598761974396982</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.1431960192324994</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.883289921638906</v>
+        <v>3.839416762788558</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.548976272806397</v>
+        <v>-5.7645015630368</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.706230345271507</v>
+        <v>1.620020229179346</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.07007408781525215</v>
+        <v>-0.1431960192324994</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.884132826018662</v>
+        <v>3.840259667168313</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354683</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.507836977939766</v>
+        <v>-5.723362268170169</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.741724162092304</v>
+        <v>1.655514046000143</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.02893479294862134</v>
+        <v>-0.1020567243658686</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.927854501812785</v>
+        <v>3.883981342962437</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.397230837860164</v>
+        <v>-5.612756128090567</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.602150614248079</v>
+        <v>1.515940498155918</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.08167134713098068</v>
+        <v>0.00854941571373341</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.810402181984481</v>
+        <v>3.766529023134133</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462781</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.527811572391006</v>
+        <v>-5.743336862621409</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.553420364509706</v>
+        <v>1.467210248417545</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.1220313188171091</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.735555785339939</v>
+        <v>3.691682626489591</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.363315238200045</v>
+        <v>-5.578840528430447</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.603645717262173</v>
+        <v>1.517435601170012</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.1220313188171091</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.719982604416022</v>
+        <v>3.676109445565674</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462765</v>
+        <v>3.821044820462768</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.238834757476093</v>
+        <v>-5.454360047706496</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.652625619988184</v>
+        <v>1.566415503896023</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.04890938739986184</v>
+        <v>-0.1220313188171091</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.719170314852452</v>
+        <v>3.675297156002103</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.832321184533049</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.249219952365983</v>
+        <v>-5.464745242596385</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.658340321157301</v>
+        <v>1.57213020506514</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.05929458228975115</v>
+        <v>-0.1324165137069984</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.72280797704359</v>
+        <v>3.678934818193242</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120421</v>
+        <v>3.834429654120423</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.267808111088208</v>
+        <v>-5.48333340131861</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.721742063444835</v>
+        <v>1.635531947352674</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.07788274101197651</v>
+        <v>-0.1510046724292238</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.782492087586681</v>
+        <v>3.738618928736332</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881691</v>
+        <v>3.855134695881693</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.126091363273803</v>
+        <v>-5.341616653504206</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.775297773388896</v>
+        <v>1.689087657296735</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.07788274101197651</v>
+        <v>-0.1510046724292238</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.779361098404979</v>
+        <v>3.735487939554631</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493991</v>
+        <v>3.815657372493995</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.025268229583375</v>
+        <v>-5.240793519813778</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.820157921804459</v>
+        <v>1.733947805712297</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.06541852552762267</v>
+        <v>-0.1385404569448699</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.791370522634983</v>
+        <v>3.747497363784634</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.836069622906843</v>
+        <v>3.8485102474377</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.836809100201775</v>
+        <v>3.858970234754953</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.025268229583375</v>
+        <v>-5.240793519813778</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.820157921804459</v>
+        <v>1.733947805712297</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.06541852552762267</v>
+        <v>-0.1385404569448699</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.829872897188143</v>
+        <v>3.85203403174132</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.7%</t>
+          <t>-686.4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.7%</t>
+          <t>-153.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-202.8%</t>
+          <t>-203.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-130.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-237.8%</t>
+          <t>-245.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-79.1%</t>
         </is>
       </c>
     </row>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.618984306435109</v>
+        <v>-4.527082093350184</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.131511723638655</v>
+        <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3614328303452544</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.498811223070611</v>
+        <v>-4.406909009985685</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.180726801424756</v>
+        <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4816059137097533</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.354139077970873</v>
+        <v>-4.262236864885947</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.248683762026091</v>
+        <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6262780588094907</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.414013905328566</v>
+        <v>-4.32211169224364</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.21077132248444</v>
+        <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5664032314517986</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.294193674417729</v>
+        <v>-4.202291461332803</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.273988584082983</v>
+        <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5664032314517986</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.296663380879535</v>
+        <v>-4.204761167794609</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.180644900820702</v>
+        <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5639335249899924</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.365033567203545</v>
+        <v>-4.273131354118619</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.0725586877764</v>
+        <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5732092240262073</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.378821620050592</v>
+        <v>-4.286919406965666</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.057480175269472</v>
+        <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5732092240262073</v>
@@ -46125,10 +46125,10 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.434341695943181</v>
+        <v>-4.342439482858255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.172302981604639</v>
+        <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5732092240262073</v>
@@ -46148,10 +46148,10 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.258867436150712</v>
+        <v>-4.166965223065786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.247059917513414</v>
+        <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5732092240262073</v>
@@ -46171,10 +46171,10 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.369803688791961</v>
+        <v>-4.277901475707035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.178427445218122</v>
+        <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5732092240262073</v>
@@ -46194,10 +46194,10 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.336140143319679</v>
+        <v>-4.244237930234752</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.120431176808484</v>
+        <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6068727694984892</v>
@@ -46217,10 +46217,10 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.276287524115956</v>
+        <v>-4.184385311031029</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.154544610922106</v>
+        <v>1.191305496156077</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6068727694984892</v>
@@ -46240,10 +46240,10 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.190044061089578</v>
+        <v>-4.098141848004651</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.183988266706517</v>
+        <v>1.220749151940488</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6068727694984892</v>
@@ -46263,10 +46263,10 @@
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.235350880488558</v>
+        <v>-4.143448667403631</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.157641314391451</v>
+        <v>1.194402199625421</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5660626064892584</v>
@@ -46286,10 +46286,10 @@
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.264383985190859</v>
+        <v>-4.172481772105932</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.146579945543632</v>
+        <v>1.183340830777603</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5660626064892584</v>
@@ -46309,10 +46309,10 @@
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.171573503739999</v>
+        <v>-4.079671290655073</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.112976830015342</v>
+        <v>1.149737715249312</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6588730879401178</v>
@@ -46332,10 +46332,10 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.215962973069427</v>
+        <v>-4.1240607599845</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.097094518208171</v>
+        <v>1.133855403442142</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6144836186106901</v>
@@ -46355,10 +46355,10 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.33250457817477</v>
+        <v>-4.240602365089843</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.045553584677757</v>
+        <v>1.082314469911728</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4979420135053474</v>
@@ -46378,10 +46378,10 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.220127576992097</v>
+        <v>-4.12822536390717</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.095995680981494</v>
+        <v>1.132756566215464</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4979420135053474</v>
@@ -46401,10 +46401,10 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.247907974893449</v>
+        <v>-4.156005761808522</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.096380723589492</v>
+        <v>1.133141608823462</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4701616156039943</v>
@@ -46424,10 +46424,10 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.366288647623588</v>
+        <v>-4.274386434538661</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8873841744980897</v>
+        <v>0.9241450597320604</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4029437634530181</v>
@@ -46447,10 +46447,10 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.474902726066919</v>
+        <v>-4.383000512981992</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9640882038399627</v>
+        <v>1.000849089073933</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4029437634530181</v>
@@ -46470,10 +46470,10 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.439493687818776</v>
+        <v>-4.347591474733849</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.992764845241543</v>
+        <v>1.029525730475514</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4029437634530181</v>
@@ -46493,10 +46493,10 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.401110025260625</v>
+        <v>-4.309207812175698</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.005537751607172</v>
+        <v>1.042298636841143</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4413274260111693</v>
@@ -46516,10 +46516,10 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.223993695225459</v>
+        <v>-4.132091482140532</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.07311331246654</v>
+        <v>1.109874197700511</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4413274260111693</v>
@@ -46539,10 +46539,10 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.269085940059004</v>
+        <v>-4.177183726974078</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.055759806295035</v>
+        <v>1.092520691529006</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3794313828417795</v>
@@ -46562,10 +46562,10 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.089710518820237</v>
+        <v>-3.99780830573531</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.121296950096957</v>
+        <v>1.158057835330927</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5362081410124981</v>
@@ -46585,10 +46585,10 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.134724732340842</v>
+        <v>-4.042822519255916</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.084098720020304</v>
+        <v>1.120859605254275</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5058592456978935</v>
@@ -46608,10 +46608,10 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.401729242613277</v>
+        <v>-4.309827029528351</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9829884782502758</v>
+        <v>1.019749363484246</v>
       </c>
       <c r="F1959" t="n">
         <v>0.311496207654945</v>
@@ -46631,10 +46631,10 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.50292702405045</v>
+        <v>-4.411024810965523</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9417132875719081</v>
+        <v>0.9784741728058788</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2430873941096258</v>
@@ -46654,10 +46654,10 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.496416057436138</v>
+        <v>-4.404513844351211</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9419176357719499</v>
+        <v>0.9786785210059206</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2430873941096258</v>
@@ -46677,10 +46677,10 @@
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.47737792972884</v>
+        <v>-4.385475716643914</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9460576060631138</v>
+        <v>0.9828184912970845</v>
       </c>
       <c r="F1962" t="n">
         <v>0.1849037827784312</v>
@@ -46700,10 +46700,10 @@
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.508504560879459</v>
+        <v>-4.416602347794532</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.052901355237057</v>
+        <v>1.089662240471027</v>
       </c>
       <c r="F1963" t="n">
         <v>0.1849037827784312</v>
@@ -46723,10 +46723,10 @@
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.522371322213377</v>
+        <v>-4.43046910912845</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.048187979689623</v>
+        <v>1.084948864923594</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1470458660446083</v>
@@ -46746,10 +46746,10 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.477567150673447</v>
+        <v>-4.38566493758852</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.072118178702521</v>
+        <v>1.108879063936492</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1470458660446083</v>
@@ -46769,10 +46769,10 @@
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.329824180438444</v>
+        <v>-4.237921967353517</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.029165588073722</v>
+        <v>1.065926473307692</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3148532232794914</v>
@@ -46792,10 +46792,10 @@
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.413645401713143</v>
+        <v>-4.321743188628216</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9984307210953232</v>
+        <v>1.035191606329294</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3148532232794914</v>
@@ -46815,10 +46815,10 @@
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.407492695660358</v>
+        <v>-4.315590482575431</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.001554151908095</v>
+        <v>1.038315037142066</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3210059293322757</v>
@@ -46838,10 +46838,10 @@
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.42430199381086</v>
+        <v>-4.332399780725933</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9939109093880047</v>
+        <v>1.030671794621975</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3041966311817741</v>
@@ -46861,10 +46861,10 @@
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.362003995034738</v>
+        <v>-4.270101781949811</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.085165662695275</v>
+        <v>1.121926547929245</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3041966311817741</v>
@@ -46884,10 +46884,10 @@
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.16021379736958</v>
+        <v>-4.068311584284653</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9681737434754649</v>
+        <v>1.004934628709436</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5022148233509285</v>
@@ -46907,10 +46907,10 @@
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.211100510055775</v>
+        <v>-4.119198296970848</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.018109290723162</v>
+        <v>1.054870175957133</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4513281106647339</v>
@@ -46930,10 +46930,10 @@
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.308841054680749</v>
+        <v>-4.216938841595822</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9936408089892161</v>
+        <v>1.030401694223187</v>
       </c>
       <c r="F1973" t="n">
         <v>0.4354388325317538</v>
@@ -46953,10 +46953,10 @@
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.369050352686034</v>
+        <v>-4.277148139601107</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9680930706117739</v>
+        <v>1.004853955845745</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3752295345264692</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.402361215459609</v>
+        <v>-4.20072609316918</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9532603435422722</v>
+        <v>1.033914392458444</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3752295345264692</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.357988083821041</v>
+        <v>-4.156352961530612</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9708724636331358</v>
+        <v>1.051526512549307</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4196026661650378</v>
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.380468434679925</v>
+        <v>-4.178833312389497</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9562741174281724</v>
+        <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4520945778033987</v>
+        <v>0.4196026661650378</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980074662295929</v>
+        <v>2.960579515312913</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.33281270411887</v>
+        <v>-4.131177581828441</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9817181666803994</v>
+        <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4997503083644543</v>
+        <v>0.4672583967260935</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015049857660367</v>
+        <v>2.995554710677351</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.232294545620115</v>
+        <v>-4.030659423329686</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.026817803454626</v>
+        <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6002684668632089</v>
+        <v>0.567776555224848</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080253126134345</v>
+        <v>3.060757979151328</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.292961136022504</v>
+        <v>-4.091326013732075</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9893058397695429</v>
+        <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5185701501446752</v>
+        <v>0.4860782385063144</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.017988808579097</v>
+        <v>2.99849366159608</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81683703393277</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.248122734414105</v>
+        <v>-4.046487612123677</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.011338903023531</v>
+        <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5231135830895447</v>
+        <v>0.4906216714511838</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.024812570956647</v>
+        <v>3.005317423973631</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.267621190656113</v>
+        <v>-4.065986068365685</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.007700460157805</v>
+        <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4750289418096404</v>
+        <v>0.4425370301712795</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.000122725819783</v>
+        <v>2.980627578836766</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.223418353570213</v>
+        <v>-4.021783231279785</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.031261197520003</v>
+        <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5192317788955408</v>
+        <v>0.48673986725718</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.03252403059916</v>
+        <v>3.013028883616144</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.260397381233656</v>
+        <v>-4.058762258943228</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.014879586923873</v>
+        <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5562056806868714</v>
+        <v>0.5237137690485105</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.053118372143206</v>
+        <v>3.03362322516019</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.102105963694384</v>
+        <v>-3.900470841403955</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.129443919122622</v>
+        <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5562056806868714</v>
+        <v>0.5237137690485105</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.104366137326246</v>
+        <v>3.084870990343229</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.894463960059908</v>
+        <v>-3.692828837769479</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.210941425170665</v>
+        <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7638476843213475</v>
+        <v>0.7313557726829867</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.227392044101185</v>
+        <v>3.207896897118168</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.84343186733738</v>
+        <v>-3.641796745046951</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.226302490497946</v>
+        <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8148797770438755</v>
+        <v>0.7823878654055146</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.252959527972971</v>
+        <v>3.233464380989955</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.778207686210174</v>
+        <v>-3.576572563919745</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.269579567041534</v>
+        <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8801039581710811</v>
+        <v>0.8476120465327203</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.309281440742</v>
+        <v>3.289786293758983</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.74078066613904</v>
+        <v>-3.539145543848611</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.280511347369268</v>
+        <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8853554962002628</v>
+        <v>0.8528635845619019</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.308393335858789</v>
+        <v>3.288898188875772</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.760892322173749</v>
+        <v>-3.55925719988332</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.273723477286624</v>
+        <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.896382841197682</v>
+        <v>0.8638909295593211</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.316266535188481</v>
+        <v>3.296771388205464</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.707147507746544</v>
+        <v>-3.505512385456115</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.455779174078717</v>
+        <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9064461506381439</v>
+        <v>0.8739542389997831</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.482862291873968</v>
+        <v>3.463367144890952</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.632365246721531</v>
+        <v>-3.430730124431102</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.605804987706539</v>
+        <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9812284116631566</v>
+        <v>0.9487365000247957</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.647844557706793</v>
+        <v>3.628349410723777</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.606281162457723</v>
+        <v>-3.404646040167294</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.607946597425921</v>
+        <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9812284116631566</v>
+        <v>0.9487365000247957</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.639552533720652</v>
+        <v>3.620057386737636</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.528149981608776</v>
+        <v>-3.326514859318348</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.63739226534928</v>
+        <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.055405222546841</v>
+        <v>1.02291331090848</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.682251815834642</v>
+        <v>3.662756668851626</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.519257520215493</v>
+        <v>-3.317622397925065</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.658503655633384</v>
+        <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.055405222546841</v>
+        <v>1.02291331090848</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.699806221561434</v>
+        <v>3.680311074578417</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.687733637185371</v>
+        <v>-3.486098514894942</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.582968256250017</v>
+        <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.02745738683026</v>
+        <v>0.9949654751918995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.67489256753607</v>
+        <v>3.655397420553053</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.989934108323788</v>
+        <v>-2.788298986033359</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.843357764982512</v>
+        <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9571093274598497</v>
+        <v>0.9246174158214888</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.613953429101685</v>
+        <v>3.594458282118668</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.967213004640636</v>
+        <v>-2.765577882350207</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.843110228952678</v>
+        <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9571093274598497</v>
+        <v>0.9246174158214888</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.604617451598589</v>
+        <v>3.585122304615573</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.096414817934678</v>
+        <v>-2.894779695644249</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.95033562948623</v>
+        <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8279075141658074</v>
+        <v>0.7954156025274466</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.686002489473333</v>
+        <v>3.666507342490317</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.251195824712934</v>
+        <v>-3.049560702422505</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.925501049268574</v>
+        <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7945398401113313</v>
+        <v>0.7620479284729704</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.703059707534294</v>
+        <v>3.683564560551277</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.24414113449776</v>
+        <v>-3.042506012207331</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.924998281344189</v>
+        <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8015945303265051</v>
+        <v>0.7691026186881442</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.703967877652943</v>
+        <v>3.684472730669927</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.217189910171272</v>
+        <v>-3.015554787880843</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.945784924719526</v>
+        <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8164748763542242</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.722902238914316</v>
+        <v>3.7034070919313</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.353142918227588</v>
+        <v>-3.151507795937159</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.075506853641959</v>
+        <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8164748763542242</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.907005371059276</v>
+        <v>3.88751022407626</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.37555103603246</v>
+        <v>-3.173915913742031</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.058660301423003</v>
+        <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8164748763542242</v>
+        <v>0.7839829647158634</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.899122065962269</v>
+        <v>3.879626918979253</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.52355680351186</v>
+        <v>-3.321921681221431</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.001511993980881</v>
+        <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7297478674906828</v>
+        <v>0.6972559558523219</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.849139860193782</v>
+        <v>3.829644713210765</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.53299772940039</v>
+        <v>-3.331362607109961</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.053989341347316</v>
+        <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8521749850340742</v>
+        <v>0.8196830733957133</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.978849848441664</v>
+        <v>3.959354701458647</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.585271336736031</v>
+        <v>-3.519482464936841</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.03597099295836</v>
+        <v>2.062286541678036</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7999013776984329</v>
+        <v>0.6315632155688333</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.95037677858558</v>
+        <v>3.84937388130782</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.661601314336937</v>
+        <v>-3.595812442537747</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.003550814811773</v>
+        <v>2.029866363531449</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7999013776984329</v>
+        <v>0.6315632155688333</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.948488591479355</v>
+        <v>3.847485694201596</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.86385503466129</v>
+        <v>-3.7980661628621</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.917469556284894</v>
+        <v>1.94378510500457</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5976476573740794</v>
+        <v>0.4293094952444799</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.821956588887605</v>
+        <v>3.720953691609846</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-4.025423460188545</v>
+        <v>-3.959634588389355</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.851276196284144</v>
+        <v>1.87759174500382</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4708647335762001</v>
+        <v>0.3025265714466005</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.74432084481903</v>
+        <v>3.64331794754127</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.157724752286098</v>
+        <v>-4.091935880486909</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.811429086311042</v>
+        <v>1.837744635030718</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4708647335762001</v>
+        <v>0.3025265714466005</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.757394251684949</v>
+        <v>3.656391354407189</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.159286395100958</v>
+        <v>-4.093497523301768</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.810804429185098</v>
+        <v>1.837119977904774</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4708647335762001</v>
+        <v>0.3025265714466005</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.757394251684949</v>
+        <v>3.656391354407189</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.187187182210431</v>
+        <v>-4.121398310411241</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.798168155468311</v>
+        <v>1.824483704187987</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4362678094332653</v>
+        <v>0.2679296473036657</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73516013832619</v>
+        <v>3.63415724104843</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.309713284913324</v>
+        <v>-4.243924413114135</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.745922158364352</v>
+        <v>1.772237707084028</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3137417067303714</v>
+        <v>0.1454035446007718</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.658408920681652</v>
+        <v>3.557406023403892</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.540227781098913</v>
+        <v>-4.474438909299724</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.72042231948062</v>
+        <v>1.746737868200296</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.08322721054478266</v>
+        <v>-0.08511095158481691</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.586806182560803</v>
+        <v>3.485803285283043</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.796948599093737</v>
+        <v>-4.731159727294548</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.758045711284538</v>
+        <v>1.784361260004213</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.02518736359903218</v>
+        <v>-0.1935255257286317</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.662069157076361</v>
+        <v>3.561066259798601</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622233</v>
       </c>
       <c r="C2017" t="n">
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.950935016869877</v>
+        <v>-4.885146145070689</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.765431413319722</v>
+        <v>1.791746962039397</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.02518736359903218</v>
+        <v>-0.1935255257286317</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.731049426222001</v>
+        <v>3.630046528944241</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808525</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.900413113042211</v>
+        <v>-4.834624241243023</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.771691376970909</v>
+        <v>1.798006925690584</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.02518736359903218</v>
+        <v>-0.1935255257286317</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.717100628342122</v>
+        <v>3.616097731064362</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.152888267049936</v>
+        <v>-5.087099395250747</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.682571804423233</v>
+        <v>1.708887353142909</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.02518736359903218</v>
+        <v>-0.1935255257286317</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.728971117397536</v>
+        <v>3.627968220119776</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.445784023529348</v>
+        <v>-5.379995151730159</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.566624036350412</v>
+        <v>1.592939585070087</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.02518736359903218</v>
+        <v>-0.1935255257286317</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.730181651916479</v>
+        <v>3.62917875463872</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.60332809525879</v>
+        <v>-5.537539223459601</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.507728149885957</v>
+        <v>1.534043698605632</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.09208916873930667</v>
+        <v>-0.2604273308689062</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.694162311059636</v>
+        <v>3.593159413781876</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.881292490842063</v>
+        <v>-5.815503619042874</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.391620244388837</v>
+        <v>1.417935793108512</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.1817089030247909</v>
+        <v>-0.3500470651543905</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.635468323224535</v>
+        <v>3.534465425946775</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.998260183480954</v>
+        <v>-5.932471311681765</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.507037224032324</v>
+        <v>1.533352772752</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.1817089030247909</v>
+        <v>-0.3500470651543905</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.797672379923579</v>
+        <v>3.696669482645819</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.082978125701907</v>
+        <v>-6.017189253902719</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.467996685107757</v>
+        <v>1.494312233827433</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2668249319528373</v>
+        <v>-0.4351630940824369</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.741449400530565</v>
+        <v>3.640446503252805</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.243486157249714</v>
+        <v>-6.099124072171602</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.414022890057126</v>
+        <v>1.47176772408837</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3738846209631836</v>
+        <v>-0.445097839669517</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.687443004692849</v>
+        <v>3.644715073469049</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.345462279498121</v>
+        <v>-6.201100194420009</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.382158079613665</v>
+        <v>1.43990291364491</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4758607432115912</v>
+        <v>-0.5470739619179246</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.635182969799707</v>
+        <v>3.592455038575907</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.2354559960209</v>
+        <v>-6.091093910942788</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.418313480248729</v>
+        <v>1.476058314279974</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.452656171294316</v>
+        <v>-0.5238693900006494</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.641258600194247</v>
+        <v>3.598530668970447</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-6.092396420279973</v>
+        <v>-5.948034335201863</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.479787321267074</v>
+        <v>1.537532155298318</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4446427447043367</v>
+        <v>-0.5158559634106701</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.650316666870209</v>
+        <v>3.607588735646409</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.790949694808136</v>
+        <v>-5.646587609730025</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.607626894338345</v>
+        <v>1.665371728369589</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1431960192324994</v>
+        <v>-0.2144092379388328</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.838445585035847</v>
+        <v>3.795717653812047</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.81553993904332</v>
+        <v>-5.671177853965209</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.598761974396982</v>
+        <v>1.656506808428226</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1431960192324994</v>
+        <v>-0.2144092379388328</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.839416762788558</v>
+        <v>3.796688831564758</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.7645015630368</v>
+        <v>-5.620139477958689</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.620020229179346</v>
+        <v>1.67776506321059</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1431960192324994</v>
+        <v>-0.2144092379388328</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.840259667168313</v>
+        <v>3.797531735944513</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354681</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.723362268170169</v>
+        <v>-5.579000183092058</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.655514046000143</v>
+        <v>1.713258880031387</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.1020567243658686</v>
+        <v>-0.173269943072202</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.883981342962437</v>
+        <v>3.841253411738637</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.612756128090567</v>
+        <v>-5.468394043012456</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.515940498155918</v>
+        <v>1.573685332187163</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.00854941571373341</v>
+        <v>-0.06266380299259999</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.766529023134133</v>
+        <v>3.723801091910333</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462781</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.743336862621409</v>
+        <v>-5.598974777543298</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.467210248417545</v>
+        <v>1.524955082448789</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1220313188171091</v>
+        <v>-0.1932445375234425</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.691682626489591</v>
+        <v>3.648954695265791</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.775043021218596</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.578840528430447</v>
+        <v>-5.434478443352337</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.517435601170012</v>
+        <v>1.575180435201257</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1220313188171091</v>
+        <v>-0.1932445375234425</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.676109445565674</v>
+        <v>3.633381514341874</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462768</v>
+        <v>3.821044820462765</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.454360047706496</v>
+        <v>-5.309997962628385</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.566415503896023</v>
+        <v>1.624160337927267</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1220313188171091</v>
+        <v>-0.1932445375234425</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.675297156002103</v>
+        <v>3.632569224778303</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533049</v>
+        <v>3.832321184533047</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.464745242596385</v>
+        <v>-5.320383157518275</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.57213020506514</v>
+        <v>1.629875039096384</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1324165137069984</v>
+        <v>-0.2036297324133318</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.678934818193242</v>
+        <v>3.636206886969442</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120423</v>
+        <v>3.834429654120421</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.48333340131861</v>
+        <v>-5.338971316240499</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.635531947352674</v>
+        <v>1.693276781383919</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1510046724292238</v>
+        <v>-0.2222178911355572</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.738618928736332</v>
+        <v>3.695890997512532</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881693</v>
+        <v>3.855134695881691</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.341616653504206</v>
+        <v>-5.348858012275107</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.689087657296735</v>
+        <v>1.686191113788374</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1510046724292238</v>
+        <v>-0.2222178911355572</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.735487939554631</v>
+        <v>3.692760008330831</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493995</v>
+        <v>3.815657372493994</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.240793519813778</v>
+        <v>-5.248034878584679</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.733947805712297</v>
+        <v>1.731051262203937</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1385404569448699</v>
+        <v>-0.2097536756512033</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.747497363784634</v>
+        <v>3.704769432560834</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.8485102474377</v>
+        <v>3.742041699171672</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.858970234754953</v>
+        <v>3.67640782846521</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.240793519813778</v>
+        <v>-5.248034878584679</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.733947805712297</v>
+        <v>1.731051262203937</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.1385404569448699</v>
+        <v>-0.2097536756512033</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.85203403174132</v>
+        <v>3.669471625451578</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.8%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.4%</t>
+          <t>-672.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.8%</t>
+          <t>-153.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-203.1%</t>
+          <t>-197.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-130.3%</t>
+          <t>-99.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-245.0%</t>
+          <t>-231.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.519482464936841</v>
+        <v>-3.383636214445602</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.062286541678036</v>
+        <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.6315632155688333</v>
+        <v>0.7674094660600721</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.84937388130782</v>
+        <v>3.930881631602563</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.595812442537747</v>
+        <v>-3.459966192046508</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.029866363531449</v>
+        <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.6315632155688333</v>
+        <v>0.7674094660600721</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.847485694201596</v>
+        <v>3.928993444496339</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.7980661628621</v>
+        <v>-3.662219912370861</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.94378510500457</v>
+        <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4293094952444799</v>
+        <v>0.5651557457357186</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.720953691609846</v>
+        <v>3.802461441904589</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.959634588389355</v>
+        <v>-3.823788337898117</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.87759174500382</v>
+        <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3025265714466005</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.64331794754127</v>
+        <v>3.724825697836013</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.091935880486909</v>
+        <v>-3.95608962999567</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.837744635030718</v>
+        <v>1.892083135227213</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3025265714466005</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.656391354407189</v>
+        <v>3.737899104701932</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.093497523301768</v>
+        <v>-3.95765127281053</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.837119977904774</v>
+        <v>1.891458478101269</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3025265714466005</v>
+        <v>0.4383728219378392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.656391354407189</v>
+        <v>3.737899104701932</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.121398310411241</v>
+        <v>-3.985552059920003</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.824483704187987</v>
+        <v>1.878822204384482</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.2679296473036657</v>
+        <v>0.4037758977949044</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.63415724104843</v>
+        <v>3.715664991343173</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.243924413114135</v>
+        <v>-4.108078162622897</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.772237707084028</v>
+        <v>1.826576207280523</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.1454035446007718</v>
+        <v>0.2812497950920105</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.557406023403892</v>
+        <v>3.638913773698636</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.474438909299724</v>
+        <v>-4.338592658808486</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.746737868200296</v>
+        <v>1.801076368396791</v>
       </c>
       <c r="F2015" t="n">
-        <v>-0.08511095158481691</v>
+        <v>0.05073529890642181</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.485803285283043</v>
+        <v>3.567311035577786</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.731159727294548</v>
+        <v>-4.595313476803311</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.784361260004213</v>
+        <v>1.838699760200708</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.1935255257286317</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.561066259798601</v>
+        <v>3.642574010093345</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.885146145070689</v>
+        <v>-4.749299894579451</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.791746962039397</v>
+        <v>1.846085462235892</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.1935255257286317</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.630046528944241</v>
+        <v>3.711554279238984</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.834624241243023</v>
+        <v>-4.698777990751785</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.798006925690584</v>
+        <v>1.852345425887079</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.1935255257286317</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.616097731064362</v>
+        <v>3.697605481359105</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.087099395250747</v>
+        <v>-4.95125314475951</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.708887353142909</v>
+        <v>1.763225853339403</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.1935255257286317</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.627968220119776</v>
+        <v>3.709475970414519</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.379995151730159</v>
+        <v>-5.244148901238922</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.592939585070087</v>
+        <v>1.647278085266582</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.1935255257286317</v>
+        <v>-0.05767927523739302</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.62917875463872</v>
+        <v>3.710686504933463</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.537539223459601</v>
+        <v>-5.401692972968363</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.534043698605632</v>
+        <v>1.588382198802127</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.2604273308689062</v>
+        <v>-0.1245810803776675</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.593159413781876</v>
+        <v>3.674667164076619</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.815503619042874</v>
+        <v>-5.679657368551637</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.417935793108512</v>
+        <v>1.472274293305007</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.3500470651543905</v>
+        <v>-0.2142008146631518</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.534465425946775</v>
+        <v>3.615973176241519</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.932471311681765</v>
+        <v>-5.796625061190528</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.533352772752</v>
+        <v>1.587691272948495</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.3500470651543905</v>
+        <v>-0.2142008146631518</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.696669482645819</v>
+        <v>3.778177232940562</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-6.017189253902719</v>
+        <v>-5.881343003411481</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.494312233827433</v>
+        <v>1.548650734023928</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.4351630940824369</v>
+        <v>-0.2993168435911981</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.640446503252805</v>
+        <v>3.721954253547549</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.099124072171602</v>
+        <v>-5.963277821680364</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.47176772408837</v>
+        <v>1.526106224284866</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.445097839669517</v>
+        <v>-0.3092515891782783</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.644715073469049</v>
+        <v>3.726222823763792</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.201100194420009</v>
+        <v>-6.065253943928772</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.43990291364491</v>
+        <v>1.494241413841405</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.5470739619179246</v>
+        <v>-0.4112277114266859</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.592455038575907</v>
+        <v>3.67396278887065</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.091093910942788</v>
+        <v>-5.95524766045155</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.476058314279974</v>
+        <v>1.530396814476469</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.5238693900006494</v>
+        <v>-0.3880231395094107</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.598530668970447</v>
+        <v>3.68003841926519</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.948034335201863</v>
+        <v>-5.812188084710625</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.537532155298318</v>
+        <v>1.591870655494813</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.5158559634106701</v>
+        <v>-0.3800097129194314</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.607588735646409</v>
+        <v>3.689096485941152</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.646587609730025</v>
+        <v>-5.510741359238787</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.665371728369589</v>
+        <v>1.719710228566084</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.2144092379388328</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.795717653812047</v>
+        <v>3.87722540410679</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.671177853965209</v>
+        <v>-5.535331603473971</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.656506808428226</v>
+        <v>1.710845308624721</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.2144092379388328</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.796688831564758</v>
+        <v>3.878196581859501</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.620139477958689</v>
+        <v>-5.484293227467451</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.67776506321059</v>
+        <v>1.732103563407084</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.2144092379388328</v>
+        <v>-0.07856298744759416</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.797531735944513</v>
+        <v>3.879039486239256</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.579000183092058</v>
+        <v>-5.44315393260082</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.713258880031387</v>
+        <v>1.767597380227882</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.173269943072202</v>
+        <v>-0.03742369258096334</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.841253411738637</v>
+        <v>3.92276116203338</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.468394043012456</v>
+        <v>-5.332547792521218</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.573685332187163</v>
+        <v>1.628023832383658</v>
       </c>
       <c r="F2033" t="n">
-        <v>-0.06266380299259999</v>
+        <v>0.07318244749863867</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.723801091910333</v>
+        <v>3.805308842205076</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.598974777543298</v>
+        <v>-5.463128527052061</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.524955082448789</v>
+        <v>1.579293582645284</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.1932445375234425</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.648954695265791</v>
+        <v>3.730462445560534</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.434478443352337</v>
+        <v>-5.298632192861099</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.575180435201257</v>
+        <v>1.629518935397752</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.1932445375234425</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.633381514341874</v>
+        <v>3.714889264636617</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.309997962628385</v>
+        <v>-5.323794291635109</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.624160337927267</v>
+        <v>1.618641806324578</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.1932445375234425</v>
+        <v>-0.05739828703220384</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.632569224778303</v>
+        <v>3.714076975073046</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.320383157518275</v>
+        <v>-5.334179486524999</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.629875039096384</v>
+        <v>1.624356507493694</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.2036297324133318</v>
+        <v>-0.06778348192209316</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.636206886969442</v>
+        <v>3.717714637264185</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.338971316240499</v>
+        <v>-5.352767645247224</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.693276781383919</v>
+        <v>1.687758249781229</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.2222178911355572</v>
+        <v>-0.08637164064431851</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.695890997512532</v>
+        <v>3.777398747807275</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.348858012275107</v>
+        <v>-5.211050897432819</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.686191113788374</v>
+        <v>1.74131395972529</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.2222178911355572</v>
+        <v>-0.08637164064431851</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.692760008330831</v>
+        <v>3.774267758625574</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493994</v>
+        <v>3.815657372493996</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.248034878584679</v>
+        <v>-5.110227763742391</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.731051262203937</v>
+        <v>1.786174108140852</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.2097536756512033</v>
+        <v>-0.07390742515996468</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.704769432560834</v>
+        <v>3.786277182855577</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.742041699171672</v>
+        <v>3.731235814169421</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.67640782846521</v>
+        <v>3.730870360702844</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.248034878584679</v>
+        <v>-5.110227763742391</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.731051262203937</v>
+        <v>1.786174108140852</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.2097536756512033</v>
+        <v>-0.07390742515996468</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.669471625451578</v>
+        <v>3.723934157689211</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>126.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>450.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.6%</t>
+          <t>-640.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.6%</t>
+          <t>-153.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.6%</t>
+          <t>-185.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-259.1%</t>
+          <t>-262.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-117.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.4%</t>
+          <t>-218.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-158.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-60.4%</t>
         </is>
       </c>
     </row>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.119052324986328</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.119541463712203</v>
       </c>
     </row>
     <row r="1838">
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.041754512197421</v>
       </c>
     </row>
     <row r="1839">
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.076695596694964</v>
       </c>
     </row>
     <row r="1840">
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.587618356407115</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.108659710640092</v>
       </c>
     </row>
     <row r="1841">
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.933089671438995</v>
       </c>
     </row>
     <row r="1842">
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.934107280569465</v>
       </c>
     </row>
     <row r="1843">
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.924735312557221</v>
       </c>
     </row>
     <row r="1844">
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.931039382556141</v>
       </c>
     </row>
     <row r="1845">
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.935804699389843</v>
       </c>
     </row>
     <row r="1846">
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.405815606229521</v>
+        <v>1.368849131759997</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.962642922183679</v>
+        <v>3.940463037501964</v>
       </c>
     </row>
     <row r="1847">
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>0.9510951082131597</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.687737514878926</v>
       </c>
     </row>
     <row r="1848">
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.702052808321955</v>
       </c>
     </row>
     <row r="1849">
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.70694495287588</v>
       </c>
     </row>
     <row r="1850">
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.9129984917923695</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.664719362517286</v>
       </c>
     </row>
     <row r="1851">
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.5469297646477168</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.438162425536944</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.3384389831960324</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.333406246404702</v>
       </c>
     </row>
     <row r="1853">
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.3585923366948448</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.353597008912558</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.059272384141832</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.057814922954695</v>
       </c>
     </row>
     <row r="1856">
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.09752997149878867</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.081341678307589</v>
       </c>
     </row>
     <row r="1857">
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.953540670831634</v>
       </c>
     </row>
     <row r="1858">
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.955313597531894</v>
       </c>
     </row>
     <row r="1859">
@@ -44314,10 +44314,10 @@
         <v>1.303983001607965</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3578482136337294</v>
+        <v>-0.3948146881032535</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.909362605850546</v>
+        <v>2.887182721168832</v>
       </c>
     </row>
     <row r="1860">
@@ -44337,10 +44337,10 @@
         <v>1.198390178957035</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3515119464044743</v>
+        <v>-0.3884784208739983</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.90144914119019</v>
+        <v>2.879269256508476</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.062705711720819</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4194429318933791</v>
+        <v>-0.4564094063629031</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.859271141552813</v>
+        <v>2.837091256871098</v>
       </c>
     </row>
     <row r="1862">
@@ -44383,10 +44383,10 @@
         <v>1.038615539873912</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3389974227997172</v>
+        <v>-0.3759638972692412</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.914026007243251</v>
+        <v>2.891846122561537</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.8918191018242445</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6353082070987297</v>
+        <v>-0.6722746815682538</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.735494051669675</v>
+        <v>2.713314166987961</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7271451349667317</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.489102329376027</v>
+        <v>2.466922444694313</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.6768264026290467</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.484287761847487</v>
+        <v>2.462107877165773</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.508263703523125</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.482281812456365</v>
+        <v>2.460101927774651</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.374052942265009</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.492540503125044</v>
+        <v>2.47036061844333</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>0.2328490995534964</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.488640068270739</v>
+        <v>2.466460183589025</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>0.2119728927115596</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.043896984279408</v>
+        <v>-1.080863458748932</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.48704498832574</v>
+        <v>2.464865103644026</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.09708733191668895</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.112640120013287</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.449578082814621</v>
+        <v>2.427398198132907</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>0.01837314405856461</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.112640120013287</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.445551778280218</v>
+        <v>2.423371893598504</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.1349295127600714</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.112640120013287</v>
+        <v>-1.149606594482811</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.445449676958634</v>
+        <v>2.42326979227692</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>-0.1341525748691965</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.117126565214675</v>
+        <v>-1.154093039684199</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.445329325809231</v>
+        <v>2.423149441127517</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-0.2726144005727473</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.117126565214675</v>
+        <v>-1.154093039684199</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.450679629107281</v>
+        <v>2.428499744425567</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-0.2848380059972584</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.167475628668897</v>
+        <v>-1.204442103138421</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.428386210991925</v>
+        <v>2.406206326310211</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-0.3208439663440479</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.265094906090294</v>
+        <v>-1.302061380559818</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.372856395160856</v>
+        <v>2.350676510479142</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.3395790098258193</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.319166405598653</v>
+        <v>-1.356132880068178</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.343307051777413</v>
+        <v>2.321127167095698</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-0.4157690828391223</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.446805350212642</v>
+        <v>-1.483771824682167</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.272236882127662</v>
+        <v>2.250056997445947</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.4247476637580756</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.54721871812968</v>
+        <v>-1.584185192599204</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.216471415861875</v>
+        <v>2.194291531180161</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-0.379988029597675</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.473748886462231</v>
+        <v>-1.510715360931755</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.275925016355766</v>
+        <v>2.253745131674051</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44820,10 +44820,10 @@
         <v>-0.4354825758047758</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.648873303848775</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.185405586671356</v>
+        <v>2.163225701989642</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-0.5364825783121674</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.648873303848775</v>
+        <v>-1.685839778318299</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.17818642176976</v>
+        <v>2.156006537088046</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-0.5849046614967222</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.753248034875221</v>
+        <v>-1.790214509344745</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.108889392379917</v>
+        <v>2.086709507698202</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44889,10 +44889,10 @@
         <v>-0.6049033338982968</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.848923521457618</v>
+        <v>-1.885889995927142</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.052599890269034</v>
+        <v>2.03042000558732</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44912,10 +44912,10 @@
         <v>-0.6526243226164978</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.823671898647876</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.070444592583994</v>
+        <v>2.04826470790228</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44935,10 +44935,10 @@
         <v>-0.6258052781717245</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.823671898647876</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.074434928270396</v>
+        <v>2.052255043588681</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44958,10 +44958,10 @@
         <v>-0.6839492417601143</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.823671898647876</v>
+        <v>-1.8606383731174</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.072959701371654</v>
+        <v>2.050779816689939</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44981,10 +44981,10 @@
         <v>-0.6490594938253085</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.774081054223042</v>
+        <v>-1.811047528692566</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.117767618191427</v>
+        <v>2.095587733509712</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.6025432936832487</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.742831463487869</v>
+        <v>-1.779797937957393</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.123466238985847</v>
+        <v>2.101286354304133</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45027,10 +45027,10 @@
         <v>-0.5026261595592758</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.700904787900705</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.158201317374354</v>
+        <v>2.136021432692639</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45050,10 +45050,10 @@
         <v>-0.4516555524681802</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.700904787900705</v>
+        <v>-1.737871262370229</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.159340461930413</v>
+        <v>2.137160577248698</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45073,10 +45073,10 @@
         <v>-0.4701798935237873</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.695949441812259</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.164947443745588</v>
+        <v>2.142767559063874</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-0.4355929191699985</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.695949441812259</v>
+        <v>-1.732915916281783</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.170681147984225</v>
+        <v>2.14850126330251</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-0.4167836245200047</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.624583049202611</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.203763721156148</v>
+        <v>2.181583836474434</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-0.3892834922388224</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.624583049202611</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.193880239843241</v>
+        <v>2.171700355161526</v>
       </c>
     </row>
     <row r="1896">
@@ -45165,10 +45165,10 @@
         <v>-0.3868567801168235</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.624583049202611</v>
+        <v>-1.661549523672135</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.192045679343867</v>
+        <v>2.169865794662153</v>
       </c>
     </row>
     <row r="1897">
@@ -45188,10 +45188,10 @@
         <v>-0.3479942796196882</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.556597299342055</v>
+        <v>-1.593563773811579</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.23253681428674</v>
+        <v>2.210356929605025</v>
       </c>
     </row>
     <row r="1898">
@@ -45211,10 +45211,10 @@
         <v>-0.3377443570838112</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.532643758366097</v>
+        <v>-1.569610232835621</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.247577445017808</v>
+        <v>2.225397560336094</v>
       </c>
     </row>
     <row r="1899">
@@ -45234,10 +45234,10 @@
         <v>-0.2453806979164446</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.268583820043301</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.392753091849734</v>
+        <v>2.370573207168019</v>
       </c>
     </row>
     <row r="1900">
@@ -45257,10 +45257,10 @@
         <v>0.03466411782518986</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.268583820043301</v>
+        <v>-1.305550294512825</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.389966058189433</v>
+        <v>2.367786173507719</v>
       </c>
     </row>
     <row r="1901">
@@ -45280,10 +45280,10 @@
         <v>0.05108146105950739</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.22839952167711</v>
+        <v>-1.265365996146634</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.414420261096989</v>
+        <v>2.392240376415274</v>
       </c>
     </row>
     <row r="1902">
@@ -45303,10 +45303,10 @@
         <v>0.1158082306560093</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.064999650737747</v>
+        <v>-1.101966125207272</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.511827004881363</v>
+        <v>2.489647120199649</v>
       </c>
     </row>
     <row r="1903">
@@ -45326,10 +45326,10 @@
         <v>0.2171251483857009</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8315184285081489</v>
+        <v>-0.8684849029776731</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.659840167056975</v>
+        <v>2.63766028237526</v>
       </c>
     </row>
     <row r="1904">
@@ -45349,10 +45349,10 @@
         <v>0.274099494475748</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.738614937265613</v>
+        <v>-0.7755814117351372</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.712690051489537</v>
+        <v>2.690510166807822</v>
       </c>
     </row>
     <row r="1905">
@@ -45372,10 +45372,10 @@
         <v>0.3223771706751295</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6063394636347263</v>
+        <v>-0.6433059381042505</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.787422822415096</v>
+        <v>2.765242937733382</v>
       </c>
     </row>
     <row r="1906">
@@ -45395,10 +45395,10 @@
         <v>0.3874875643866629</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4506011310749848</v>
+        <v>-0.487567605544509</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.883680882638578</v>
+        <v>2.861500997956863</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>0.4999938250837541</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2016013323914041</v>
+        <v>-0.2385678068609283</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.045987103072385</v>
+        <v>3.023807218390671</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>0.3297818995752935</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3071913221645085</v>
+        <v>-0.3441577966340326</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.854657179609304</v>
+        <v>2.832477294927589</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>0.3708322806049411</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3127873318246397</v>
+        <v>-0.3497538062941639</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.899843915690311</v>
+        <v>2.877664031008597</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>0.3101293744798133</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2924664159160822</v>
+        <v>-0.3294328903856064</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.792157542547278</v>
+        <v>2.769977657865564</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>0.3226031971279304</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2394968936620933</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.815225269646193</v>
+        <v>2.793045384964479</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>0.3330619477411134</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2394968936620933</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.8082646575511</v>
+        <v>2.786084772869386</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>0.3608695847137642</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2394968936620933</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.822727011932243</v>
+        <v>2.800547127250529</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>0.3987053600219679</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2394968936620933</v>
+        <v>-0.2764633681316175</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.817259132391438</v>
+        <v>2.795079247709724</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>0.445519907959397</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1162057588449628</v>
+        <v>-0.153172233314487</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.888731907292294</v>
+        <v>2.866552022610579</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>0.4616805657580993</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09505655994151946</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.909122404871685</v>
+        <v>2.88694252018997</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.5549674508985278</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09505655994151946</v>
+        <v>-0.1320230344110436</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.904903113218735</v>
+        <v>2.882723228537021</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.5977968929294621</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.08183749154909076</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.914958868174208</v>
+        <v>2.892778983492494</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.6904791254927938</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.08183749154909076</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.907700943157911</v>
+        <v>2.885521058476196</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.7644350860004154</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.08183749154909076</v>
+        <v>-0.1188039660186149</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.911300066678559</v>
+        <v>2.889120181996845</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>0.8463411772639544</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.08960897147337238</v>
+        <v>0.05264249700384821</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.027495450546591</v>
+        <v>3.005315565864877</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>0.875077481175587</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1638985372117117</v>
+        <v>0.1269320627421875</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.071089667605892</v>
+        <v>3.048909782924177</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>0.9052265791234784</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2275342794456462</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.11396591400057</v>
+        <v>3.091786029318855</v>
       </c>
     </row>
     <row r="1924">
@@ -45809,10 +45809,10 @@
         <v>0.930991541637642</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2275342794456462</v>
+        <v>0.190567804976122</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.095160172784365</v>
+        <v>3.072980288102651</v>
       </c>
     </row>
     <row r="1925">
@@ -45832,10 +45832,10 @@
         <v>0.9285335690364036</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2170316563803573</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.090601675570069</v>
+        <v>3.068421790888355</v>
       </c>
     </row>
     <row r="1926">
@@ -45855,10 +45855,10 @@
         <v>0.9613599101397019</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2170316563803573</v>
+        <v>0.1800651819108331</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.094530989404889</v>
+        <v>3.072351104723175</v>
       </c>
     </row>
     <row r="1927">
@@ -45878,10 +45878,10 @@
         <v>0.9691239688081881</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2202129852772741</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.097118370660379</v>
+        <v>3.074938485978665</v>
       </c>
     </row>
     <row r="1928">
@@ -45901,10 +45901,10 @@
         <v>1.009643994220072</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2202129852772741</v>
+        <v>0.18324651080775</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.094116441880373</v>
+        <v>3.071936557198658</v>
       </c>
     </row>
     <row r="1929">
@@ -45924,10 +45924,10 @@
         <v>1.099231350445491</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3614328303452544</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.180427385931775</v>
+        <v>3.158247501250061</v>
       </c>
     </row>
     <row r="1930">
@@ -45947,10 +45947,10 @@
         <v>1.168272608872625</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3614328303452544</v>
+        <v>0.3244663558757302</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.196321568733599</v>
+        <v>3.174141684051884</v>
       </c>
     </row>
     <row r="1931">
@@ -45970,10 +45970,10 @@
         <v>1.217487686658726</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4816059137097533</v>
+        <v>0.4446394392402291</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.2695712631926</v>
+        <v>3.247391378510885</v>
       </c>
     </row>
     <row r="1932">
@@ -45993,10 +45993,10 @@
         <v>1.285444647260061</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6262780588094907</v>
+        <v>0.5893115843399666</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.366462652813882</v>
+        <v>3.344282768132168</v>
       </c>
     </row>
     <row r="1933">
@@ -46016,10 +46016,10 @@
         <v>1.24753220771841</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5664032314517986</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.316575247800693</v>
+        <v>3.294395363118978</v>
       </c>
     </row>
     <row r="1934">
@@ -46039,10 +46039,10 @@
         <v>1.310749469316953</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5664032314517986</v>
+        <v>0.5294367569822744</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.331864417034901</v>
+        <v>3.309684532353187</v>
       </c>
     </row>
     <row r="1935">
@@ -46062,10 +46062,10 @@
         <v>1.217405786054673</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5639335249899924</v>
+        <v>0.5269670505204682</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.238026792480259</v>
+        <v>3.215846907798545</v>
       </c>
     </row>
     <row r="1936">
@@ -46085,10 +46085,10 @@
         <v>1.10931957301037</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5732092240262073</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.162854073387289</v>
+        <v>3.140674188705575</v>
       </c>
     </row>
     <row r="1937">
@@ -46108,10 +46108,10 @@
         <v>1.094241060503442</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5732092240262073</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.153290782019181</v>
+        <v>3.131110897337466</v>
       </c>
     </row>
     <row r="1938">
@@ -46131,10 +46131,10 @@
         <v>1.209063866838609</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5732092240262073</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.290321618711383</v>
+        <v>3.268141734029669</v>
       </c>
     </row>
     <row r="1939">
@@ -46154,10 +46154,10 @@
         <v>1.283820802747385</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5732092240262073</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.294888850703171</v>
+        <v>3.272708966021456</v>
       </c>
     </row>
     <row r="1940">
@@ -46177,10 +46177,10 @@
         <v>1.215188330452092</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5732092240262073</v>
+        <v>0.5362427495566832</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.270630879464378</v>
+        <v>3.248450994782663</v>
       </c>
     </row>
     <row r="1941">
@@ -46200,10 +46200,10 @@
         <v>1.157192062042455</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6068727694984892</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.219367320149197</v>
+        <v>3.197187435467483</v>
       </c>
     </row>
     <row r="1942">
@@ -46223,10 +46223,10 @@
         <v>1.191305496156077</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6068727694984892</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.229539706581329</v>
+        <v>3.207359821899615</v>
       </c>
     </row>
     <row r="1943">
@@ -46246,10 +46246,10 @@
         <v>1.220749151940488</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6068727694984892</v>
+        <v>0.5699062950289651</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.22448597715519</v>
+        <v>3.202306092473475</v>
       </c>
     </row>
     <row r="1944">
@@ -46269,10 +46269,10 @@
         <v>1.194402199625421</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5660626064892584</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.191775654794176</v>
+        <v>3.169595770112462</v>
       </c>
     </row>
     <row r="1945">
@@ -46292,10 +46292,10 @@
         <v>1.183340830777603</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5660626064892584</v>
+        <v>0.5290961320197343</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.192327527827278</v>
+        <v>3.170147643145564</v>
       </c>
     </row>
     <row r="1946">
@@ -46315,10 +46315,10 @@
         <v>1.149737715249312</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6588730879401178</v>
+        <v>0.6219066134705936</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.177286508589159</v>
+        <v>3.155106623907445</v>
       </c>
     </row>
     <row r="1947">
@@ -46338,10 +46338,10 @@
         <v>1.133855403442142</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6144836186106901</v>
+        <v>0.577517144141166</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.152526302916104</v>
+        <v>3.130346418234389</v>
       </c>
     </row>
     <row r="1948">
@@ -46361,10 +46361,10 @@
         <v>1.082314469911728</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4979420135053474</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.077677048364621</v>
+        <v>3.055497163682907</v>
       </c>
     </row>
     <row r="1949">
@@ -46384,10 +46384,10 @@
         <v>1.132756566215464</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4979420135053474</v>
+        <v>0.4609755390358232</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.083168344195288</v>
+        <v>3.060988459513574</v>
       </c>
     </row>
     <row r="1950">
@@ -46407,10 +46407,10 @@
         <v>1.133141608823462</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4701616156039943</v>
+        <v>0.4331951411344701</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.077997307223015</v>
+        <v>3.055817422541301</v>
       </c>
     </row>
     <row r="1951">
@@ -46430,10 +46430,10 @@
         <v>0.9241450597320604</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4029437634530181</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.876022315933083</v>
+        <v>2.853842431251369</v>
       </c>
     </row>
     <row r="1952">
@@ -46453,10 +46453,10 @@
         <v>1.000849089073933</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4029437634530181</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.996171976652289</v>
+        <v>2.973992091970574</v>
       </c>
     </row>
     <row r="1953">
@@ -46476,10 +46476,10 @@
         <v>1.029525730475514</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4029437634530181</v>
+        <v>0.3659772889834939</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.010685002754612</v>
+        <v>2.988505118072897</v>
       </c>
     </row>
     <row r="1954">
@@ -46499,10 +46499,10 @@
         <v>1.042298636841143</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4413274260111693</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.031134641631871</v>
+        <v>3.008954756950156</v>
       </c>
     </row>
     <row r="1955">
@@ -46522,10 +46522,10 @@
         <v>1.109874197700511</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4413274260111693</v>
+        <v>0.4043609515416451</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.027863670477173</v>
+        <v>3.005683785795458</v>
       </c>
     </row>
     <row r="1956">
@@ -46545,10 +46545,10 @@
         <v>1.092520691529006</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3794313828417795</v>
+        <v>0.3424649083722553</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.991409436337452</v>
+        <v>2.969229551655738</v>
       </c>
     </row>
     <row r="1957">
@@ -46568,10 +46568,10 @@
         <v>1.158057835330927</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5362081410124981</v>
+        <v>0.499241666542974</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.079262466546298</v>
+        <v>3.057082581864583</v>
       </c>
     </row>
     <row r="1958">
@@ -46591,10 +46591,10 @@
         <v>1.120859605254275</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5058592456978935</v>
+        <v>0.4688927712283694</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.041860584689125</v>
+        <v>3.01968070000741</v>
       </c>
     </row>
     <row r="1959">
@@ -46614,10 +46614,10 @@
         <v>1.019749363484246</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.311496207654945</v>
+        <v>0.2745297331854208</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.930934324202301</v>
+        <v>2.908754439520587</v>
       </c>
     </row>
     <row r="1960">
@@ -46637,10 +46637,10 @@
         <v>0.9784741728058788</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2430873941096258</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.889092957971611</v>
+        <v>2.866913073289897</v>
       </c>
     </row>
     <row r="1961">
@@ -46660,10 +46660,10 @@
         <v>0.9786785210059206</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2430873941096258</v>
+        <v>0.2061209196401016</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.886692919525928</v>
+        <v>2.864513034844213</v>
       </c>
     </row>
     <row r="1962">
@@ -46683,10 +46683,10 @@
         <v>0.9828184912970845</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1849037827784312</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.848307471935456</v>
+        <v>2.826127587253742</v>
       </c>
     </row>
     <row r="1963">
@@ -46706,10 +46706,10 @@
         <v>1.089662240471027</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1849037827784312</v>
+        <v>0.1479373083089071</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.967601873569647</v>
+        <v>2.945421988887932</v>
       </c>
     </row>
     <row r="1964">
@@ -46729,10 +46729,10 @@
         <v>1.084948864923594</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1470458660446083</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.945720452515487</v>
+        <v>2.923540567833772</v>
       </c>
     </row>
     <row r="1965">
@@ -46752,10 +46752,10 @@
         <v>1.108879063936492</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1470458660446083</v>
+        <v>0.1100793915750841</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.951728982912412</v>
+        <v>2.929549098230698</v>
       </c>
     </row>
     <row r="1966">
@@ -46775,10 +46775,10 @@
         <v>1.065926473307692</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3148532232794914</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.950363618530542</v>
+        <v>2.928183733848827</v>
       </c>
     </row>
     <row r="1967">
@@ -46798,10 +46798,10 @@
         <v>1.035191606329294</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3148532232794914</v>
+        <v>0.2778867488099673</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.953157240062023</v>
+        <v>2.930977355380308</v>
       </c>
     </row>
     <row r="1968">
@@ -46821,10 +46821,10 @@
         <v>1.038315037142066</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3210059293322757</v>
+        <v>0.2840394548627516</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.957511212085352</v>
+        <v>2.935331327403637</v>
       </c>
     </row>
     <row r="1969">
@@ -46844,10 +46844,10 @@
         <v>1.030671794621975</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3041966311817741</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.946506109935161</v>
+        <v>2.924326225253446</v>
       </c>
     </row>
     <row r="1970">
@@ -46867,10 +46867,10 @@
         <v>1.121926547929245</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3041966311817741</v>
+        <v>0.2672301567122499</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.012841663731982</v>
+        <v>2.990661779050267</v>
       </c>
     </row>
     <row r="1971">
@@ -46890,10 +46890,10 @@
         <v>1.004934628709436</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5022148233509285</v>
+        <v>0.4652483488814043</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.933944580747601</v>
+        <v>2.911764696065887</v>
       </c>
     </row>
     <row r="1972">
@@ -46913,10 +46913,10 @@
         <v>1.054870175957133</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4513281106647339</v>
+        <v>0.4143616361952098</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.97370278545806</v>
+        <v>2.951522900776345</v>
       </c>
     </row>
     <row r="1973">
@@ -46936,10 +46936,10 @@
         <v>1.030401694223187</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4354388325317538</v>
+        <v>0.3984723580622296</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.978796954694316</v>
+        <v>2.956617070012601</v>
       </c>
     </row>
     <row r="1974">
@@ -46959,10 +46959,10 @@
         <v>1.004853955845745</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3752295345264692</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.941207356715816</v>
+        <v>2.919027472034102</v>
       </c>
     </row>
     <row r="1975">
@@ -46982,10 +46982,10 @@
         <v>1.033914392458444</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3752295345264692</v>
+        <v>0.3382630600569451</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.939698974755745</v>
+        <v>2.91751909007403</v>
       </c>
     </row>
     <row r="1976">
@@ -47005,10 +47005,10 @@
         <v>1.051526512549307</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4196026661650378</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.966185721174322</v>
+        <v>2.944005836492608</v>
       </c>
     </row>
     <row r="1977">
@@ -47028,10 +47028,10 @@
         <v>1.036928166344344</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4196026661650378</v>
+        <v>0.3826361916955137</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.960579515312913</v>
+        <v>2.938399630631198</v>
       </c>
     </row>
     <row r="1978">
@@ -47051,10 +47051,10 @@
         <v>1.062372215596571</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4672583967260935</v>
+        <v>0.4302919222565693</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.995554710677351</v>
+        <v>2.973374825995637</v>
       </c>
     </row>
     <row r="1979">
@@ -47074,10 +47074,10 @@
         <v>1.107471852370798</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.567776555224848</v>
+        <v>0.5308100807553239</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.060757979151328</v>
+        <v>3.038578094469614</v>
       </c>
     </row>
     <row r="1980">
@@ -47097,10 +47097,10 @@
         <v>1.069959888685714</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4860782385063144</v>
+        <v>0.4491117640367902</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.99849366159608</v>
+        <v>2.976313776914366</v>
       </c>
     </row>
     <row r="1981">
@@ -47120,10 +47120,10 @@
         <v>1.091992951939702</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4906216714511838</v>
+        <v>0.4536551969816597</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.005317423973631</v>
+        <v>2.983137539291916</v>
       </c>
     </row>
     <row r="1982">
@@ -47143,10 +47143,10 @@
         <v>1.088354509073977</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4425370301712795</v>
+        <v>0.4055705557017554</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.980627578836766</v>
+        <v>2.958447694155052</v>
       </c>
     </row>
     <row r="1983">
@@ -47166,10 +47166,10 @@
         <v>1.111915246436174</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.48673986725718</v>
+        <v>0.4497733927876558</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.013028883616144</v>
+        <v>2.990848998934429</v>
       </c>
     </row>
     <row r="1984">
@@ -47189,10 +47189,10 @@
         <v>1.095533635840044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5237137690485105</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.03362322516019</v>
+        <v>3.011443340478475</v>
       </c>
     </row>
     <row r="1985">
@@ -47212,10 +47212,10 @@
         <v>1.210097968038793</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5237137690485105</v>
+        <v>0.4867472945789864</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.084870990343229</v>
+        <v>3.062691105661515</v>
       </c>
     </row>
     <row r="1986">
@@ -47235,10 +47235,10 @@
         <v>1.291595474086837</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7313557726829867</v>
+        <v>0.6943892982134625</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.207896897118168</v>
+        <v>3.185717012436454</v>
       </c>
     </row>
     <row r="1987">
@@ -47258,10 +47258,10 @@
         <v>1.306956539414118</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7823878654055146</v>
+        <v>0.7454213909359905</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.233464380989955</v>
+        <v>3.21128449630824</v>
       </c>
     </row>
     <row r="1988">
@@ -47281,10 +47281,10 @@
         <v>1.350233615957705</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8476120465327203</v>
+        <v>0.8106455720631961</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.289786293758983</v>
+        <v>3.267606409077268</v>
       </c>
     </row>
     <row r="1989">
@@ -47304,10 +47304,10 @@
         <v>1.361165396285439</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8528635845619019</v>
+        <v>0.8158971100923778</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.288898188875772</v>
+        <v>3.266718304194058</v>
       </c>
     </row>
     <row r="1990">
@@ -47327,10 +47327,10 @@
         <v>1.354377526202796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8638909295593211</v>
+        <v>0.826924455089797</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.296771388205464</v>
+        <v>3.27459150352375</v>
       </c>
     </row>
     <row r="1991">
@@ -47350,10 +47350,10 @@
         <v>1.536433222994889</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8739542389997831</v>
+        <v>0.8369877645302589</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.463367144890952</v>
+        <v>3.441187260209237</v>
       </c>
     </row>
     <row r="1992">
@@ -47373,10 +47373,10 @@
         <v>1.686459036622711</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.628349410723777</v>
+        <v>3.606169526042062</v>
       </c>
     </row>
     <row r="1993">
@@ -47396,10 +47396,10 @@
         <v>1.688600646342093</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9487365000247957</v>
+        <v>0.9117700255552715</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.620057386737636</v>
+        <v>3.597877502055921</v>
       </c>
     </row>
     <row r="1994">
@@ -47419,10 +47419,10 @@
         <v>1.718046314265451</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.02291331090848</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.662756668851626</v>
+        <v>3.640576784169911</v>
       </c>
     </row>
     <row r="1995">
@@ -47442,10 +47442,10 @@
         <v>1.739157704549556</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.02291331090848</v>
+        <v>0.9859468364389561</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.680311074578417</v>
+        <v>3.658131189896703</v>
       </c>
     </row>
     <row r="1996">
@@ -47465,10 +47465,10 @@
         <v>1.663622305166189</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9949654751918995</v>
+        <v>0.9579990007223753</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655397420553053</v>
+        <v>3.633217535871339</v>
       </c>
     </row>
     <row r="1997">
@@ -47488,10 +47488,10 @@
         <v>1.924011813898684</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.594458282118668</v>
+        <v>3.572278397436954</v>
       </c>
     </row>
     <row r="1998">
@@ -47511,10 +47511,10 @@
         <v>1.92376427786885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9246174158214888</v>
+        <v>0.8876509413519647</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.585122304615573</v>
+        <v>3.562942419933858</v>
       </c>
     </row>
     <row r="1999">
@@ -47534,10 +47534,10 @@
         <v>2.030989678402402</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7954156025274466</v>
+        <v>0.7584491280579224</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.666507342490317</v>
+        <v>3.644327457808602</v>
       </c>
     </row>
     <row r="2000">
@@ -47557,10 +47557,10 @@
         <v>2.006155098184746</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7620479284729704</v>
+        <v>0.7250814540034463</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.683564560551277</v>
+        <v>3.661384675869563</v>
       </c>
     </row>
     <row r="2001">
@@ -47580,10 +47580,10 @@
         <v>2.00565233026036</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7691026186881442</v>
+        <v>0.7321361442186201</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.684472730669927</v>
+        <v>3.662292845988212</v>
       </c>
     </row>
     <row r="2002">
@@ -47603,10 +47603,10 @@
         <v>2.026438973635697</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.7034070919313</v>
+        <v>3.681227207249585</v>
       </c>
     </row>
     <row r="2003">
@@ -47626,10 +47626,10 @@
         <v>2.15616090255813</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.88751022407626</v>
+        <v>3.865330339394545</v>
       </c>
     </row>
     <row r="2004">
@@ -47649,10 +47649,10 @@
         <v>2.139314350339175</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7839829647158634</v>
+        <v>0.7470164902463392</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.879626918979253</v>
+        <v>3.857447034297538</v>
       </c>
     </row>
     <row r="2005">
@@ -47672,10 +47672,10 @@
         <v>2.082166042897052</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6972559558523219</v>
+        <v>0.6602894813827977</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.829644713210765</v>
+        <v>3.807464828529051</v>
       </c>
     </row>
     <row r="2006">
@@ -47695,10 +47695,10 @@
         <v>2.134643390263487</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8196830733957133</v>
+        <v>0.7827165989261892</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.959354701458647</v>
+        <v>3.937174816776933</v>
       </c>
     </row>
     <row r="2007">
@@ -47718,10 +47718,10 @@
         <v>2.116625041874532</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.930881631602563</v>
+        <v>3.908701746920849</v>
       </c>
     </row>
     <row r="2008">
@@ -47741,10 +47741,10 @@
         <v>2.084204863727945</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7674094660600721</v>
+        <v>0.7304429915905479</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.928993444496339</v>
+        <v>3.906813559814624</v>
       </c>
     </row>
     <row r="2009">
@@ -47764,10 +47764,10 @@
         <v>1.998123605201066</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5651557457357186</v>
+        <v>0.5281892712661944</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.802461441904589</v>
+        <v>3.780281557222875</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.46180200467331</v>
@@ -47787,10 +47787,10 @@
         <v>1.931930245200316</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.724825697836013</v>
+        <v>3.702645813154299</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.95608962999567</v>
+        <v>-3.993441058337615</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.892083135227213</v>
+        <v>1.877142563890435</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.737899104701932</v>
+        <v>3.715719220020218</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.95765127281053</v>
+        <v>-3.995002701152475</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.891458478101269</v>
+        <v>1.876517906764491</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4383728219378392</v>
+        <v>0.4014063474683151</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.737899104701932</v>
+        <v>3.715719220020218</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.985552059920003</v>
+        <v>-4.022903488261948</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.878822204384482</v>
+        <v>1.863881633047704</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4037758977949044</v>
+        <v>0.3668094233253802</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.715664991343173</v>
+        <v>3.693485106661459</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.108078162622897</v>
+        <v>-4.145429590964842</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.826576207280523</v>
+        <v>1.811635635943745</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2812497950920105</v>
+        <v>0.2442833206224864</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.638913773698636</v>
+        <v>3.616733889016921</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.338592658808486</v>
+        <v>-4.37594408715043</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.801076368396791</v>
+        <v>1.786135797060013</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.05073529890642181</v>
+        <v>0.01376882443689764</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.567311035577786</v>
+        <v>3.545131150896072</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.595313476803311</v>
+        <v>-4.632664905145255</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.838699760200708</v>
+        <v>1.823759188863931</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.642574010093345</v>
+        <v>3.62039412541163</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.749299894579451</v>
+        <v>-4.786651322921395</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.846085462235892</v>
+        <v>1.831144890899114</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.711554279238984</v>
+        <v>3.68937439455727</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.698777990751785</v>
+        <v>-4.73612941909373</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.852345425887079</v>
+        <v>1.837404854550301</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.697605481359105</v>
+        <v>3.675425596677391</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.95125314475951</v>
+        <v>-4.988604573101454</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.763225853339403</v>
+        <v>1.748285282002626</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.709475970414519</v>
+        <v>3.687296085732805</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.244148901238922</v>
+        <v>-5.281500329580866</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.647278085266582</v>
+        <v>1.632337513929805</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.05767927523739302</v>
+        <v>-0.09464574970691719</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.710686504933463</v>
+        <v>3.688506620251748</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.401692972968363</v>
+        <v>-5.439044401310308</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.588382198802127</v>
+        <v>1.573441627465349</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1245810803776675</v>
+        <v>-0.1615475548471917</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.674667164076619</v>
+        <v>3.652487279394905</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.679657368551637</v>
+        <v>-5.717008796893581</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.472274293305007</v>
+        <v>1.457333721968229</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2511672891326759</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.615973176241519</v>
+        <v>3.593793291559804</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.796625061190528</v>
+        <v>-5.833976489532472</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.587691272948495</v>
+        <v>1.572750701611717</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2142008146631518</v>
+        <v>-0.2511672891326759</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.778177232940562</v>
+        <v>3.755997348258848</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.881343003411481</v>
+        <v>-5.918694431753425</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.548650734023928</v>
+        <v>1.53371016268715</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.2993168435911981</v>
+        <v>-0.3362833180607223</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.721954253547549</v>
+        <v>3.699774368865834</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.963277821680364</v>
+        <v>-6.000629250022309</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.526106224284866</v>
+        <v>1.511165652948088</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3092515891782783</v>
+        <v>-0.3462180636478025</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.726222823763792</v>
+        <v>3.704042939082077</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.065253943928772</v>
+        <v>-6.102605372270716</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.494241413841405</v>
+        <v>1.479300842504627</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4112277114266859</v>
+        <v>-0.4481941858962101</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.67396278887065</v>
+        <v>3.651782904188935</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.95524766045155</v>
+        <v>-5.992599088793495</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.530396814476469</v>
+        <v>1.515456243139691</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.3880231395094107</v>
+        <v>-0.4249896139789349</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.68003841926519</v>
+        <v>3.657858534583476</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.812188084710625</v>
+        <v>-5.849539513052569</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.591870655494813</v>
+        <v>1.576930084158036</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.3800097129194314</v>
+        <v>-0.4169761873889556</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.689096485941152</v>
+        <v>3.666916601259437</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436925</v>
+        <v>3.777251572436924</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.510741359238787</v>
+        <v>-5.548092787580732</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.719710228566084</v>
+        <v>1.704769657229307</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.87722540410679</v>
+        <v>3.855045519425076</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064763</v>
+        <v>3.812650101064762</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.535331603473971</v>
+        <v>-5.572683031815916</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.710845308624721</v>
+        <v>1.695904737287943</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.878196581859501</v>
+        <v>3.856016697177786</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859297</v>
+        <v>3.821198342859295</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.484293227467451</v>
+        <v>-5.521644655809395</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.732103563407084</v>
+        <v>1.717162992070307</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.07856298744759416</v>
+        <v>-0.1155294619171183</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.879039486239256</v>
+        <v>3.856859601557542</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354681</v>
+        <v>3.831748677354679</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.44315393260082</v>
+        <v>-5.480505360942765</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.767597380227882</v>
+        <v>1.752656808891105</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.03742369258096334</v>
+        <v>-0.07439016705048751</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.92276116203338</v>
+        <v>3.900581277351665</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085616</v>
+        <v>3.825767093085615</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.332547792521218</v>
+        <v>-5.369899220863163</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.628023832383658</v>
+        <v>1.61308326104688</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.07318244749863867</v>
+        <v>0.0362159730291145</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.805308842205076</v>
+        <v>3.783128957523362</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462778</v>
+        <v>3.804703121462777</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.463128527052061</v>
+        <v>-5.500479955394005</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.579293582645284</v>
+        <v>1.564353011308507</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.730462445560534</v>
+        <v>3.708282560878819</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218596</v>
+        <v>3.775043021218594</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.298632192861099</v>
+        <v>-5.335983621203043</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.629518935397752</v>
+        <v>1.614578364060974</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.714889264636617</v>
+        <v>3.692709379954902</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462765</v>
+        <v>3.821044820462763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.323794291635109</v>
+        <v>-5.211503140479092</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.618641806324578</v>
+        <v>1.663558266786984</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.05739828703220384</v>
+        <v>-0.09436476150172801</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.714076975073046</v>
+        <v>3.691897090391332</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533047</v>
+        <v>3.832321184533045</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.334179486524999</v>
+        <v>-5.221888335368981</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.624356507493694</v>
+        <v>1.669272967956101</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.06778348192209316</v>
+        <v>-0.1047499563916173</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.717714637264185</v>
+        <v>3.695534752582471</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120421</v>
+        <v>3.834429654120419</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.352767645247224</v>
+        <v>-5.240476494091206</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.687758249781229</v>
+        <v>1.732674710243636</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.1233381151138427</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.777398747807275</v>
+        <v>3.755218863125561</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855134695881691</v>
+        <v>3.85513469588169</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.211050897432819</v>
+        <v>-5.098759746276802</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.74131395972529</v>
+        <v>1.786230420187696</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.08637164064431851</v>
+        <v>-0.1233381151138427</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.774267758625574</v>
+        <v>3.752087873943859</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493996</v>
+        <v>3.815657372493993</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.110227763742391</v>
+        <v>-4.997936612586374</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.786174108140852</v>
+        <v>1.831090568603259</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.07390742515996468</v>
+        <v>-0.1108738996294888</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.786277182855577</v>
+        <v>3.764097298173863</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.731235814169421</v>
+        <v>3.478283254493697</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.730870360702844</v>
+        <v>3.822494961960489</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.110227763742391</v>
+        <v>-4.785512594056867</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.786174108140852</v>
+        <v>1.907933500023995</v>
       </c>
       <c r="F2041" t="n">
-        <v>-0.07390742515996468</v>
+        <v>0.0561027964782797</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.723934157689211</v>
+        <v>3.856156639847457</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240730.xlsx
+++ b/tame_output/ON/bt/strategyON_20240730.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.7%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>450.5%</t>
+          <t>454.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-640.1%</t>
+          <t>-677.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-153.4%</t>
+          <t>-154.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-185.4%</t>
+          <t>-205.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-262.8%</t>
+          <t>-259.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-117.7%</t>
+          <t>157.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-218.4%</t>
+          <t>-218.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-60.4%</t>
+          <t>-65.3%</t>
         </is>
       </c>
     </row>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.119052324986328</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.119541463712203</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.041754512197421</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.076695596694964</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.587618356407115</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.108659710640092</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.933089671438995</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.934107280569465</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.924735312557221</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.931039382556141</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.935804699389843</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.368849131759997</v>
+        <v>1.405815606229521</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940463037501964</v>
+        <v>3.962642922183679</v>
       </c>
     </row>
     <row r="1847">
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9510951082131597</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.687737514878926</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.702052808321955</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.70694495287588</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9129984917923695</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.664719362517286</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5469297646477168</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.438162425536944</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3384389831960324</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.333406246404702</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3585923366948448</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.353597008912558</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.059272384141832</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.057814922954695</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.09752997149878867</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.081341678307589</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.953540670831634</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.955313597531894</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44314,10 +44314,10 @@
         <v>1.303983001607965</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.3948146881032535</v>
+        <v>-0.3578482136337294</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.887182721168832</v>
+        <v>2.909362605850546</v>
       </c>
     </row>
     <row r="1860">
@@ -44337,10 +44337,10 @@
         <v>1.198390178957035</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3884784208739983</v>
+        <v>-0.3515119464044743</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.879269256508476</v>
+        <v>2.90144914119019</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.062705711720819</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4564094063629031</v>
+        <v>-0.4194429318933791</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.837091256871098</v>
+        <v>2.859271141552813</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>1.038615539873912</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3759638972692412</v>
+        <v>-0.3389974227997172</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.891846122561537</v>
+        <v>2.914026007243251</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.8918191018242445</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6722746815682538</v>
+        <v>-0.6353082070987297</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713314166987961</v>
+        <v>2.735494051669675</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.7271451349667317</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.466922444694313</v>
+        <v>2.489102329376027</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.6768264026290467</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462107877165773</v>
+        <v>2.484287761847487</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.508263703523125</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460101927774651</v>
+        <v>2.482281812456365</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>0.374052942265009</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.47036061844333</v>
+        <v>2.492540503125044</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.2328490995534964</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466460183589025</v>
+        <v>2.488640068270739</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>0.2119728927115596</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080863458748932</v>
+        <v>-1.043896984279408</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.464865103644026</v>
+        <v>2.48704498832574</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>0.09708733191668895</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.149606594482811</v>
+        <v>-1.112640120013287</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.427398198132907</v>
+        <v>2.449578082814621</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>0.01837314405856461</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.149606594482811</v>
+        <v>-1.112640120013287</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.423371893598504</v>
+        <v>2.445551778280218</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.1349295127600714</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.149606594482811</v>
+        <v>-1.112640120013287</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.42326979227692</v>
+        <v>2.445449676958634</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.1341525748691965</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.154093039684199</v>
+        <v>-1.117126565214675</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.423149441127517</v>
+        <v>2.445329325809231</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.2726144005727473</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.154093039684199</v>
+        <v>-1.117126565214675</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.428499744425567</v>
+        <v>2.450679629107281</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.2848380059972584</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.204442103138421</v>
+        <v>-1.167475628668897</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.406206326310211</v>
+        <v>2.428386210991925</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.3208439663440479</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.302061380559818</v>
+        <v>-1.265094906090294</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.350676510479142</v>
+        <v>2.372856395160856</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.3395790098258193</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.356132880068178</v>
+        <v>-1.319166405598653</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.321127167095698</v>
+        <v>2.343307051777413</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44751,10 +44751,10 @@
         <v>-0.4157690828391223</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.483771824682167</v>
+        <v>-1.446805350212642</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.250056997445947</v>
+        <v>2.272236882127662</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-0.4247476637580756</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.584185192599204</v>
+        <v>-1.54721871812968</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.194291531180161</v>
+        <v>2.216471415861875</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44797,10 +44797,10 @@
         <v>-0.379988029597675</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.510715360931755</v>
+        <v>-1.473748886462231</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.253745131674051</v>
+        <v>2.275925016355766</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-0.4354825758047758</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.685839778318299</v>
+        <v>-1.648873303848775</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.163225701989642</v>
+        <v>2.185405586671356</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44843,10 +44843,10 @@
         <v>-0.5364825783121674</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.685839778318299</v>
+        <v>-1.648873303848775</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.156006537088046</v>
+        <v>2.17818642176976</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44866,10 +44866,10 @@
         <v>-0.5849046614967222</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.790214509344745</v>
+        <v>-1.753248034875221</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.086709507698202</v>
+        <v>2.108889392379917</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-0.6049033338982968</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.885889995927142</v>
+        <v>-1.848923521457618</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.03042000558732</v>
+        <v>2.052599890269034</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-0.6526243226164978</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.823671898647876</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.04826470790228</v>
+        <v>2.070444592583994</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-0.6258052781717245</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.823671898647876</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.052255043588681</v>
+        <v>2.074434928270396</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-0.6839492417601143</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.8606383731174</v>
+        <v>-1.823671898647876</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.050779816689939</v>
+        <v>2.072959701371654</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-0.6490594938253085</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.811047528692566</v>
+        <v>-1.774081054223042</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.095587733509712</v>
+        <v>2.117767618191427</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-0.6025432936832487</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.779797937957393</v>
+        <v>-1.742831463487869</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.101286354304133</v>
+        <v>2.123466238985847</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-0.5026261595592758</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.737871262370229</v>
+        <v>-1.700904787900705</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.136021432692639</v>
+        <v>2.158201317374354</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-0.4516555524681802</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.737871262370229</v>
+        <v>-1.700904787900705</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.137160577248698</v>
+        <v>2.159340461930413</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.130851445107458</v>
+        <v>-9.09766619688855</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4701798935237873</v>
+        <v>-0.4569057942362242</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.732915916281783</v>
+        <v>-1.685997652713371</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.142767559063874</v>
+        <v>2.170918517204921</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.058718269819577</v>
+        <v>-9.025533021600669</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4355929191699985</v>
+        <v>-0.422318819882435</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.732915916281783</v>
+        <v>-1.685997652713371</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14850126330251</v>
+        <v>2.176652221443558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.98735187720993</v>
+        <v>-8.954166628991022</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4167836245200047</v>
+        <v>-0.4035095252324412</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.614631260103723</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.181583836474434</v>
+        <v>2.209734794615481</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.893892843224705</v>
+        <v>-8.860707595005797</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3892834922388224</v>
+        <v>-0.3760093929512593</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.614631260103723</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.171700355161526</v>
+        <v>2.199851313302573</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.883239661671274</v>
+        <v>-8.850054413452366</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3868567801168235</v>
+        <v>-0.3735826808292604</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.661549523672135</v>
+        <v>-1.614631260103723</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.169865794662153</v>
+        <v>2.1980167528032</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.785332622994783</v>
+        <v>-8.752147374775875</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3479942796196882</v>
+        <v>-0.3347201803321247</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.593563773811579</v>
+        <v>-1.546645510243167</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.210356929605025</v>
+        <v>2.238507887746072</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.761379082018825</v>
+        <v>-8.728193833799917</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3377443570838112</v>
+        <v>-0.3244702577962482</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.569610232835621</v>
+        <v>-1.522691969267209</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.225397560336094</v>
+        <v>2.253548518477141</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.497319143696028</v>
+        <v>-8.46413389547712</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2453806979164446</v>
+        <v>-0.2321065986288815</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.305550294512825</v>
+        <v>-1.258632030944413</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.370573207168019</v>
+        <v>2.398724165309067</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.79023952019119</v>
+        <v>-7.757054271972282</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.03466411782518986</v>
+        <v>0.04793821711275292</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.305550294512825</v>
+        <v>-1.258632030944413</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.367786173507719</v>
+        <v>2.395937131648766</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.750055221825</v>
+        <v>-7.716869973606092</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.05108146105950739</v>
+        <v>0.06435556034707046</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.265365996146634</v>
+        <v>-1.218447732578222</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.392240376415274</v>
+        <v>2.420391334556321</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.586655350885637</v>
+        <v>-7.553470102666729</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1158082306560093</v>
+        <v>0.1290823299435724</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.101966125207272</v>
+        <v>-1.05504786163886</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.489647120199649</v>
+        <v>2.517798078340696</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.353174128656039</v>
+        <v>-7.319988880437131</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2171251483857009</v>
+        <v>0.2303992476732644</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8684849029776731</v>
+        <v>-0.8215666394092613</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.63766028237526</v>
+        <v>2.665811240516307</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.203507737648524</v>
+        <v>-7.170322489429616</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.274099494475748</v>
+        <v>0.2873735937633111</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7755814117351372</v>
+        <v>-0.7286631481667254</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.690510166807822</v>
+        <v>2.71866112494887</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.071232264017637</v>
+        <v>-7.038047015798729</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3223771706751295</v>
+        <v>0.3356512699626926</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6433059381042505</v>
+        <v>-0.5963876745358387</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.765242937733382</v>
+        <v>2.793393895874429</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.915493931457895</v>
+        <v>-6.882308683238987</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3874875643866629</v>
+        <v>0.4007616636742259</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.487567605544509</v>
+        <v>-0.4406493419760972</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.861500997956863</v>
+        <v>2.88965195609791</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.666494132774314</v>
+        <v>-6.633308884555406</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4999938250837541</v>
+        <v>0.5132679243713172</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2385678068609283</v>
+        <v>-0.1916495432925165</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.023807218390671</v>
+        <v>3.051958176531718</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.772084122547419</v>
+        <v>-6.738898874328511</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3297818995752935</v>
+        <v>0.343055998862857</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3441577966340326</v>
+        <v>-0.2972395330656208</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.832477294927589</v>
+        <v>2.860628253068636</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.790819024666016</v>
+        <v>-6.757633776447108</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3708322806049411</v>
+        <v>0.3841063798925042</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3497538062941639</v>
+        <v>-0.3028355427257521</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.877664031008597</v>
+        <v>2.905814989149644</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.642878983258417</v>
+        <v>-6.609693735039508</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3101293744798133</v>
+        <v>0.3234034737673763</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3294328903856064</v>
+        <v>-0.2825146268171946</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769977657865564</v>
+        <v>2.798128616006611</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.589909461004428</v>
+        <v>-6.55672421278552</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3226031971279304</v>
+        <v>0.3358772964154939</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.2295451045632057</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793045384964479</v>
+        <v>2.821196343105526</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.546361054233738</v>
+        <v>-6.513175806014829</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3330619477411134</v>
+        <v>0.3463360470286769</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.2295451045632057</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786084772869386</v>
+        <v>2.814235731010433</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.512997847754969</v>
+        <v>-6.479812599536061</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3608695847137642</v>
+        <v>0.3741436840013272</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.2295451045632057</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800547127250529</v>
+        <v>2.828698085391576</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.404738710632447</v>
+        <v>-6.371553462413539</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3987053600219679</v>
+        <v>0.4119794593095309</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2764633681316175</v>
+        <v>-0.2295451045632057</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795079247709724</v>
+        <v>2.823230205850771</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.281447575815316</v>
+        <v>-6.248262327596408</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.445519907959397</v>
+        <v>0.4587940072469601</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.153172233314487</v>
+        <v>-0.1062539697460752</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866552022610579</v>
+        <v>2.894702980751626</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.260298376911873</v>
+        <v>-6.227113128692965</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4616805657580993</v>
+        <v>0.4749546650456629</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1320230344110436</v>
+        <v>-0.08510477084263185</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.88694252018997</v>
+        <v>2.915093478331017</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.016532934928429</v>
+        <v>-5.983347686709521</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5549674508985278</v>
+        <v>0.5682415501860913</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1320230344110436</v>
+        <v>-0.08510477084263185</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.882723228537021</v>
+        <v>2.910874186678068</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.914770114651134</v>
+        <v>-5.881584866432226</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5977968929294621</v>
+        <v>0.6110709922170252</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.07188570245020315</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.892778983492494</v>
+        <v>2.920929941633541</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.664919720702059</v>
+        <v>-5.631734472483151</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6904791254927938</v>
+        <v>0.7037532247803573</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.07188570245020315</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.885521058476196</v>
+        <v>2.913672016617243</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.489027628234627</v>
+        <v>-5.455842380015719</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7644350860004154</v>
+        <v>0.7777091852879789</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1188039660186149</v>
+        <v>-0.07188570245020315</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.889120181996845</v>
+        <v>2.917271140137892</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.317581165212164</v>
+        <v>-5.284395916993256</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8463411772639544</v>
+        <v>0.8596152765515179</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.05264249700384821</v>
+        <v>0.09956076057225999</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.005315565864877</v>
+        <v>3.033466524005924</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.243291599473825</v>
+        <v>-5.210106351254916</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.875077481175587</v>
+        <v>0.8883515804631505</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1269320627421875</v>
+        <v>0.1738503263105993</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.048909782924177</v>
+        <v>3.077060741065224</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.17965585723989</v>
+        <v>-5.146470609020982</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9052265791234784</v>
+        <v>0.9185006784110414</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.190567804976122</v>
+        <v>0.2374860685445338</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.091786029318855</v>
+        <v>3.119936987459902</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.06822909791397</v>
+        <v>-5.035043849695062</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.930991541637642</v>
+        <v>0.944265640925205</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.190567804976122</v>
+        <v>0.2374860685445338</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.072980288102651</v>
+        <v>3.101131246243698</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.078731720979259</v>
+        <v>-5.045546472760351</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9285335690364036</v>
+        <v>0.9418076683239671</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1800651819108331</v>
+        <v>0.2269834454792449</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.068421790888355</v>
+        <v>3.096572749029402</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.006489152808064</v>
+        <v>-4.973303904589156</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9613599101397019</v>
+        <v>0.9746340094272652</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1800651819108331</v>
+        <v>0.2269834454792449</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.072351104723175</v>
+        <v>3.100502062864222</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.988775465930199</v>
+        <v>-4.955590217711291</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9691239688081881</v>
+        <v>0.9823980680957511</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.18324651080775</v>
+        <v>0.2301647743761617</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.074938485978665</v>
+        <v>3.103089444119712</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.879970580450472</v>
+        <v>-4.917748391286902</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.009643994220072</v>
+        <v>0.9945328698855003</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.18324651080775</v>
+        <v>0.2301647743761617</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.071936557198658</v>
+        <v>3.100087515339705</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.659949782413461</v>
+        <v>-4.697727593249891</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.099231350445491</v>
+        <v>1.084120226110919</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3244663558757302</v>
+        <v>0.371384619444142</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.158247501250061</v>
+        <v>3.186398459391108</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.527082093350184</v>
+        <v>-4.564859904186614</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.168272608872625</v>
+        <v>1.153161484538053</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3244663558757302</v>
+        <v>0.371384619444142</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.174141684051884</v>
+        <v>3.202292642192931</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.406909009985685</v>
+        <v>-4.444686820822115</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.217487686658726</v>
+        <v>1.202376562324154</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4446394392402291</v>
+        <v>0.4915577028086409</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.247391378510885</v>
+        <v>3.275542336651932</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.262236864885947</v>
+        <v>-4.300014675722378</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.285444647260061</v>
+        <v>1.270333522925489</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5893115843399666</v>
+        <v>0.6362298479083783</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.344282768132168</v>
+        <v>3.372433726273215</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.32211169224364</v>
+        <v>-4.35988950308007</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24753220771841</v>
+        <v>1.232421083383838</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5294367569822744</v>
+        <v>0.5763550205506862</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.294395363118978</v>
+        <v>3.322546321260025</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.202291461332803</v>
+        <v>-4.240069272169233</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.310749469316953</v>
+        <v>1.295638344982381</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5294367569822744</v>
+        <v>0.5763550205506862</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.309684532353187</v>
+        <v>3.337835490494234</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.204761167794609</v>
+        <v>-4.242538978631039</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.217405786054673</v>
+        <v>1.2022946617201</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5269670505204682</v>
+        <v>0.57388531408888</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.215846907798545</v>
+        <v>3.243997865939592</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.273131354118619</v>
+        <v>-4.310909164955049</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10931957301037</v>
+        <v>1.094208448675798</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5831610131250949</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.140674188705575</v>
+        <v>3.168825146846622</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.286919406965666</v>
+        <v>-4.324697217802096</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.094241060503442</v>
+        <v>1.07912993616887</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5831610131250949</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.131110897337466</v>
+        <v>3.159261855478513</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.342439482858255</v>
+        <v>-4.380217293694685</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.209063866838609</v>
+        <v>1.193952742504037</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5831610131250949</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.268141734029669</v>
+        <v>3.296292692170716</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.166965223065786</v>
+        <v>-4.204743033902217</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.283820802747385</v>
+        <v>1.268709678412812</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5831610131250949</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.272708966021456</v>
+        <v>3.300859924162503</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.277901475707035</v>
+        <v>-4.315679286543466</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.215188330452092</v>
+        <v>1.20007720611752</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5362427495566832</v>
+        <v>0.5831610131250949</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.248450994782663</v>
+        <v>3.27660195292371</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.244237930234752</v>
+        <v>-4.282015741071183</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.157192062042455</v>
+        <v>1.142080937707882</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.6168245585973768</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.197187435467483</v>
+        <v>3.22533839360853</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.184385311031029</v>
+        <v>-4.22216312186746</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.191305496156077</v>
+        <v>1.176194371821504</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.6168245585973768</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.207359821899615</v>
+        <v>3.235510780040662</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.098141848004651</v>
+        <v>-4.135919658841082</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.220749151940488</v>
+        <v>1.205638027605916</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5699062950289651</v>
+        <v>0.6168245585973768</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.202306092473475</v>
+        <v>3.230457050614522</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.143448667403631</v>
+        <v>-4.181226478240062</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.194402199625421</v>
+        <v>1.179291075290849</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5290961320197343</v>
+        <v>0.576014395588146</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.169595770112462</v>
+        <v>3.197746728253509</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.172481772105932</v>
+        <v>-4.210259582942363</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.183340830777603</v>
+        <v>1.16822970644303</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5290961320197343</v>
+        <v>0.576014395588146</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.170147643145564</v>
+        <v>3.198298601286611</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.079671290655073</v>
+        <v>-4.117449101491504</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.149737715249312</v>
+        <v>1.13462659091474</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6219066134705936</v>
+        <v>0.6688248770390054</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.155106623907445</v>
+        <v>3.183257582048492</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.1240607599845</v>
+        <v>-4.161838570820931</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.133855403442142</v>
+        <v>1.118744279107569</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.577517144141166</v>
+        <v>0.6244354077095777</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.130346418234389</v>
+        <v>3.158497376375436</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.240602365089843</v>
+        <v>-4.278380175926274</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.082314469911728</v>
+        <v>1.067203345577155</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4609755390358232</v>
+        <v>0.507893802604235</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.055497163682907</v>
+        <v>3.083648121823954</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.12822536390717</v>
+        <v>-4.166003174743601</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.132756566215464</v>
+        <v>1.117645441880892</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4609755390358232</v>
+        <v>0.507893802604235</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.060988459513574</v>
+        <v>3.089139417654621</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.156005761808522</v>
+        <v>-4.193783572644953</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.133141608823462</v>
+        <v>1.11803048448889</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4331951411344701</v>
+        <v>0.4801134047028819</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.055817422541301</v>
+        <v>3.083968380682348</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.274386434538661</v>
+        <v>-4.312164245375092</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9241450597320604</v>
+        <v>0.9090339353974879</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.4128955525519057</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.853842431251369</v>
+        <v>2.881993389392416</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.383000512981992</v>
+        <v>-4.420778323818423</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000849089073933</v>
+        <v>0.9857379647393611</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.4128955525519057</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.973992091970574</v>
+        <v>3.002143050111621</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.347591474733849</v>
+        <v>-4.38536928557028</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.029525730475514</v>
+        <v>1.014414606140941</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3659772889834939</v>
+        <v>0.4128955525519057</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.988505118072897</v>
+        <v>3.016656076213944</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.309207812175698</v>
+        <v>-4.346985623012129</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.042298636841143</v>
+        <v>1.02718751250657</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4043609515416451</v>
+        <v>0.4512792151100569</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.008954756950156</v>
+        <v>3.037105715091204</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.132091482140532</v>
+        <v>-4.169869292976963</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109874197700511</v>
+        <v>1.094763073365939</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4043609515416451</v>
+        <v>0.4512792151100569</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.005683785795458</v>
+        <v>3.033834743936505</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.177183726974078</v>
+        <v>-4.214961537810509</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.092520691529006</v>
+        <v>1.077409567194433</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3424649083722553</v>
+        <v>0.3893831719406671</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.969229551655738</v>
+        <v>2.997380509796785</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.99780830573531</v>
+        <v>-4.035586116571741</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.158057835330927</v>
+        <v>1.142946710996355</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.499241666542974</v>
+        <v>0.5461599301113857</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.057082581864583</v>
+        <v>3.08523354000563</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042822519255916</v>
+        <v>-4.080600330092347</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120859605254275</v>
+        <v>1.105748480919702</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4688927712283694</v>
+        <v>0.5158110347967811</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.01968070000741</v>
+        <v>3.047831658148457</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309827029528351</v>
+        <v>-4.347604840364782</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019749363484246</v>
+        <v>1.004638239149674</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2745297331854208</v>
+        <v>0.3214479967538326</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.908754439520587</v>
+        <v>2.936905397661634</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.411024810965523</v>
+        <v>-4.448802621801955</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9784741728058788</v>
+        <v>0.9633630484713065</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2061209196401016</v>
+        <v>0.2530391832085134</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.866913073289897</v>
+        <v>2.895064031430944</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.404513844351211</v>
+        <v>-4.442291655187642</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9786785210059206</v>
+        <v>0.9635673966713483</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2061209196401016</v>
+        <v>0.2530391832085134</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.864513034844213</v>
+        <v>2.89266399298526</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.385475716643914</v>
+        <v>-4.423253527480345</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9828184912970845</v>
+        <v>0.967707366962512</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1479373083089071</v>
+        <v>0.1948555718773188</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.826127587253742</v>
+        <v>2.854278545394789</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.856659603902588</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.416602347794532</v>
+        <v>-4.454380158630963</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.089662240471027</v>
+        <v>1.074551116136455</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1479373083089071</v>
+        <v>0.1948555718773188</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.945421988887932</v>
+        <v>2.973572947028979</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.857492932888721</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43046910912845</v>
+        <v>-4.60114459369133</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.084948864923594</v>
+        <v>1.016678671098442</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1100793915750841</v>
+        <v>0.1510103202344126</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.923540567833772</v>
+        <v>2.948099125029369</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.863501463285647</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.38566493758852</v>
+        <v>-4.556340422151401</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.108879063936492</v>
+        <v>1.04060887011134</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1100793915750841</v>
+        <v>0.1510103202344126</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.929549098230698</v>
+        <v>2.954107655426295</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.761451684562847</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237921967353517</v>
+        <v>-4.408597451916398</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.065926473307692</v>
+        <v>0.9976562794825401</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2778867488099673</v>
+        <v>0.3188176774692958</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.928183733848827</v>
+        <v>2.952742291044424</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.764245306094328</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321743188628216</v>
+        <v>-4.492418673191096</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.035191606329294</v>
+        <v>0.9669214125041417</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2778867488099673</v>
+        <v>0.3188176774692958</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.930977355380308</v>
+        <v>2.955535912575905</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.764907654485986</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315590482575431</v>
+        <v>-4.486265967138312</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.038315037142066</v>
+        <v>0.9700448433169138</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2840394548627516</v>
+        <v>0.3249703835220801</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.935331327403637</v>
+        <v>2.959889884599234</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.763988131226096</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.332399780725933</v>
+        <v>-4.503075265288814</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.030671794621975</v>
+        <v>0.9624016007968232</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2672301567122499</v>
+        <v>0.3081610853715784</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.924326225253446</v>
+        <v>2.948884782449043</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.830323685022917</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.270101781949811</v>
+        <v>-4.440777266512692</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.121926547929245</v>
+        <v>1.053656354104093</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2672301567122499</v>
+        <v>0.3081610853715784</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.990661779050267</v>
+        <v>3.015220336245864</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.632615686737044</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.068311584284653</v>
+        <v>-4.238987068847534</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.004934628709436</v>
+        <v>0.9366644348842832</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4652483488814043</v>
+        <v>0.5061792775407328</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.911764696065887</v>
+        <v>2.936323253261484</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.702905919059219</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.119198296970848</v>
+        <v>-4.289873781533728</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.054870175957133</v>
+        <v>0.9865999821319806</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4143616361952098</v>
+        <v>0.4552925648545382</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.951522900776345</v>
+        <v>2.976081457971942</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.717533655175263</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.216938841595822</v>
+        <v>-4.387614326158703</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.030401694223187</v>
+        <v>0.9621315003980344</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3984723580622296</v>
+        <v>0.439403286721558</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.956617070012601</v>
+        <v>2.981175627208198</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.716069635999935</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.277148139601107</v>
+        <v>-4.447823624163988</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.004853955845745</v>
+        <v>0.9365837620205921</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3382630600569451</v>
+        <v>0.3791939887162735</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.919027472034102</v>
+        <v>2.943586029229699</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.714561254039863</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.20072609316918</v>
+        <v>-4.371401577732061</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.033914392458444</v>
+        <v>0.9656441986332915</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3382630600569451</v>
+        <v>0.3791939887162735</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.91751909007403</v>
+        <v>2.942077647269628</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.714424121475299</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.156352961530612</v>
+        <v>-4.327028446093492</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.051526512549307</v>
+        <v>0.9832563187241552</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.4235671203548421</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.944005836492608</v>
+        <v>2.968564393688205</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.70881791561389</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.178833312389497</v>
+        <v>-4.349508796952377</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.036928166344344</v>
+        <v>0.9686579725191917</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3826361916955137</v>
+        <v>0.456059031993203</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938399630631198</v>
+        <v>2.982453334809812</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.715199672641694</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.131177581828441</v>
+        <v>-4.301853066391321</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.062372215596571</v>
+        <v>0.9941020217714187</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4302919222565693</v>
+        <v>0.5037147625542586</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973374825995637</v>
+        <v>3.01742853017425</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.720092046016419</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.030659423329686</v>
+        <v>-4.201334907892567</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.107471852370798</v>
+        <v>1.039201658545645</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5308100807553239</v>
+        <v>0.6042329210530132</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038578094469614</v>
+        <v>3.082631798648228</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.706846718492292</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.091326013732075</v>
+        <v>-4.262001498294955</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.069959888685714</v>
+        <v>1.001689694860562</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4491117640367902</v>
+        <v>0.5225346043344795</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.976313776914366</v>
+        <v>3.020367481092979</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.71094442110292</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.046487612123677</v>
+        <v>-4.217163096686557</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.091992951939702</v>
+        <v>1.02372275811455</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4536551969816597</v>
+        <v>0.527078037279349</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.983137539291916</v>
+        <v>3.02719124347053</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.715105360733998</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.065986068365685</v>
+        <v>-4.236661552928565</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.088354509073977</v>
+        <v>1.020084315248825</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4055705557017554</v>
+        <v>0.4789933959994447</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.958447694155052</v>
+        <v>3.002501398333665</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.720984963261835</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.021783231279785</v>
+        <v>-4.192458715842664</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.111915246436174</v>
+        <v>1.043645052611022</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4497733927876558</v>
+        <v>0.5231962330853451</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.990848998934429</v>
+        <v>3.034902703113043</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.719394963731083</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.058762258943228</v>
+        <v>-4.229437743506107</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095533635840044</v>
+        <v>1.027263442014893</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5601701348766757</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.011443340478475</v>
+        <v>3.055497044657089</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.770642728914122</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.900470841403955</v>
+        <v>-4.071146325966835</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210097968038793</v>
+        <v>1.141827774213641</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4867472945789864</v>
+        <v>0.5601701348766757</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.062691105661515</v>
+        <v>3.106744809840128</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.769083433508376</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.692828837769479</v>
+        <v>-3.863504322332359</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291595474086837</v>
+        <v>1.223325280261685</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6943892982134625</v>
+        <v>0.7678121385111518</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.185717012436454</v>
+        <v>3.229770716615067</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.764031661746646</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.641796745046951</v>
+        <v>-3.812472229609831</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.306956539414118</v>
+        <v>1.238686345588966</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7454213909359905</v>
+        <v>0.8188442312336798</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.21128449630824</v>
+        <v>3.255338200486854</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.781219065839351</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.576572563919745</v>
+        <v>-3.747248048482626</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350233615957705</v>
+        <v>1.281963422132553</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8106455720631961</v>
+        <v>0.8840684123608854</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.267606409077268</v>
+        <v>3.311660113255882</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.777180038138631</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.539145543848611</v>
+        <v>-3.709821028411492</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361165396285439</v>
+        <v>1.292895202460287</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8158971100923778</v>
+        <v>0.8893199503900671</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.266718304194058</v>
+        <v>3.310772008372671</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.778436830469871</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.55925719988332</v>
+        <v>-3.818664070877711</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.354377526202796</v>
+        <v>1.25061477780504</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.826924455089797</v>
+        <v>0.9157182656866734</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.27459150352375</v>
+        <v>3.327867789881875</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.938994601491082</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.505512385456115</v>
+        <v>-3.764919256450506</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.536433222994889</v>
+        <v>1.432670474597132</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8369877645302589</v>
+        <v>0.9257815751271353</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.441187260209237</v>
+        <v>3.494463546567363</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>3.059107510708899</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.430730124431102</v>
+        <v>-3.690136995425493</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.686459036622711</v>
+        <v>1.582696288224954</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9117700255552715</v>
+        <v>1.000563836152148</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.606169526042062</v>
+        <v>3.659445812400188</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>3.050815486722758</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.404646040167294</v>
+        <v>-3.664052911161686</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.688600646342093</v>
+        <v>1.584837897944337</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9117700255552715</v>
+        <v>1.000563836152148</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.597877502055921</v>
+        <v>3.651153788414047</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>3.049008682306538</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.326514859318348</v>
+        <v>-3.585921730312739</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.718046314265451</v>
+        <v>1.614283565867695</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.074740647035833</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.640576784169911</v>
+        <v>3.693853070528037</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>3.066563088033329</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.317622397925065</v>
+        <v>-3.577029268919456</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.739157704549556</v>
+        <v>1.635394956151799</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9859468364389561</v>
+        <v>1.074740647035833</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.658131189896703</v>
+        <v>3.711407476254829</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>3.058418135437913</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.486098514894942</v>
+        <v>-3.745505385889334</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.663622305166189</v>
+        <v>1.559859556768432</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9579990007223753</v>
+        <v>1.046792811319252</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.633217535871339</v>
+        <v>3.686493822229465</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>3.039687832625775</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.788298986033359</v>
+        <v>-3.047705857027751</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.924011813898684</v>
+        <v>1.820249065500927</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9764447519488413</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.572278397436954</v>
+        <v>3.62555468379508</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>3.030351855122679</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.765577882350207</v>
+        <v>-3.024984753344598</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.92376427786885</v>
+        <v>1.820001529471093</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8876509413519647</v>
+        <v>0.9764447519488413</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.562942419933858</v>
+        <v>3.616218706291984</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.189257980973848</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.894779695644249</v>
+        <v>-3.154186566638641</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.030989678402402</v>
+        <v>1.927226930004645</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7584491280579224</v>
+        <v>0.847242938654799</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.644327457808602</v>
+        <v>3.697603744166728</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.226335803467495</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.049560702422505</v>
+        <v>-3.308967573416896</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.006155098184746</v>
+        <v>1.902392349786989</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7250814540034463</v>
+        <v>0.8138752646003229</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.661384675869563</v>
+        <v>3.714660962227689</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.22301115945704</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.042506012207331</v>
+        <v>-3.301912883201723</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.00565233026036</v>
+        <v>1.901889581862604</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7321361442186201</v>
+        <v>0.8209299548154967</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.662292845988212</v>
+        <v>3.715569132346338</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.233017313101782</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.015554787880843</v>
+        <v>-3.274961658875235</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.026438973635697</v>
+        <v>1.92267622523794</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.8358103008432158</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.681227207249585</v>
+        <v>3.734503493607711</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.417120445246741</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.151507795937159</v>
+        <v>-3.410914666931551</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.15616090255813</v>
+        <v>2.052398154160374</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.8358103008432158</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.865330339394545</v>
+        <v>3.918606625752671</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.409237140149735</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173915913742031</v>
+        <v>-3.433322784736423</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.139314350339175</v>
+        <v>2.035551601941418</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7470164902463392</v>
+        <v>0.8358103008432158</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.857447034297538</v>
+        <v>3.910723320655665</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.411291139699372</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.321921681221431</v>
+        <v>-3.581328552215822</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.082166042897052</v>
+        <v>1.978403294499296</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6602894813827977</v>
+        <v>0.7490832919796744</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.807464828529051</v>
+        <v>3.860741114887177</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.467544857421219</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.331362607109961</v>
+        <v>-3.590769478104352</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.134643390263487</v>
+        <v>2.030880641865731</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7827165989261892</v>
+        <v>0.8715104095230658</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.937174816776933</v>
+        <v>3.990451103135059</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.383636214445602</v>
+        <v>-3.643043085439994</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.116625041874532</v>
+        <v>2.012862293476775</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.8192368021874246</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.908701746920849</v>
+        <v>3.961978033278975</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.459966192046508</v>
+        <v>-3.7193730630409</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.084204863727945</v>
+        <v>1.980442115330188</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7304429915905479</v>
+        <v>0.8192368021874246</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.906813559814624</v>
+        <v>3.960089846172751</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.662219912370861</v>
+        <v>-3.921626783365253</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.998123605201066</v>
+        <v>1.894360856803309</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.5281892712661944</v>
+        <v>0.616983081863071</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.780281557222875</v>
+        <v>3.833557843581</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.823788337898117</v>
+        <v>-4.083195208892508</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.931930245200316</v>
+        <v>1.828167496802559</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4902001580651917</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.702645813154299</v>
+        <v>3.755922099512425</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.993441058337615</v>
+        <v>-4.215496500990061</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.877142563890435</v>
+        <v>1.788320386829457</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4902001580651917</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.715719220020218</v>
+        <v>3.768995506378344</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.995002701152475</v>
+        <v>-4.217058143804921</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.876517906764491</v>
+        <v>1.787695729703513</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4014063474683151</v>
+        <v>0.4902001580651917</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.715719220020218</v>
+        <v>3.768995506378344</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.47339945266623</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.022903488261948</v>
+        <v>-4.244958930914393</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.863881633047704</v>
+        <v>1.775059455986726</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3668094233253802</v>
+        <v>0.4556032339222569</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.693485106661459</v>
+        <v>3.746761393019585</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.470163896643429</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.145429590964842</v>
+        <v>-4.367485033617287</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.811635635943745</v>
+        <v>1.722813458882767</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2442833206224864</v>
+        <v>0.333077131219363</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.616733889016921</v>
+        <v>3.670010175375047</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.536869856233933</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.37594408715043</v>
+        <v>-4.597999529802876</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.786135797060013</v>
+        <v>1.697313619999035</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.01376882443689764</v>
+        <v>0.1025626350337743</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.545131150896072</v>
+        <v>3.598407437254198</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.67718157523578</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.632664905145255</v>
+        <v>-4.8547203477977</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.823759188863931</v>
+        <v>1.734937011802953</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.00585193911004056</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.62039412541163</v>
+        <v>3.673670411769756</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.74616184438142</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.786651322921395</v>
+        <v>-5.008706765573841</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.831144890899114</v>
+        <v>1.742322713838136</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.00585193911004056</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.68937439455727</v>
+        <v>3.742650680915396</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808525</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.732213046501541</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.73612941909373</v>
+        <v>-4.958184861746175</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.837404854550301</v>
+        <v>1.748582677489323</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.00585193911004056</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.675425596677391</v>
+        <v>3.728701883035517</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.744083535556955</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.988604573101454</v>
+        <v>-5.210660015753899</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.748285282002626</v>
+        <v>1.659463104941648</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.00585193911004056</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.687296085732805</v>
+        <v>3.740572372090931</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.745294070075898</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.281500329580866</v>
+        <v>-5.503555772233311</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.632337513929805</v>
+        <v>1.543515336868826</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.09464574970691719</v>
+        <v>-0.00585193911004056</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.688506620251748</v>
+        <v>3.741782906609874</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74941581230322</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.439044401310308</v>
+        <v>-5.661099843962753</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.573441627465349</v>
+        <v>1.484619450404371</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.1615475548471917</v>
+        <v>-0.07275374425031506</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.652487279394905</v>
+        <v>3.705763565753031</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.744493665039409</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.717008796893581</v>
+        <v>-5.939064239546027</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.457333721968229</v>
+        <v>1.368511544907251</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.1623734785357993</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.593793291559804</v>
+        <v>3.64706957791793</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.906697721738453</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.833976489532472</v>
+        <v>-6.056031932184918</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.572750701611717</v>
+        <v>1.483928524550739</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.2511672891326759</v>
+        <v>-0.1623734785357993</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.755997348258848</v>
+        <v>3.809273634616974</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.901544359702267</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.918694431753425</v>
+        <v>-6.140749874405871</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.53371016268715</v>
+        <v>1.444887985626172</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.3362833180607223</v>
+        <v>-0.2474895074638457</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.699774368865834</v>
+        <v>3.75305065522396</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.911773777270759</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.000629250022309</v>
+        <v>-6.222684692674754</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.511165652948088</v>
+        <v>1.422343475887109</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.3462180636478025</v>
+        <v>-0.2574242530509259</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.704042939082077</v>
+        <v>3.757319225440203</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.920699415726661</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.102605372270716</v>
+        <v>-6.324660814923162</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.479300842504627</v>
+        <v>1.390478665443649</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.4481941858962101</v>
+        <v>-0.3594003752993334</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.651782904188935</v>
+        <v>3.705059190547061</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.912852302970836</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.992599088793495</v>
+        <v>-6.21465453144594</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.515456243139691</v>
+        <v>1.426634066078713</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.4249896139789349</v>
+        <v>-0.3361958033820582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.657858534583476</v>
+        <v>3.711134820941602</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.917102313692811</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.849539513052569</v>
+        <v>-6.071594955705015</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.576930084158036</v>
+        <v>1.488107907097057</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.4169761873889556</v>
+        <v>-0.328182376792079</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.666916601259437</v>
+        <v>3.720192887617563</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436924</v>
+        <v>3.777251572436925</v>
       </c>
       <c r="C2029" t="n">
         <v>3.924363196575347</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.548092787580732</v>
+        <v>-5.770148230233177</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.704769657229307</v>
+        <v>1.615947480168328</v>
       </c>
       <c r="F2029" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.02673565132024169</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.855045519425076</v>
+        <v>3.908321805783202</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064762</v>
+        <v>3.812650101064763</v>
       </c>
       <c r="C2030" t="n">
         <v>3.925334374328057</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.572683031815916</v>
+        <v>-5.794738474468361</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.695904737287943</v>
+        <v>1.607082560226965</v>
       </c>
       <c r="F2030" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.02673565132024169</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.856016697177786</v>
+        <v>3.909292983535912</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859295</v>
+        <v>3.821198342859297</v>
       </c>
       <c r="C2031" t="n">
         <v>3.926177278707812</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.521644655809395</v>
+        <v>-5.743700098461841</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.717162992070307</v>
+        <v>1.628340815009329</v>
       </c>
       <c r="F2031" t="n">
-        <v>-0.1155294619171183</v>
+        <v>-0.02673565132024169</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.856859601557542</v>
+        <v>3.910135887915668</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354679</v>
+        <v>3.83174867735468</v>
       </c>
       <c r="C2032" t="n">
         <v>3.945215377581958</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.480505360942765</v>
+        <v>-5.70256080359521</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.752656808891105</v>
+        <v>1.663834631830126</v>
       </c>
       <c r="F2032" t="n">
-        <v>-0.07439016705048751</v>
+        <v>0.01440364354638912</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.900581277351665</v>
+        <v>3.953857563709792</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085615</v>
+        <v>3.825767093085616</v>
       </c>
       <c r="C2033" t="n">
         <v>3.761399373705892</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.369899220863163</v>
+        <v>-5.591954663515608</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.61308326104688</v>
+        <v>1.524261083985902</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.0362159730291145</v>
+        <v>0.1250097836259911</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.783128957523362</v>
+        <v>3.836405243881488</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462777</v>
+        <v>3.804703121462778</v>
       </c>
       <c r="C2034" t="n">
         <v>3.764901417779856</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.500479955394005</v>
+        <v>-5.722535398046451</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.564353011308507</v>
+        <v>1.475530834247528</v>
       </c>
       <c r="F2034" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.005570950904851379</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.708282560878819</v>
+        <v>3.761558847236945</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218594</v>
+        <v>3.775043021218595</v>
       </c>
       <c r="C2035" t="n">
         <v>3.749328236855939</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.335983621203043</v>
+        <v>-5.558039063855489</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.614578364060974</v>
+        <v>1.525756186999996</v>
       </c>
       <c r="F2035" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.005570950904851379</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.692709379954902</v>
+        <v>3.745985666313028</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462763</v>
+        <v>3.821044820462764</v>
       </c>
       <c r="C2036" t="n">
         <v>3.748515947292368</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.211503140479092</v>
+        <v>-5.433558583131537</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.663558266786984</v>
+        <v>1.574736089726006</v>
       </c>
       <c r="F2036" t="n">
-        <v>-0.09436476150172801</v>
+        <v>-0.005570950904851379</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.691897090391332</v>
+        <v>3.745173376749458</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832321184533045</v>
+        <v>3.832321184533046</v>
       </c>
       <c r="C2037" t="n">
         <v>3.758384726417441</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.221888335368981</v>
+        <v>-5.443943778021427</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.669272967956101</v>
+        <v>1.580450790895123</v>
       </c>
       <c r="F2037" t="n">
-        <v>-0.1047499563916173</v>
+        <v>-0.01595614579474069</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.695534752582471</v>
+        <v>3.748811038940597</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834429654120419</v>
+        <v>3.83442965412042</v>
       </c>
       <c r="C2038" t="n">
         <v>3.829221732193866</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.240476494091206</v>
+        <v>-5.462531936743652</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.732674710243636</v>
+        <v>1.643852533182658</v>
       </c>
       <c r="F2038" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.03454430451696605</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.755218863125561</v>
+        <v>3.808495149483687</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85513469588169</v>
+        <v>3.855134695881691</v>
       </c>
       <c r="C2039" t="n">
         <v>3.826090743012164</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.098759746276802</v>
+        <v>-5.320815188929247</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.786230420187696</v>
+        <v>1.697408243126719</v>
       </c>
       <c r="F2039" t="n">
-        <v>-0.1233381151138427</v>
+        <v>-0.03454430451696605</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.752087873943859</v>
+        <v>3.805364160301985</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815657372493993</v>
+        <v>3.815657372493999</v>
       </c>
       <c r="C2040" t="n">
         <v>3.830621637951556</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.997936612586374</v>
+        <v>-5.219992055238819</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.831090568603259</v>
+        <v>1.742268391542281</v>
       </c>
       <c r="F2040" t="n">
-        <v>-0.1108738996294888</v>
+        <v>-0.02208008903261222</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.764097298173863</v>
+        <v>3.817373584531989</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.478283254493697</v>
+        <v>3.848510247437695</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.822494961960489</v>
+        <v>3.773659748550566</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.785512594056867</v>
+        <v>-5.160402521484376</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.907933500023995</v>
+        <v>1.709142315643068</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.0561027964782797</v>
+        <v>0.05665514448079162</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.856156639847457</v>
+        <v>3.807652835239041</v>
       </c>
     </row>
   </sheetData>
